--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -1119,28 +1119,28 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.08782328920802665</v>
+        <v>0.0872820175588496</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3046577231035404</v>
+        <v>0.3035668257168786</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6075189876884329</v>
+        <v>0.6091511567242718</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06680752523784006</v>
+        <v>0.06843969427367891</v>
       </c>
       <c r="V7" t="n">
         <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06680752523784006</v>
+        <v>0.06843969427367891</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6075189876884329</v>
+        <v>0.6091511567242718</v>
       </c>
       <c r="Y7" t="n">
         <v>1.75</v>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>9.301357700623464</v>
+        <v>9.32634685872037</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.301357700623464</v>
+        <v>9.32634685872037</v>
       </c>
     </row>
     <row r="8">

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -605,55 +605,55 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="J2" t="n">
         <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6499535747446611</v>
+        <v>0.6566604127579737</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2243887341380377</v>
+        <v>0.225140712945591</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1256576911173011</v>
+        <v>0.1181988742964353</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06108374384236459</v>
+        <v>0.05753968253968256</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3543207301500569</v>
+        <v>0.3533540521549642</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3309504969275024</v>
+        <v>0.3312568815562585</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3147287729224407</v>
+        <v>0.3153890662887772</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2956328445946042</v>
+        <v>-0.3033063606030095</v>
       </c>
       <c r="V2" t="n">
         <v>-1</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2956328445946042</v>
+        <v>0.3033063606030095</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6456792698499432</v>
+        <v>0.6466459478450357</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.692307692307693</v>
+        <v>2.754098360655738</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>9.885606821282982</v>
+        <v>9.900407046454362</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.885606821282982</v>
+        <v>9.900407046454362</v>
       </c>
     </row>
     <row r="3">
@@ -703,25 +703,25 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3781597573306371</v>
+        <v>0.3938223938223938</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2780586450960567</v>
+        <v>0.277992277992278</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3437815975733064</v>
+        <v>0.3281853281853282</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05775401069518704</v>
+        <v>0.05800653594771243</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -739,13 +739,13 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09334360928615032</v>
+        <v>0.09340997638992898</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.09334360928615032</v>
+        <v>0.09340997638992898</v>
       </c>
       <c r="X3" t="n">
         <v>0.371402254382207</v>
@@ -801,25 +801,25 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4839055793991416</v>
+        <v>0.4748201438848921</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2859442060085837</v>
+        <v>0.2877697841726619</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2301502145922747</v>
+        <v>0.2374100719424461</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05975325487520622</v>
+        <v>0.05303030303030298</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -837,13 +837,13 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06992162857763712</v>
+        <v>0.06809605041355887</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06992162857763712</v>
+        <v>0.06809605041355887</v>
       </c>
       <c r="X4" t="n">
         <v>0.3558658345862208</v>
@@ -899,25 +899,25 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="J5" t="n">
         <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3306780664681976</v>
+        <v>0.30625</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3072105907833578</v>
+        <v>0.30625</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3621113427484446</v>
+        <v>0.3875</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05003100426564178</v>
+        <v>0.05332455562870297</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
@@ -935,19 +935,19 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1250478112870113</v>
+        <v>0.09965915403545589</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1250478112870113</v>
+        <v>0.09965915403545589</v>
       </c>
       <c r="X5" t="n">
         <v>0.4871591540354559</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -997,55 +997,55 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
         <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5657460116663153</v>
+        <v>0.557163531114327</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2699416684236418</v>
+        <v>0.2706222865412445</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1643123199100429</v>
+        <v>0.1722141823444284</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05842972440212746</v>
+        <v>0.05576776165011466</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4014381059865235</v>
+        <v>0.4004323421999652</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3129428747972791</v>
+        <v>0.3133599884648639</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2856190192161973</v>
+        <v>0.2862076693351709</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1643079056797918</v>
+        <v>-0.1567311889143619</v>
       </c>
       <c r="V6" t="n">
         <v>-1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1643079056797918</v>
+        <v>0.1567311889143619</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5985618940134765</v>
+        <v>0.5995676578000348</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.175675675675676</v>
+        <v>2.138888888888889</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>9.164221028491188</v>
+        <v>9.179619672699342</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.164221028491188</v>
+        <v>9.179619672699342</v>
       </c>
     </row>
     <row r="7">
@@ -1101,19 +1101,19 @@
         <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2102766798418972</v>
+        <v>0.2089704059251724</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2490118577075099</v>
+        <v>0.2474649543850726</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5407114624505929</v>
+        <v>0.543564639689755</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05680868838763575</v>
+        <v>0.06341479903998914</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
@@ -1131,19 +1131,19 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06843969427367891</v>
+        <v>0.06558651703451679</v>
       </c>
       <c r="V7" t="n">
         <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06843969427367891</v>
+        <v>0.06558651703451679</v>
       </c>
       <c r="X7" t="n">
         <v>0.6091511567242718</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1291,55 +1291,55 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1740031071983429</v>
+        <v>0.1656281233419296</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2278612118073537</v>
+        <v>0.2199449674863961</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5981356809943036</v>
+        <v>0.6144269091716742</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04491341991341979</v>
+        <v>0.05002121601793164</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08103257282901304</v>
+        <v>0.08097761801861028</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2903271265316048</v>
+        <v>0.2903499805399003</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6286403006393823</v>
+        <v>0.6286724014414894</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03050461964507867</v>
+        <v>0.0142454922698152</v>
       </c>
       <c r="V9" t="n">
         <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03050461964507867</v>
+        <v>0.0142454922698152</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6286403006393823</v>
+        <v>0.6286724014414894</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>9.624733415366299</v>
+        <v>9.625224891433593</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.624733415366299</v>
+        <v>9.625224891433593</v>
       </c>
     </row>
     <row r="10">
@@ -1413,28 +1413,28 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3609999082839134</v>
+        <v>0.3619446495385069</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3275469899490511</v>
+        <v>0.3271958842757376</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3114531017670354</v>
+        <v>0.3108594661857555</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.03516622590139018</v>
+        <v>-0.0342214846467967</v>
       </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.03516622590139018</v>
+        <v>-0.0342214846467967</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3609999082839134</v>
+        <v>0.3619446495385069</v>
       </c>
       <c r="Y10" t="n">
         <v>2.4</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>5.52705239653018</v>
+        <v>5.541516761466237</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.52705239653018</v>
+        <v>5.541516761466237</v>
       </c>
     </row>
     <row r="11">
@@ -1595,13 +1595,13 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1838937751487623</v>
+        <v>0.1832230959753477</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2459078968870776</v>
+        <v>0.2459087725764776</v>
       </c>
       <c r="S12" t="n">
-        <v>0.57019832796416</v>
+        <v>0.5708681314481747</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>0.42980167203584</v>
+        <v>0.4291318685518253</v>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>6.580434806066749</v>
+        <v>6.570179847916965</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.580434806066749</v>
+        <v>6.570179847916965</v>
       </c>
     </row>
     <row r="13">
@@ -1673,13 +1673,13 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7540168523407008</v>
+        <v>0.7541548770431651</v>
       </c>
       <c r="R13" t="n">
-        <v>0.131951511035547</v>
+        <v>0.1318757805956413</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1140316366237523</v>
+        <v>0.1139693423611936</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
-        <v>0.2459831476592992</v>
+        <v>0.2458451229568349</v>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr">
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>3.766099975590909</v>
+        <v>3.763986762415422</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.766099975590909</v>
+        <v>3.763986762415422</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AB26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,55 +605,55 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="J2" t="n">
         <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6499535747446611</v>
+        <v>0.6566604127579737</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2243887341380377</v>
+        <v>0.225140712945591</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1256576911173011</v>
+        <v>0.1181988742964353</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06108374384236459</v>
+        <v>0.05753968253968256</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3543207301500569</v>
+        <v>0.3533540521549642</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3309504969275024</v>
+        <v>0.3312568815562585</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3147287729224407</v>
+        <v>0.3153890662887772</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2956328445946042</v>
+        <v>-0.3033063606030095</v>
       </c>
       <c r="V2" t="n">
         <v>-1</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2956328445946042</v>
+        <v>0.3033063606030095</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6456792698499432</v>
+        <v>0.6466459478450357</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.692307692307693</v>
+        <v>2.754098360655738</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>9.885606821282982</v>
+        <v>9.900407046454362</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.885606821282982</v>
+        <v>9.900407046454362</v>
       </c>
     </row>
     <row r="3">
@@ -703,25 +703,25 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3781597573306371</v>
+        <v>0.3852691218130311</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2780586450960567</v>
+        <v>0.2776203966005666</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3437815975733064</v>
+        <v>0.3371104815864023</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05775401069518704</v>
+        <v>0.05942376950780304</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -739,13 +739,13 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09334360928615032</v>
+        <v>0.09378185778164039</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.09334360928615032</v>
+        <v>0.09378185778164039</v>
       </c>
       <c r="X3" t="n">
         <v>0.371402254382207</v>
@@ -801,25 +801,25 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4839055793991416</v>
+        <v>0.4748201438848921</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2859442060085837</v>
+        <v>0.2877697841726619</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2301502145922747</v>
+        <v>0.2374100719424461</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05975325487520622</v>
+        <v>0.05303030303030298</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -837,13 +837,13 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.06992162857763712</v>
+        <v>0.06809605041355887</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.06992162857763712</v>
+        <v>0.06809605041355887</v>
       </c>
       <c r="X4" t="n">
         <v>0.3558658345862208</v>
@@ -899,25 +899,25 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="J5" t="n">
         <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3306780664681976</v>
+        <v>0.30625</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3072105907833578</v>
+        <v>0.30625</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3621113427484446</v>
+        <v>0.3875</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05003100426564178</v>
+        <v>0.05332455562870297</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
@@ -935,19 +935,19 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1250478112870113</v>
+        <v>0.09965915403545589</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1250478112870113</v>
+        <v>0.09965915403545589</v>
       </c>
       <c r="X5" t="n">
         <v>0.4871591540354559</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -997,55 +997,55 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
         <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5657460116663153</v>
+        <v>0.557163531114327</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2699416684236418</v>
+        <v>0.2706222865412445</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1643123199100429</v>
+        <v>0.1722141823444284</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05842972440212746</v>
+        <v>0.05576776165011466</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4014381059865235</v>
+        <v>0.4004323421999652</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3129428747972791</v>
+        <v>0.3133599884648639</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2856190192161973</v>
+        <v>0.2862076693351709</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1643079056797918</v>
+        <v>-0.1567311889143619</v>
       </c>
       <c r="V6" t="n">
         <v>-1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1643079056797918</v>
+        <v>0.1567311889143619</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5985618940134765</v>
+        <v>0.5995676578000348</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.175675675675676</v>
+        <v>2.138888888888889</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>9.164221028491188</v>
+        <v>9.179619672699342</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.164221028491188</v>
+        <v>9.179619672699342</v>
       </c>
     </row>
     <row r="7">
@@ -1101,19 +1101,19 @@
         <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2102766798418972</v>
+        <v>0.2089704059251724</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2490118577075099</v>
+        <v>0.2474649543850726</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5407114624505929</v>
+        <v>0.543564639689755</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05680868838763575</v>
+        <v>0.06341479903998914</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
@@ -1131,19 +1131,19 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06843969427367891</v>
+        <v>0.06558651703451679</v>
       </c>
       <c r="V7" t="n">
         <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>0.06843969427367891</v>
+        <v>0.06558651703451679</v>
       </c>
       <c r="X7" t="n">
         <v>0.6091511567242718</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1291,55 +1291,55 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1740031071983429</v>
+        <v>0.1656281233419296</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2278612118073537</v>
+        <v>0.2199449674863961</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5981356809943036</v>
+        <v>0.6144269091716742</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04491341991341979</v>
+        <v>0.05002121601793164</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08103257282901304</v>
+        <v>0.08097761801861028</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2903271265316048</v>
+        <v>0.2903499805399003</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6286403006393823</v>
+        <v>0.6286724014414894</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.03050461964507867</v>
+        <v>0.0142454922698152</v>
       </c>
       <c r="V9" t="n">
         <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>0.03050461964507867</v>
+        <v>0.0142454922698152</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6286403006393823</v>
+        <v>0.6286724014414894</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>9.624733415366299</v>
+        <v>9.625224891433593</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.624733415366299</v>
+        <v>9.625224891433593</v>
       </c>
     </row>
     <row r="10">
@@ -1413,28 +1413,28 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3609999082839134</v>
+        <v>0.3619446495385069</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3275469899490511</v>
+        <v>0.3271958842757376</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3114531017670354</v>
+        <v>0.3108594661857555</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.03516622590139018</v>
+        <v>-0.0342214846467967</v>
       </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.03516622590139018</v>
+        <v>-0.0342214846467967</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3609999082839134</v>
+        <v>0.3619446495385069</v>
       </c>
       <c r="Y10" t="n">
         <v>2.4</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>5.52705239653018</v>
+        <v>5.541516761466237</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.52705239653018</v>
+        <v>5.541516761466237</v>
       </c>
     </row>
     <row r="11">
@@ -1552,27 +1552,27 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45665.66666666666</v>
+        <v>45527.58333333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>148</v>
       </c>
       <c r="F12" t="n">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>super cup</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1595,13 +1595,13 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1838937751487623</v>
+        <v>0.2776266437921275</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2459078968870776</v>
+        <v>0.32089015791687</v>
       </c>
       <c r="S12" t="n">
-        <v>0.57019832796416</v>
+        <v>0.4014831982910024</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
-        <v>0.42980167203584</v>
+        <v>0.5985168017089976</v>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr">
@@ -1621,36 +1621,36 @@
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>6.580434806066749</v>
+        <v>9.163530647347546</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.580434806066749</v>
+        <v>9.163530647347546</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CWcwKOO8</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45665.66666666666</v>
+        <v>45527.6875</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>148</v>
       </c>
       <c r="F13" t="n">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>super cup</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1673,13 +1673,13 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7540168523407008</v>
+        <v>0.3806237581102401</v>
       </c>
       <c r="R13" t="n">
-        <v>0.131951511035547</v>
+        <v>0.3414669869586378</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1140316366237523</v>
+        <v>0.2779092549311222</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
-        <v>0.2459831476592992</v>
+        <v>0.6193762418897599</v>
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr">
@@ -1699,10 +1699,1024 @@
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>3.766099975590909</v>
+        <v>9.48289698566442</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.766099975590909</v>
+        <v>9.48289698566442</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45528.5</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>148</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3727327830464132</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.2939945387713352</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3332726781822516</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="n">
+        <v>0.6272672169535868</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA14" t="n">
+        <v>9.603710957182615</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9.603710957182615</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45528.58333333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>148</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.6305413988571781</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.215998691712071</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.1534599094307509</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="n">
+        <v>0.3694586011428219</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA15" t="n">
+        <v>5.656558353635783</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.656558353635783</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>148</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1754682055520337</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.352904280039557</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4716275144084091</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="n">
+        <v>0.5283724855915909</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>8.089593226303167</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.089593226303167</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>148</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.4015671413155298</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3069511978135699</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2914816608709002</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="n">
+        <v>0.5984328586844702</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>9.162245446204167</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>9.162245446204167</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>148</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.6583867155497598</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.2259186812441538</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1156946032060865</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="n">
+        <v>0.3416132844502402</v>
+      </c>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>5.230235463168905</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>5.230235463168905</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45529.58333333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>148</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2831197728904012</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3208029954802057</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.3960772316293931</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="n">
+        <v>0.603922768370607</v>
+      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>9.246298150349546</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>9.246298150349546</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45529.59375</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>148</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.2004437737903364</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.3928490849840709</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.4067071412255927</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="n">
+        <v>0.5932928587744073</v>
+      </c>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>9.08355000011354</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>9.08355000011354</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45529.6875</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>148</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.4009290097477253</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3510835272714545</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2479874629808201</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="n">
+        <v>0.5990709902522747</v>
+      </c>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>9.172015494700583</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>9.172015494700583</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45530.6875</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>148</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.4711112882959352</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.3074691009281309</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.2214196107759338</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="n">
+        <v>0.5288887117040648</v>
+      </c>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>8.097496853718653</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>8.097496853718653</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45531.58333333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>148</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.1818912031461918</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.3304487078731354</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.487660088980673</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="n">
+        <v>0.512339911019327</v>
+      </c>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>7.844128123186052</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>7.844128123186052</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45531.6875</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>148</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.1514698788371654</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.360902966766516</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.4876271543963185</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="n">
+        <v>0.5123728456036815</v>
+      </c>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>7.844632364791681</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>7.844632364791681</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>148</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1484</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>super cup</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.1832230959753477</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.2459087725764776</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.5708681314481747</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="n">
+        <v>0.4291318685518253</v>
+      </c>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA25" t="n">
+        <v>6.570179847916965</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>6.570179847916965</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45665.66666666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>148</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1484</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>super cup</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.7541548770431651</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.1318757805956413</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.1139693423611936</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="n">
+        <v>0.2458451229568349</v>
+      </c>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.763986762415422</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>3.763986762415422</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB26"/>
+  <dimension ref="A1:AB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -703,25 +703,25 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="J3" t="n">
         <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3852691218130311</v>
+        <v>0.3997567403202919</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2776203966005666</v>
+        <v>0.2763024528684371</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3371104815864023</v>
+        <v>0.323940806811271</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05942376950780304</v>
+        <v>0.06447714815933714</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -739,13 +739,13 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09378185778164039</v>
+        <v>0.0950998015137699</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.09378185778164039</v>
+        <v>0.0950998015137699</v>
       </c>
       <c r="X3" t="n">
         <v>0.371402254382207</v>
@@ -1487,25 +1487,25 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3266613290632506</v>
+        <v>0.3165610142630745</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2786228983186549</v>
+        <v>0.2793185419968304</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3947157726180944</v>
+        <v>0.4041204437400951</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05561189993238691</v>
+        <v>0.05298289528577382</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1523,13 +1523,13 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0862042354979321</v>
+        <v>0.08550859181975656</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0862042354979321</v>
+        <v>0.08550859181975656</v>
       </c>
       <c r="X11" t="n">
         <v>0.364827133816587</v>
@@ -1708,27 +1708,27 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>ng6idLW1</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.5</v>
+        <v>45665.66666666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>148</v>
       </c>
       <c r="F14" t="n">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>super cup</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1748,27 +1748,27 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3727327830464132</v>
+        <v>0.1832230959753477</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2939945387713352</v>
+        <v>0.2459087725764776</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3332726781822516</v>
+        <v>0.5708681314481747</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
-        <v>0.6272672169535868</v>
+        <v>0.4291318685518253</v>
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr">
@@ -1777,36 +1777,36 @@
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>9.603710957182615</v>
+        <v>6.570179847916965</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.603710957182615</v>
+        <v>6.570179847916965</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>CWcwKOO8</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45665.66666666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>148</v>
       </c>
       <c r="F15" t="n">
-        <v>1481</v>
+        <v>1484</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>laliga</t>
+          <t>super cup</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1829,13 +1829,13 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6305413988571781</v>
+        <v>0.7541548770431651</v>
       </c>
       <c r="R15" t="n">
-        <v>0.215998691712071</v>
+        <v>0.1318757805956413</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1534599094307509</v>
+        <v>0.1139693423611936</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
-        <v>0.3694586011428219</v>
+        <v>0.2458451229568349</v>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr">
@@ -1855,867 +1855,9 @@
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>5.656558353635783</v>
+        <v>3.763986762415422</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.656558353635783</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45528.6875</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>espanyol</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>148</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.1754682055520337</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.352904280039557</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.4716275144084091</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="n">
-        <v>0.5283724855915909</v>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA16" t="n">
-        <v>8.089593226303167</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>8.089593226303167</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45528.6875</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>getafe</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>rayo vallecano</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>148</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.4015671413155298</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.3069511978135699</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.2914816608709002</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="n">
-        <v>0.5984328586844702</v>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA17" t="n">
-        <v>9.162245446204167</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>9.162245446204167</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45529.5</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>real madrid</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>valladolid</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>148</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.6583867155497598</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.2259186812441538</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.1156946032060865</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="n">
-        <v>0.3416132844502402</v>
-      </c>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA18" t="n">
-        <v>5.230235463168905</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>5.230235463168905</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45529.58333333334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>leganes</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>las palmas</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>148</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.2831197728904012</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.3208029954802057</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.3960772316293931</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="n">
-        <v>0.603922768370607</v>
-      </c>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA19" t="n">
-        <v>9.246298150349546</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>9.246298150349546</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45529.59375</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>alaves</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>betis</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>148</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.2004437737903364</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.3928490849840709</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.4067071412255927</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="n">
-        <v>0.5932928587744073</v>
-      </c>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA20" t="n">
-        <v>9.08355000011354</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>9.08355000011354</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ChPK4l66</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45529.6875</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>atl  madrid</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>girona</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>148</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.4009290097477253</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.3510835272714545</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.2479874629808201</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="n">
-        <v>0.5990709902522747</v>
-      </c>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA21" t="n">
-        <v>9.172015494700583</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>9.172015494700583</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>hpMqQeYq</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45530.6875</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>villarreal</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>celta vigo</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>148</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.4711112882959352</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.3074691009281309</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.2214196107759338</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="n">
-        <v>0.5288887117040648</v>
-      </c>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA22" t="n">
-        <v>8.097496853718653</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>8.097496853718653</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>4KmdZaBc</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45531.58333333334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>mallorca</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>sevilla</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>148</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.1818912031461918</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.3304487078731354</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.487660088980673</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="n">
-        <v>-2</v>
-      </c>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="n">
-        <v>0.512339911019327</v>
-      </c>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA23" t="n">
-        <v>7.844128123186052</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>7.844128123186052</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>8CpDVHAM</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45531.6875</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>rayo vallecano</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>barcelona</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>148</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.1514698788371654</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.360902966766516</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.4876271543963185</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="n">
-        <v>-2</v>
-      </c>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="n">
-        <v>0.5123728456036815</v>
-      </c>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA24" t="n">
-        <v>7.844632364791681</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>7.844632364791681</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>45665.66666666666</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>ath bilbao</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>barcelona</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>148</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1484</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>super cup</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.1832230959753477</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.2459087725764776</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.5708681314481747</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="n">
-        <v>-2</v>
-      </c>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="n">
-        <v>0.4291318685518253</v>
-      </c>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA25" t="n">
-        <v>6.570179847916965</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>6.570179847916965</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>CWcwKOO8</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45665.66666666666</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>real madrid</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>mallorca</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>148</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1484</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>super cup</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.7541548770431651</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0.1318757805956413</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0.1139693423611936</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="n">
-        <v>0.2458451229568349</v>
-      </c>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
-        </is>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.763986762415422</v>
-      </c>
-      <c r="AB26" t="n">
         <v>3.763986762415422</v>
       </c>
     </row>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB15"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,40 +530,45 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>emergency_fill</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>dif_prob_mod_bm</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>result_to_bet</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_result_to_bet</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>prob_result_to_bet</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>odd_to_bet</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -629,42 +634,43 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3533540521549642</v>
+        <v>0.3551871866268897</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3312568815562585</v>
+        <v>0.3308009955283355</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3153890662887772</v>
+        <v>0.3140118178447748</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
-        <v>-0.3033063606030095</v>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
+        <v>-0.301473226131084</v>
+      </c>
+      <c r="W2" t="n">
         <v>-1</v>
       </c>
-      <c r="W2" t="n">
-        <v>0.3033063606030095</v>
-      </c>
       <c r="X2" t="n">
-        <v>0.6466459478450357</v>
+        <v>0.301473226131084</v>
       </c>
       <c r="Y2" t="n">
+        <v>0.6448128133731104</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.754098360655738</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
-      <c r="AA2" t="n">
-        <v>9.900407046454362</v>
-      </c>
       <c r="AB2" t="n">
-        <v>9.900407046454362</v>
+        <v>9.872341027478399</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9.872341027478399</v>
       </c>
     </row>
     <row r="3">
@@ -727,42 +733,43 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3450016956237524</v>
+        <v>0.3445443678570443</v>
       </c>
       <c r="R3" t="n">
-        <v>0.371402254382207</v>
+        <v>0.3725972524486703</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2835960499940407</v>
+        <v>0.2828583796942853</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>0.0950998015137699</v>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
+        <v>0.09629479958023324</v>
+      </c>
+      <c r="W3" t="n">
         <v>0</v>
       </c>
-      <c r="W3" t="n">
-        <v>0.0950998015137699</v>
-      </c>
       <c r="X3" t="n">
-        <v>0.371402254382207</v>
+        <v>0.09629479958023324</v>
       </c>
       <c r="Y3" t="n">
+        <v>0.3725972524486703</v>
+      </c>
+      <c r="Z3" t="n">
         <v>3.4</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
-      <c r="AA3" t="n">
-        <v>5.686316458965599</v>
-      </c>
       <c r="AB3" t="n">
-        <v>5.686316458965599</v>
+        <v>5.704612355378683</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5.704612355378683</v>
       </c>
     </row>
     <row r="4">
@@ -825,42 +832,43 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2917897629546954</v>
+        <v>0.2888580769425779</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3558658345862208</v>
+        <v>0.3558202745189112</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3523444024590837</v>
+        <v>0.3553216485385109</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
-        <v>0.06809605041355887</v>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
+        <v>0.06805049034624927</v>
+      </c>
+      <c r="W4" t="n">
         <v>0</v>
       </c>
-      <c r="W4" t="n">
-        <v>0.06809605041355887</v>
-      </c>
       <c r="X4" t="n">
-        <v>0.3558658345862208</v>
+        <v>0.06805049034624927</v>
       </c>
       <c r="Y4" t="n">
+        <v>0.3558202745189112</v>
+      </c>
+      <c r="Z4" t="n">
         <v>3.3</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
-      <c r="AA4" t="n">
-        <v>5.448447683111589</v>
-      </c>
       <c r="AB4" t="n">
-        <v>5.448447683111589</v>
+        <v>5.447750140332682</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.447750140332682</v>
       </c>
     </row>
     <row r="5">
@@ -899,66 +907,67 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="L5" t="n">
-        <v>0.30625</v>
+        <v>0.3180446590223295</v>
       </c>
       <c r="M5" t="n">
-        <v>0.30625</v>
+        <v>0.3077851538925769</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3875</v>
+        <v>0.3741701870850936</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05332455562870297</v>
+        <v>0.04807084123972172</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1663911399929355</v>
+        <v>0.1662353179703218</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3464497059716086</v>
+        <v>0.3466310980339207</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4871591540354559</v>
+        <v>0.4871335839957573</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>0.09965915403545589</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
+        <v>0.1129633969106637</v>
+      </c>
+      <c r="W5" t="n">
         <v>2</v>
       </c>
-      <c r="W5" t="n">
-        <v>0.09965915403545589</v>
-      </c>
       <c r="X5" t="n">
-        <v>0.4871591540354559</v>
+        <v>0.1129633969106637</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z5" t="inlineStr">
+        <v>0.4871335839957573</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
-      <c r="AA5" t="n">
-        <v>7.458600703260249</v>
-      </c>
       <c r="AB5" t="n">
-        <v>7.458600703260249</v>
+        <v>7.458209215766893</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.458209215766893</v>
       </c>
     </row>
     <row r="6">
@@ -997,66 +1006,67 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="L6" t="n">
-        <v>0.557163531114327</v>
+        <v>0.5439668439257036</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2706222865412445</v>
+        <v>0.2767831294092551</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1722141823444284</v>
+        <v>0.1792500266650414</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05576776165011466</v>
+        <v>0.06262851961593885</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4004323421999652</v>
+        <v>0.4055413572813194</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3133599884648639</v>
+        <v>0.3122043685209249</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2862076693351709</v>
+        <v>0.2822542741977558</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>-0.1567311889143619</v>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
+        <v>-0.1384254866443842</v>
+      </c>
+      <c r="W6" t="n">
         <v>-1</v>
       </c>
-      <c r="W6" t="n">
-        <v>0.1567311889143619</v>
-      </c>
       <c r="X6" t="n">
-        <v>0.5995676578000348</v>
+        <v>0.1384254866443842</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.138888888888889</v>
-      </c>
-      <c r="Z6" t="inlineStr">
+        <v>0.5944586427186807</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.063583815028902</v>
+      </c>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
-      <c r="AA6" t="n">
-        <v>9.179619672699342</v>
-      </c>
       <c r="AB6" t="n">
-        <v>9.179619672699342</v>
+        <v>9.101398616678742</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>9.101398616678742</v>
       </c>
     </row>
     <row r="7">
@@ -1095,66 +1105,67 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="J7" t="n">
         <v>3.8</v>
       </c>
       <c r="K7" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2089704059251724</v>
+        <v>0.1982507288629737</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2474649543850726</v>
+        <v>0.2478134110787172</v>
       </c>
       <c r="N7" t="n">
-        <v>0.543564639689755</v>
+        <v>0.5539358600583091</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06341479903998914</v>
+        <v>0.0619195046439629</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0872820175588496</v>
+        <v>0.0930336616149489</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3035668257168786</v>
+        <v>0.3059103192054957</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6091511567242718</v>
+        <v>0.6010560191795553</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>0.06558651703451679</v>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
+        <v>0.04712015912124623</v>
+      </c>
+      <c r="W7" t="n">
         <v>2</v>
       </c>
-      <c r="W7" t="n">
-        <v>0.06558651703451679</v>
-      </c>
       <c r="X7" t="n">
-        <v>0.6091511567242718</v>
+        <v>0.04712015912124623</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z7" t="inlineStr">
+        <v>0.6010560191795553</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
-      <c r="AA7" t="n">
-        <v>9.32634685872037</v>
-      </c>
       <c r="AB7" t="n">
-        <v>9.32634685872037</v>
+        <v>9.202407078293673</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.202407078293673</v>
       </c>
     </row>
     <row r="8">
@@ -1217,42 +1228,43 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5528953169629541</v>
+        <v>0.5471808745807486</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2831583750474474</v>
+        <v>0.2857138081708761</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1639463079895984</v>
+        <v>0.1671053172483753</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>-0.05789531758064959</v>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>-0.06360975996285512</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.05789531758064959</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5528953169629541</v>
+        <v>-0.06360975996285512</v>
       </c>
       <c r="Y8" t="n">
+        <v>0.5471808745807486</v>
+      </c>
+      <c r="Z8" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
-      <c r="AA8" t="n">
-        <v>8.465047543023386</v>
-      </c>
       <c r="AB8" t="n">
-        <v>8.465047543023386</v>
+        <v>8.377557153860842</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.377557153860842</v>
       </c>
     </row>
     <row r="9">
@@ -1315,42 +1327,43 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08097761801861028</v>
+        <v>0.08251124533067621</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2903499805399003</v>
+        <v>0.2907346621830229</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6286724014414894</v>
+        <v>0.626754092486301</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>0.0142454922698152</v>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
+        <v>0.01232718331462679</v>
+      </c>
+      <c r="W9" t="n">
         <v>2</v>
       </c>
-      <c r="W9" t="n">
-        <v>0.0142454922698152</v>
-      </c>
       <c r="X9" t="n">
-        <v>0.6286724014414894</v>
+        <v>0.01232718331462679</v>
       </c>
       <c r="Y9" t="n">
+        <v>0.626754092486301</v>
+      </c>
+      <c r="Z9" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
-      <c r="AA9" t="n">
-        <v>9.625224891433593</v>
-      </c>
       <c r="AB9" t="n">
-        <v>9.625224891433593</v>
+        <v>9.595854817190469</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9.595854817190469</v>
       </c>
     </row>
     <row r="10">
@@ -1413,42 +1426,43 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3619446495385069</v>
+        <v>0.3626848147943531</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3271958842757376</v>
+        <v>0.3272059782742643</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3108594661857555</v>
+        <v>0.3101092069313825</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>-0.0342214846467967</v>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>-0.03348131939095045</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0342214846467967</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3619446495385069</v>
+        <v>-0.03348131939095045</v>
       </c>
       <c r="Y10" t="n">
+        <v>0.3626848147943531</v>
+      </c>
+      <c r="Z10" t="n">
         <v>2.4</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
-      <c r="AA10" t="n">
-        <v>5.541516761466237</v>
-      </c>
       <c r="AB10" t="n">
-        <v>5.541516761466237</v>
+        <v>5.552848986370671</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.552848986370671</v>
       </c>
     </row>
     <row r="11">
@@ -1511,42 +1525,43 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2799751019411993</v>
+        <v>0.2764868085573639</v>
       </c>
       <c r="R11" t="n">
-        <v>0.364827133816587</v>
+        <v>0.3660099208545817</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3551977642422137</v>
+        <v>0.3575032705880543</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>0.08550859181975656</v>
-      </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
+        <v>0.0866913788577513</v>
+      </c>
+      <c r="W11" t="n">
         <v>0</v>
       </c>
-      <c r="W11" t="n">
-        <v>0.08550859181975656</v>
-      </c>
       <c r="X11" t="n">
-        <v>0.364827133816587</v>
+        <v>0.0866913788577513</v>
       </c>
       <c r="Y11" t="n">
+        <v>0.3660099208545817</v>
+      </c>
+      <c r="Z11" t="n">
         <v>3.4</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
-      <c r="AA11" t="n">
-        <v>5.585648743972431</v>
-      </c>
       <c r="AB11" t="n">
-        <v>5.585648743972431</v>
+        <v>5.60375768467552</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.60375768467552</v>
       </c>
     </row>
     <row r="12">
@@ -1595,36 +1610,37 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2776266437921275</v>
+        <v>0.2721478018497692</v>
       </c>
       <c r="R12" t="n">
-        <v>0.32089015791687</v>
+        <v>0.3202098010190783</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4014831982910024</v>
+        <v>0.4076423971311525</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="n">
         <v>-2</v>
       </c>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="n">
-        <v>0.5985168017089976</v>
-      </c>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr">
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>0.5923576028688475</v>
+      </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
-      <c r="AA12" t="n">
-        <v>9.163530647347546</v>
-      </c>
       <c r="AB12" t="n">
-        <v>9.163530647347546</v>
+        <v>9.069230859649583</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.069230859649583</v>
       </c>
     </row>
     <row r="13">
@@ -1673,62 +1689,63 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3806237581102401</v>
+        <v>0.3836670302200452</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3414669869586378</v>
+        <v>0.3406700668715578</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2779092549311222</v>
+        <v>0.2756629029083971</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="n">
         <v>-1</v>
       </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="n">
-        <v>0.6193762418897599</v>
-      </c>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr">
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>0.6163329697799548</v>
+      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
-      <c r="AA13" t="n">
-        <v>9.48289698566442</v>
-      </c>
       <c r="AB13" t="n">
-        <v>9.48289698566442</v>
+        <v>9.43630327740629</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.43630327740629</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45665.66666666666</v>
+        <v>45528.5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>148</v>
       </c>
       <c r="F14" t="n">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1737,7 +1754,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>super cup</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1748,65 +1765,66 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1832230959753477</v>
+        <v>0.3767902132274593</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2459087725764776</v>
+        <v>0.2933858240380768</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5708681314481747</v>
+        <v>0.3298239627344639</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>-2</v>
-      </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="n">
-        <v>0.4291318685518253</v>
-      </c>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr">
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="n">
+        <v>0.6232097867725408</v>
+      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
-      <c r="AA14" t="n">
-        <v>6.570179847916965</v>
-      </c>
       <c r="AB14" t="n">
-        <v>6.570179847916965</v>
+        <v>9.541590084874063</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.541590084874063</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>CWcwKOO8</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45665.66666666666</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>148</v>
       </c>
       <c r="F15" t="n">
-        <v>1484</v>
+        <v>1481</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1815,7 +1833,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>super cup</t>
+          <t>laliga</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1829,36 +1847,432 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.7541548770431651</v>
+        <v>0.6125215638731244</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1318757805956413</v>
+        <v>0.2244131522127685</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1139693423611936</v>
+        <v>0.1630652839141071</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="n">
         <v>-1</v>
       </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="n">
-        <v>0.2458451229568349</v>
-      </c>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr">
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>0.3874784361268756</v>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
-      <c r="AA15" t="n">
-        <v>3.763986762415422</v>
-      </c>
       <c r="AB15" t="n">
-        <v>3.763986762415422</v>
+        <v>5.932449205262713</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.932449205262713</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>148</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1781672772446573</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3526352181742142</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4691975045811286</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="n">
+        <v>0.5308024954188714</v>
+      </c>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>8.126797644728946</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.126797644728946</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45528.6875</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>148</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3996119055953075</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.307872278781112</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2925158156235805</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="n">
+        <v>0.6003880944046925</v>
+      </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>9.192180883929369</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.192180883929369</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45529.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>148</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.6505344555610122</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.2306375156928695</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1188280287461184</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="n">
+        <v>0.3494655444389878</v>
+      </c>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>5.350456691465875</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.350456691465875</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45529.58333333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>148</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2796136529751624</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3214350883035954</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.3989512587212423</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="n">
+        <v>0.6010487412787577</v>
+      </c>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>9.202295650733383</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.202295650733383</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45529.59375</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>148</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1968185380794433</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.3932467173604851</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.4099347445600715</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="n">
+        <v>0.5900652554399285</v>
+      </c>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>9.034134107379158</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.034134107379158</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>ITdtTrn2</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45519.58333333334</v>
+        <v>45523.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,86 +610,86 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6566604127579737</v>
+        <v>0.4125736738703339</v>
       </c>
       <c r="M2" t="n">
-        <v>0.225140712945591</v>
+        <v>0.3163064833005893</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1181988742964353</v>
+        <v>0.2711198428290766</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05753968253968256</v>
+        <v>0.0538302277432714</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3551871866268897</v>
+        <v>0.3609667480078562</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3308009955283355</v>
+        <v>0.3275515608591498</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3140118178447748</v>
+        <v>0.3114816911329941</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.301473226131084</v>
+        <v>-0.05160692586247778</v>
       </c>
       <c r="W2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.301473226131084</v>
+        <v>-0.05160692586247778</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6448128133731104</v>
+        <v>0.3609667480078562</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.754098360655738</v>
+        <v>2.3</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>9.872341027478399</v>
+        <v>5.526544699494679</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.872341027478399</v>
+        <v>5.526544699494679</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>E1Xs9lu2</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45519.6875</v>
+        <v>45523.6875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3997567403202919</v>
+        <v>0.2804889172671714</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2763024528684371</v>
+        <v>0.2543099516555687</v>
       </c>
       <c r="N3" t="n">
-        <v>0.323940806811271</v>
+        <v>0.4652011310772599</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06447714815933714</v>
+        <v>0.04858919177427068</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3445443678570443</v>
+        <v>0.2915492590455471</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3725972524486703</v>
+        <v>0.3642274081226547</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2828583796942853</v>
+        <v>0.3442233328317983</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.09629479958023324</v>
+        <v>0.109917456467086</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.09629479958023324</v>
+        <v>0.109917456467086</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3725972524486703</v>
+        <v>0.3642274081226547</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,20 +766,20 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.704612355378683</v>
+        <v>5.576466704703596</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.704612355378683</v>
+        <v>5.576466704703596</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45520.58333333334</v>
+        <v>45527.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J4" t="n">
         <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4748201438848921</v>
+        <v>0.44</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2877697841726619</v>
+        <v>0.28</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2374100719424461</v>
+        <v>0.28</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05303030303030298</v>
+        <v>0.08225108225108224</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2888580769425779</v>
+        <v>0.4432017310763952</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3558202745189112</v>
+        <v>0.2527220757181619</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3553216485385109</v>
+        <v>0.304076193205443</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.06805049034624927</v>
+        <v>0.003201731076395209</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06805049034624927</v>
+        <v>0.003201731076395209</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3558202745189112</v>
+        <v>0.4432017310763952</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>5.447750140332682</v>
+        <v>6.785595047757168</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.447750140332682</v>
+        <v>6.785595047757168</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45520.6875</v>
+        <v>45527.6875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3180446590223295</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3077851538925769</v>
+        <v>0.2621082621082621</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3741701870850936</v>
+        <v>0.3276353276353276</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04807084123972172</v>
+        <v>0.05978260869565233</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1662353179703218</v>
+        <v>0.3716284788203622</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3466310980339207</v>
+        <v>0.3620539402766553</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4871335839957573</v>
+        <v>0.2663175809029825</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1129633969106637</v>
+        <v>-0.03862793143604804</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1129633969106637</v>
+        <v>-0.03862793143604804</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4871335839957573</v>
+        <v>0.3716284788203622</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,20 +964,20 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>7.458209215766893</v>
+        <v>5.689780045227999</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.458209215766893</v>
+        <v>5.689780045227999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45521.58333333334</v>
+        <v>45528.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,86 +1006,86 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>5.25</v>
+        <v>3.25</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5439668439257036</v>
+        <v>0.40822528363047</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2767831294092551</v>
+        <v>0.3028768233387358</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1792500266650414</v>
+        <v>0.2888978930307942</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06262851961593885</v>
+        <v>0.0650555615492503</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4055413572813194</v>
+        <v>0.4955530652721178</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3122043685209249</v>
+        <v>0.2606879838970469</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2822542741977558</v>
+        <v>0.2437589508308354</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1384254866443842</v>
+        <v>0.08732778164164784</v>
       </c>
       <c r="W6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1384254866443842</v>
+        <v>0.08732778164164784</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5944586427186807</v>
+        <v>0.4955530652721178</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.063583815028902</v>
+        <v>2.3</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>9.101398616678742</v>
+        <v>7.587114827924145</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.101398616678742</v>
+        <v>7.587114827924145</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45521.6875</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
         <v>4.75</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.7</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1982507288629737</v>
+        <v>0.5727204220045216</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2478134110787172</v>
+        <v>0.2319517709118312</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5539358600583091</v>
+        <v>0.1953278070836473</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0619195046439629</v>
+        <v>0.07781026640675748</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0930336616149489</v>
+        <v>0.6927641661020215</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3059103192054957</v>
+        <v>0.1807983382045923</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6010560191795553</v>
+        <v>0.1264374956933861</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.04712015912124623</v>
+        <v>0.1200437440975</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04712015912124623</v>
+        <v>0.1200437440975</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6010560191795553</v>
+        <v>0.6927641661020215</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1162,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>9.202407078293673</v>
+        <v>10.60649533869987</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.202407078293673</v>
+        <v>10.60649533869987</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45522.58333333334</v>
+        <v>45528.6875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.55</v>
+        <v>3.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6107906345436037</v>
+        <v>0.2659279778393352</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2629793009840516</v>
+        <v>0.2908587257617729</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1262300644723447</v>
+        <v>0.443213296398892</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05627240143369172</v>
+        <v>0.07440476190476186</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5471808745807486</v>
+        <v>0.1330263412532114</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2857138081708761</v>
+        <v>0.3716666620537907</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1671053172483753</v>
+        <v>0.495306996692998</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.06360975996285512</v>
+        <v>0.05209370029410604</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.06360975996285512</v>
+        <v>0.05209370029410604</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5471808745807486</v>
+        <v>0.495306996692998</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1261,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>8.377557153860842</v>
+        <v>7.583347419958862</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.377557153860842</v>
+        <v>7.583347419958862</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45522.6875</v>
+        <v>45528.6875</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.75</v>
+        <v>2.35</v>
       </c>
       <c r="J9" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1656281233419296</v>
+        <v>0.3974358974358974</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2199449674863961</v>
+        <v>0.3012820512820513</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6144269091716742</v>
+        <v>0.3012820512820513</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05002121601793164</v>
+        <v>0.07069320521619771</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08251124533067621</v>
+        <v>0.3707462725730166</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2907346621830229</v>
+        <v>0.3392849136912613</v>
       </c>
       <c r="S9" t="n">
-        <v>0.626754092486301</v>
+        <v>0.289968813735722</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.01232718331462679</v>
+        <v>-0.02668962486288079</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01232718331462679</v>
+        <v>-0.02668962486288079</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.626754092486301</v>
+        <v>0.3707462725730166</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.55</v>
+        <v>2.35</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1360,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>9.595854817190469</v>
+        <v>5.676273116163101</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.595854817190469</v>
+        <v>5.676273116163101</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45523.58333333334</v>
+        <v>45529.5</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>valladolid</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>espanyol</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,86 +1402,86 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.4</v>
+        <v>1.14</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3961661341853036</v>
+        <v>0.8071955719557197</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3067092651757188</v>
+        <v>0.1314575645756458</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2971246006389776</v>
+        <v>0.06134686346863469</v>
       </c>
       <c r="O10" t="n">
-        <v>0.051747311827957</v>
+        <v>0.08671679197994986</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3626848147943531</v>
+        <v>0.6484638063745553</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3272059782742643</v>
+        <v>0.2243093349409515</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3101092069313825</v>
+        <v>0.1272268586844932</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.03348131939095045</v>
+        <v>-0.1587317655811644</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.03348131939095045</v>
+        <v>0.1587317655811644</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3626848147943531</v>
+        <v>0.3515361936254447</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.4</v>
+        <v>4.772727272727272</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>5.552848986370671</v>
+        <v>5.382159155332928</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.552848986370671</v>
+        <v>5.382159155332928</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45523.6875</v>
+        <v>45529.58333333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1501,56 +1501,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3165610142630745</v>
+        <v>0.4063908234330192</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2793185419968304</v>
+        <v>0.3015157722244981</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4041204437400951</v>
+        <v>0.2920934043424825</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05298289528577382</v>
+        <v>0.06986325385694259</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2764868085573639</v>
+        <v>0.2977768912470203</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3660099208545817</v>
+        <v>0.3160042679908979</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3575032705880543</v>
+        <v>0.3862188407620817</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.0866913788577513</v>
+        <v>0.0941254364195992</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0866913788577513</v>
+        <v>0.0941254364195992</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3660099208545817</v>
+        <v>0.3862188407620817</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1558,29 +1558,29 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>5.60375768467552</v>
+        <v>5.913164298480501</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.60375768467552</v>
+        <v>5.913164298480501</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45527.58333333334</v>
+        <v>45529.59375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1599,67 +1599,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.3884711779448622</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.3007518796992481</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3107769423558897</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.07258064516129026</v>
+      </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2721478018497692</v>
+        <v>0.2157539465268551</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3202098010190783</v>
+        <v>0.4173571457739895</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4076423971311525</v>
+        <v>0.3668889076991553</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1166052660747414</v>
+      </c>
       <c r="W12" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1166052660747414</v>
+      </c>
       <c r="Y12" t="n">
-        <v>0.5923576028688475</v>
-      </c>
-      <c r="Z12" t="inlineStr"/>
+        <v>0.4173571457739895</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.1</v>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>9.069230859649583</v>
+        <v>6.389904151845228</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.069230859649583</v>
+        <v>6.389904151845228</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45527.6875</v>
+        <v>45529.6875</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1678,67 +1698,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5648296364052138</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2389663846329751</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1962039789618111</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.07299717826033625</v>
+      </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3836670302200452</v>
+        <v>0.4008373847314341</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3406700668715578</v>
+        <v>0.3562924221243946</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2756629029083971</v>
+        <v>0.2428701931441714</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.1639922516737797</v>
+      </c>
       <c r="W13" t="n">
         <v>-1</v>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="n">
+        <v>0.1639922516737797</v>
+      </c>
       <c r="Y13" t="n">
-        <v>0.6163329697799548</v>
-      </c>
-      <c r="Z13" t="inlineStr"/>
+        <v>0.5991626152685658</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.141618497109826</v>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>9.43630327740629</v>
+        <v>9.17341831019791</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.43630327740629</v>
+        <v>9.17341831019791</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.5</v>
+        <v>45530.6875</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1768,13 +1808,13 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3767902132274593</v>
+        <v>0.4993545418187478</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2933858240380768</v>
+        <v>0.2804995326043608</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3298239627344639</v>
+        <v>0.2201459255768913</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
@@ -1786,7 +1826,7 @@
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="n">
-        <v>0.6232097867725408</v>
+        <v>0.5006454581812522</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
@@ -1795,29 +1835,29 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>9.541590084874063</v>
+        <v>7.665081391866783</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.541590084874063</v>
+        <v>7.665081391866783</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45531.58333333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1844,16 +1884,16 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6125215638731244</v>
+        <v>0.1988318436953661</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2244131522127685</v>
+        <v>0.3211609572097018</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1630652839141071</v>
+        <v>0.480007199094932</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
@@ -1861,11 +1901,11 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
-        <v>0.3874784361268756</v>
+        <v>0.5199928009050681</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
@@ -1874,29 +1914,29 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>5.932449205262713</v>
+        <v>7.961296915788905</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.932449205262713</v>
+        <v>7.961296915788905</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45528.6875</v>
+        <v>45531.6875</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1926,13 +1966,13 @@
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1781672772446573</v>
+        <v>0.08238158578913075</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3526352181742142</v>
+        <v>0.3560933415480854</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4691975045811286</v>
+        <v>0.5615250726627838</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
@@ -1944,7 +1984,7 @@
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="n">
-        <v>0.5308024954188714</v>
+        <v>0.4384749273372162</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
@@ -1953,29 +1993,29 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>8.126797644728946</v>
+        <v>6.713225799635335</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.126797644728946</v>
+        <v>6.713225799635335</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45528.6875</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2005,13 +2045,13 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.3996119055953075</v>
+        <v>0.6623528285601014</v>
       </c>
       <c r="R17" t="n">
-        <v>0.307872278781112</v>
+        <v>0.1872974015694643</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2925158156235805</v>
+        <v>0.1503497698704343</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
@@ -2023,7 +2063,7 @@
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="n">
-        <v>0.6003880944046925</v>
+        <v>0.3376471714398986</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
@@ -2032,29 +2072,29 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>9.192180883929369</v>
+        <v>5.16951269311912</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.192180883929369</v>
+        <v>5.16951269311912</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45529.5</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2084,13 +2124,13 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.6505344555610122</v>
+        <v>0.4381715698294549</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2306375156928695</v>
+        <v>0.3407983196297328</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1188280287461184</v>
+        <v>0.2210301105408121</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
@@ -2102,7 +2142,7 @@
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="n">
-        <v>0.3494655444389878</v>
+        <v>0.5618284301705452</v>
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
@@ -2111,29 +2151,29 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>5.350456691465875</v>
+        <v>8.601817064647921</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.350456691465875</v>
+        <v>8.601817064647921</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45529.58333333334</v>
+        <v>45532.6875</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2160,16 +2200,16 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.2796136529751624</v>
+        <v>0.5809632128174886</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3214350883035954</v>
+        <v>0.2576139139960263</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3989512587212423</v>
+        <v>0.161422873186485</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
@@ -2177,11 +2217,11 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="n">
-        <v>0.6010487412787577</v>
+        <v>0.4190367871825114</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
@@ -2190,29 +2230,29 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>9.202295650733383</v>
+        <v>6.415620130878056</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.202295650733383</v>
+        <v>6.415620130878056</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45529.59375</v>
+        <v>45532.6875</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>alaves</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>betis</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2239,16 +2279,16 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1968185380794433</v>
+        <v>0.4529537764554369</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3932467173604851</v>
+        <v>0.3240503335688117</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4099347445600715</v>
+        <v>0.2229958899757515</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -2256,11 +2296,11 @@
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="n">
-        <v>0.5900652554399285</v>
+        <v>0.5470462235445631</v>
       </c>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
@@ -2269,10 +2309,958 @@
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>9.034134107379158</v>
+        <v>8.375495592859949</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.034134107379158</v>
+        <v>8.375495592859949</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45533.58333333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>148</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.420330272815787</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3434810282368668</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2361886989473463</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="n">
+        <v>0.5796697271842131</v>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>8.874974428829429</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8.874974428829429</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45533.6875</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>148</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.05774201082369097</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.310300051972702</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.6319579372036069</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="n">
+        <v>0.3680420627963931</v>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>5.634870587288073</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>5.634870587288073</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>148</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.5233242204946955</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.2860977031780409</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.1905780763272637</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>0.4766757795053045</v>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>7.29809606325622</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.29809606325622</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>148</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.2671457038321254</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.3703314384226164</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.3625228577452582</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="n">
+        <v>0.6296685615773836</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>9.640476499924562</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.640476499924562</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45535.59375</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>148</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.3245626240707248</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.3264104107580943</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.3490269651711809</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="n">
+        <v>0.6509730348288191</v>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>9.966656471827914</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.966656471827914</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>148</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.2766203608697107</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.3295395218269393</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.39384011730335</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="n">
+        <v>0.60615988269665</v>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>9.280549261813386</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.280549261813386</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>148</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.2261918547481493</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.3507932830357221</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.4230148622161287</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="n">
+        <v>0.5769851377838713</v>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>8.833872295730854</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.833872295730854</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>148</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.3721296237310348</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.3428384560458949</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.2850319202230702</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>0.6278703762689652</v>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>9.612945566563541</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9.612945566563541</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>148</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.3585421678402223</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.2962697422193015</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.3451880899404762</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="n">
+        <v>0.6414578321597777</v>
+      </c>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>9.82097492867906</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>9.82097492867906</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45536.58333333334</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>148</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.3262343704139893</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.3271789073670893</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.3465867222189214</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="n">
+        <v>0.6534132777810786</v>
+      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>10.00401756347338</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>10.00401756347338</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45536.59375</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>148</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.2083248705412798</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.3650334408897374</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.4266416885689829</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="n">
+        <v>0.5733583114310171</v>
+      </c>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>8.778344139558648</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.778344139558648</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45536.6875</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>148</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.5837498761127003</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.2654937267925118</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.1507563970947878</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="n">
+        <v>0.4162501238872997</v>
+      </c>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>6.372955205788907</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>6.372955205788907</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45519.58333333334</v>
+        <v>45527.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,86 +610,86 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6566604127579737</v>
+        <v>0.44</v>
       </c>
       <c r="M2" t="n">
-        <v>0.225140712945591</v>
+        <v>0.28</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1181988742964353</v>
+        <v>0.28</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05753968253968256</v>
+        <v>0.08225108225108224</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3551871866268897</v>
+        <v>0.4432017310763952</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3308009955283355</v>
+        <v>0.2527220757181619</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3140118178447748</v>
+        <v>0.304076193205443</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.301473226131084</v>
+        <v>0.003201731076395209</v>
       </c>
       <c r="W2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.301473226131084</v>
+        <v>0.003201731076395209</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6448128133731104</v>
+        <v>0.4432017310763952</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.754098360655738</v>
+        <v>2.1</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>9.872341027478399</v>
+        <v>6.785595047757168</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.872341027478399</v>
+        <v>6.785595047757168</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45519.6875</v>
+        <v>45527.6875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3997567403202919</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2763024528684371</v>
+        <v>0.2621082621082621</v>
       </c>
       <c r="N3" t="n">
-        <v>0.323940806811271</v>
+        <v>0.3276353276353276</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06447714815933714</v>
+        <v>0.05978260869565233</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3445443678570443</v>
+        <v>0.4053712514185447</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3725972524486703</v>
+        <v>0.3364516127719515</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2828583796942853</v>
+        <v>0.2581771358095038</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.09629479958023324</v>
+        <v>-0.0048851588378655</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.09629479958023324</v>
+        <v>-0.0048851588378655</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3725972524486703</v>
+        <v>0.4053712514185447</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.704612355378683</v>
+        <v>6.206395334802211</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.704612355378683</v>
+        <v>6.206395334802211</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45520.58333333334</v>
+        <v>45528.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4748201438848921</v>
+        <v>0.40822528363047</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2877697841726619</v>
+        <v>0.3028768233387358</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2374100719424461</v>
+        <v>0.2888978930307942</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05303030303030298</v>
+        <v>0.0650555615492503</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2888580769425779</v>
+        <v>0.491877216413348</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3558202745189112</v>
+        <v>0.2619556173757928</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3553216485385109</v>
+        <v>0.2461671662108592</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.06805049034624927</v>
+        <v>0.08365193278287797</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06805049034624927</v>
+        <v>0.08365193278287797</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3558202745189112</v>
+        <v>0.491877216413348</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>5.447750140332682</v>
+        <v>7.530836117658744</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.447750140332682</v>
+        <v>7.530836117658744</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45520.6875</v>
+        <v>45528.58333333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.55</v>
+        <v>4.75</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3180446590223295</v>
+        <v>0.5727204220045216</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3077851538925769</v>
+        <v>0.2319517709118312</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3741701870850936</v>
+        <v>0.1953278070836473</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04807084123972172</v>
+        <v>0.07781026640675748</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1662353179703218</v>
+        <v>0.6927641661020215</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3466310980339207</v>
+        <v>0.1807983382045923</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4871335839957573</v>
+        <v>0.1264374956933861</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1129633969106637</v>
+        <v>0.1200437440975</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1129633969106637</v>
+        <v>0.1200437440975</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4871335839957573</v>
+        <v>0.6927641661020215</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>7.458209215766893</v>
+        <v>10.60649533869987</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.458209215766893</v>
+        <v>10.60649533869987</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45521.58333333334</v>
+        <v>45528.6875</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,86 +1006,86 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.73</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>5.25</v>
+        <v>2.1</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5439668439257036</v>
+        <v>0.2659279778393352</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2767831294092551</v>
+        <v>0.2908587257617729</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1792500266650414</v>
+        <v>0.443213296398892</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06262851961593885</v>
+        <v>0.07440476190476186</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4055413572813194</v>
+        <v>0.1151454501749231</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3122043685209249</v>
+        <v>0.3743238198393466</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2822542741977558</v>
+        <v>0.5105307299857302</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1384254866443842</v>
+        <v>0.06731743358683828</v>
       </c>
       <c r="W6" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1384254866443842</v>
+        <v>0.06731743358683828</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5944586427186807</v>
+        <v>0.5105307299857302</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.063583815028902</v>
+        <v>2.1</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>9.101398616678742</v>
+        <v>7.816428840892513</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.101398616678742</v>
+        <v>7.816428840892513</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45521.6875</v>
+        <v>45528.6875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.75</v>
+        <v>2.35</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1982507288629737</v>
+        <v>0.3974358974358974</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2478134110787172</v>
+        <v>0.3012820512820513</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5539358600583091</v>
+        <v>0.3012820512820513</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0619195046439629</v>
+        <v>0.07069320521619771</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0930336616149489</v>
+        <v>0.3707462725730165</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3059103192054957</v>
+        <v>0.3392849136912614</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6010560191795553</v>
+        <v>0.2899688137357221</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.04712015912124623</v>
+        <v>-0.0266896248628809</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.04712015912124623</v>
+        <v>-0.0266896248628809</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6010560191795553</v>
+        <v>0.3707462725730165</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1162,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>9.202407078293673</v>
+        <v>5.6762731161631</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.202407078293673</v>
+        <v>5.6762731161631</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45522.58333333334</v>
+        <v>45529.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,86 +1204,86 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.55</v>
+        <v>1.13</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="K8" t="n">
-        <v>7.5</v>
+        <v>17</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6107906345436037</v>
+        <v>0.8216000257756871</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2629793009840516</v>
+        <v>0.1237877372168702</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1262300644723447</v>
+        <v>0.05461223700744273</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05627240143369172</v>
+        <v>0.07711261495748745</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5471808745807486</v>
+        <v>0.6662643304858075</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2857138081708761</v>
+        <v>0.2152653765870909</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1671053172483753</v>
+        <v>0.1184702929271016</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.06360975996285512</v>
+        <v>-0.1553356952898797</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.06360975996285512</v>
+        <v>0.1553356952898797</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5471808745807486</v>
+        <v>0.3337356695141925</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.55</v>
+        <v>5.204081632653061</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>8.377557153860842</v>
+        <v>5.109626040528882</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.377557153860842</v>
+        <v>5.109626040528882</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45522.6875</v>
+        <v>45529.58333333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.75</v>
+        <v>2.35</v>
       </c>
       <c r="J9" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>1.55</v>
+        <v>3.2</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1656281233419296</v>
+        <v>0.4012133468149647</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2199449674863961</v>
+        <v>0.3041456016177958</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6144269091716742</v>
+        <v>0.2946410515672397</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05002121601793164</v>
+        <v>0.06061256005490723</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08251124533067621</v>
+        <v>0.2977768912470203</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2907346621830229</v>
+        <v>0.3160042679908979</v>
       </c>
       <c r="S9" t="n">
-        <v>0.626754092486301</v>
+        <v>0.3862188407620817</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.01232718331462679</v>
+        <v>0.09157778919484205</v>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01232718331462679</v>
+        <v>0.09157778919484205</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.626754092486301</v>
+        <v>0.3862188407620817</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.55</v>
+        <v>3.2</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1360,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>9.595854817190469</v>
+        <v>5.913164298480501</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.595854817190469</v>
+        <v>5.913164298480501</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45523.58333333334</v>
+        <v>45529.59375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="J10" t="n">
         <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3961661341853036</v>
+        <v>0.3835842441740565</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3067092651757188</v>
+        <v>0.303155289750464</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2971246006389776</v>
+        <v>0.3132604660754795</v>
       </c>
       <c r="O10" t="n">
-        <v>0.051747311827957</v>
+        <v>0.06407724380074598</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3626848147943531</v>
+        <v>0.2157539465268552</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3272059782742643</v>
+        <v>0.4173571457739895</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3101092069313825</v>
+        <v>0.3668889076991553</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.03348131939095045</v>
+        <v>0.1142018560235255</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.03348131939095045</v>
+        <v>0.1142018560235255</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3626848147943531</v>
+        <v>0.4173571457739895</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,29 +1459,29 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>5.552848986370671</v>
+        <v>6.389904151845228</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.552848986370671</v>
+        <v>6.389904151845228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45523.6875</v>
+        <v>45529.6875</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1501,56 +1501,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3165610142630745</v>
+        <v>0.578368999421631</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2793185419968304</v>
+        <v>0.2342394447657606</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4041204437400951</v>
+        <v>0.1873915558126084</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05298289528577382</v>
+        <v>0.06728395061728398</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2764868085573639</v>
+        <v>0.5153492880843086</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3660099208545817</v>
+        <v>0.3018830255468939</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3575032705880543</v>
+        <v>0.1827676863687975</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.0866913788577513</v>
+        <v>-0.06301971133732243</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0866913788577513</v>
+        <v>-0.06301971133732243</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3660099208545817</v>
+        <v>0.5153492880843086</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1558,29 +1558,29 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>5.60375768467552</v>
+        <v>7.89020288480618</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.60375768467552</v>
+        <v>7.89020288480618</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45527.58333333334</v>
+        <v>45530.6875</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>celta vigo</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>valencia</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1599,67 +1599,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5031363194628501</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2778514003003799</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2190122802367701</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.07434212087416636</v>
+      </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2721478018497692</v>
+        <v>0.4083156274645323</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3202098010190783</v>
+        <v>0.330961166955077</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4076423971311525</v>
+        <v>0.2607232055803907</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.09482069199831777</v>
+      </c>
       <c r="W12" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.09482069199831777</v>
+      </c>
       <c r="Y12" t="n">
-        <v>0.5923576028688475</v>
-      </c>
-      <c r="Z12" t="inlineStr"/>
+        <v>0.4083156274645323</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.85</v>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>9.069230859649583</v>
+        <v>6.251474904929034</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.069230859649583</v>
+        <v>6.251474904929034</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45527.6875</v>
+        <v>45531.58333333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>sevilla</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>villarreal</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1678,67 +1698,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.4239097592909659</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3057709739147951</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2703192667942391</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.07226937946823897</v>
+      </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3836670302200452</v>
+        <v>0.2012766325295379</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3406700668715578</v>
+        <v>0.3211367435605933</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2756629029083971</v>
+        <v>0.4775866239098688</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.2072673571156297</v>
+      </c>
       <c r="W13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X13" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.2072673571156297</v>
+      </c>
       <c r="Y13" t="n">
-        <v>0.6163329697799548</v>
-      </c>
-      <c r="Z13" t="inlineStr"/>
+        <v>0.4775866239098688</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.45</v>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>9.43630327740629</v>
+        <v>7.31204145391586</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.43630327740629</v>
+        <v>7.31204145391586</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.5</v>
+        <v>45531.6875</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1757,67 +1797,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2026762097401587</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2390539909755718</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.5582697992842695</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.07260395596766345</v>
+      </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3767902132274593</v>
+        <v>0.08238158578913078</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2933858240380768</v>
+        <v>0.3560933415480854</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3298239627344639</v>
+        <v>0.5615250726627838</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.003255273378514389</v>
+      </c>
       <c r="W14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.003255273378514389</v>
+      </c>
       <c r="Y14" t="n">
-        <v>0.6232097867725408</v>
-      </c>
-      <c r="Z14" t="inlineStr"/>
+        <v>0.5615250726627838</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.67</v>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>9.541590084874063</v>
+        <v>8.597172540364665</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.541590084874063</v>
+        <v>8.597172540364665</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1836,67 +1896,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6007170362501659</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2387465144071173</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1605364493427168</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.0739853398362853</v>
+      </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6125215638731244</v>
+        <v>0.6623528285601014</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2244131522127685</v>
+        <v>0.1872974015694643</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1630652839141071</v>
+        <v>0.1503497698704343</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.06163579230993543</v>
+      </c>
       <c r="W15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.06163579230993543</v>
+      </c>
       <c r="Y15" t="n">
-        <v>0.3874784361268756</v>
-      </c>
-      <c r="Z15" t="inlineStr"/>
+        <v>0.6623528285601014</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.55</v>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>5.932449205262713</v>
+        <v>10.14088564688088</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.932449205262713</v>
+        <v>10.14088564688088</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45528.6875</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1915,67 +1995,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4265402843601895</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.3127962085308056</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.2606635071090047</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06565656565656575</v>
+      </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1781672772446573</v>
+        <v>0.5151387301867983</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3526352181742142</v>
+        <v>0.300936599063943</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4691975045811286</v>
+        <v>0.1839246707492587</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.08859844582660881</v>
+      </c>
       <c r="W16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.08859844582660881</v>
+      </c>
       <c r="Y16" t="n">
-        <v>0.5308024954188714</v>
-      </c>
-      <c r="Z16" t="inlineStr"/>
+        <v>0.5151387301867983</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.2</v>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>8.126797644728946</v>
+        <v>7.886979159521665</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.126797644728946</v>
+        <v>7.886979159521665</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45528.6875</v>
+        <v>45532.6875</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1994,67 +2094,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6900615424905067</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2003404478198245</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1095980096896687</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.07344156300513038</v>
+      </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.3996119055953075</v>
+        <v>0.6782378990541292</v>
       </c>
       <c r="R17" t="n">
-        <v>0.307872278781112</v>
+        <v>0.2056992415104</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2925158156235805</v>
+        <v>0.1160628594354707</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-0.01182364343637743</v>
+      </c>
       <c r="W17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.01182364343637743</v>
+      </c>
       <c r="Y17" t="n">
-        <v>0.6003880944046925</v>
-      </c>
-      <c r="Z17" t="inlineStr"/>
+        <v>0.6782378990541292</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.35</v>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>9.192180883929369</v>
+        <v>10.38409240380343</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.192180883929369</v>
+        <v>10.38409240380343</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45529.5</v>
+        <v>45532.6875</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2073,67 +2193,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.5713546681228354</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2623403124056963</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.1663050194714682</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.07375850193183653</v>
+      </c>
       <c r="P18" t="n">
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.6505344555610122</v>
+        <v>0.4532698396172484</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2306375156928695</v>
+        <v>0.3238631092199253</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1188280287461184</v>
+        <v>0.2228670511628263</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-0.118084828505587</v>
+      </c>
       <c r="W18" t="n">
         <v>-1</v>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="n">
+        <v>0.118084828505587</v>
+      </c>
       <c r="Y18" t="n">
-        <v>0.3494655444389878</v>
-      </c>
-      <c r="Z18" t="inlineStr"/>
+        <v>0.5467301603827516</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.172677595628415</v>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>5.350456691465875</v>
+        <v>8.370656539952014</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.350456691465875</v>
+        <v>8.370656539952014</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45529.58333333334</v>
+        <v>45533.58333333334</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2152,67 +2292,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.6054210908131636</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.220800633120095</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.1737782760667414</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.06564059315482451</v>
+      </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.2796136529751624</v>
+        <v>0.4191259123300792</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3214350883035954</v>
+        <v>0.3441946673292654</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3989512587212423</v>
+        <v>0.2366794203406553</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>-0.1862951784830844</v>
+      </c>
       <c r="W19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X19" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.1862951784830844</v>
+      </c>
       <c r="Y19" t="n">
-        <v>0.6010487412787577</v>
-      </c>
-      <c r="Z19" t="inlineStr"/>
+        <v>0.5808740876699208</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.378238341968912</v>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>9.202295650733383</v>
+        <v>8.89341366761057</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.202295650733383</v>
+        <v>8.89341366761057</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45529.59375</v>
+        <v>45533.6875</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2231,48 +2391,858 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.1432036275440261</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.1919223874301381</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.6648739850258356</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.07431743514217759</v>
+      </c>
       <c r="P20" t="n">
         <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1968185380794433</v>
+        <v>0.05860567409946173</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3932467173604851</v>
+        <v>0.3112300605303968</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4099347445600715</v>
+        <v>0.6301642653701416</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>-0.03470971965569403</v>
+      </c>
       <c r="W20" t="n">
+        <v>2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.03470971965569403</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.6301642653701416</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>9.648065922450336</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.648065922450336</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>148</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.6649581279960287</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.2061381778094315</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1289036941945398</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="n">
+        <v>0.3350418720039713</v>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>5.129624520960094</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.129624520960094</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>148</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.2833389815261664</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.3660599929724459</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.3506010255013876</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="n">
+        <v>0.633940007027554</v>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>9.705874031254252</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.705874031254252</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45535.59375</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>148</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.3013030370092886</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.3452447177301354</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.353452245260576</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="n">
         <v>-2</v>
       </c>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="n">
-        <v>0.5900652554399285</v>
-      </c>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr">
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>0.6465477547394241</v>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
-      <c r="AB20" t="n">
-        <v>9.034134107379158</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>9.034134107379158</v>
+      <c r="AB23" t="n">
+        <v>9.898903670893205</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.898903670893205</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>148</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.273626796577441</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.3300062404058863</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.3963669630166726</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="n">
+        <v>0.6036330369833274</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>9.241862247398695</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.241862247398695</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>148</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.1610742039322944</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.3692574763118636</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.469668319755842</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="n">
+        <v>0.530331680244158</v>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>8.119589276859568</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.119589276859568</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>148</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.372129623731035</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.3428384560458949</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.2850319202230702</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="n">
+        <v>0.627870376268965</v>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>9.612945566563537</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.612945566563537</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>148</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.3585421678402223</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.2962697422193015</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.3451880899404762</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="n">
+        <v>0.6414578321597777</v>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>9.82097492867906</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.82097492867906</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45536.58333333334</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>148</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.3261781594284425</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.3271225336354991</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.3466993069360583</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>0.6533006930639418</v>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>10.00229384660702</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>10.00229384660702</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45536.59375</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>148</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.2083400654105221</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.3650600658212159</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.4265998687682619</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="n">
+        <v>0.5734001312317381</v>
+      </c>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>8.778984417366186</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.778984417366186</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45536.6875</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>148</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.581116933013066</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.2666908478214459</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.152192219165488</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="n">
+        <v>0.418883066986934</v>
+      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>6.413266613450864</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>6.413266613450864</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -634,29 +634,29 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4432017310763952</v>
+        <v>0.4284736097345697</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2527220757181619</v>
+        <v>0.2555038255714536</v>
       </c>
       <c r="S2" t="n">
-        <v>0.304076193205443</v>
+        <v>0.3160225646939767</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.003201731076395209</v>
+        <v>-0.01152639026543034</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.003201731076395209</v>
+        <v>-0.01152639026543034</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4432017310763952</v>
+        <v>0.4284736097345697</v>
       </c>
       <c r="Z2" t="n">
         <v>2.1</v>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>6.785595047757168</v>
+        <v>5.765995743033519</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.785595047757168</v>
+        <v>5.765995743033519</v>
       </c>
     </row>
     <row r="3">
@@ -715,47 +715,47 @@
         <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4064516129032258</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2621082621082621</v>
+        <v>0.2596774193548387</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3276353276353276</v>
+        <v>0.3338709677419355</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05978260869565233</v>
+        <v>0.06970324361628721</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4053712514185447</v>
+        <v>0.3906618995084899</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3364516127719515</v>
+        <v>0.3403036898509849</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2581771358095038</v>
+        <v>0.2690344106405253</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.0048851588378655</v>
+        <v>-0.01578971339473589</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0048851588378655</v>
+        <v>-0.01578971339473589</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4053712514185447</v>
+        <v>0.3906618995084899</v>
       </c>
       <c r="Z3" t="n">
         <v>2.3</v>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>6.206395334802211</v>
+        <v>5.257161230832282</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.206395334802211</v>
+        <v>5.257161230832282</v>
       </c>
     </row>
     <row r="4">
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>7.530836117658744</v>
+        <v>6.619221981235865</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.530836117658744</v>
+        <v>6.619221981235865</v>
       </c>
     </row>
     <row r="5">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>10.60649533869987</v>
+        <v>9.322570029796969</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.60649533869987</v>
+        <v>9.322570029796969</v>
       </c>
     </row>
     <row r="6">
@@ -1030,29 +1030,29 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1151454501749231</v>
+        <v>0.1152265855333144</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3743238198393466</v>
+        <v>0.3748086521324477</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5105307299857302</v>
+        <v>0.5099647623342379</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.06731743358683828</v>
+        <v>0.06675146593534598</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06731743358683828</v>
+        <v>0.06675146593534598</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5105307299857302</v>
+        <v>0.5099647623342379</v>
       </c>
       <c r="Z6" t="n">
         <v>2.1</v>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>7.816428840892513</v>
+        <v>6.862627200162609</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.816428840892513</v>
+        <v>6.862627200162609</v>
       </c>
     </row>
     <row r="7">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>5.6762731161631</v>
+        <v>4.989155413155623</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.6762731161631</v>
+        <v>4.989155413155623</v>
       </c>
     </row>
     <row r="8">
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.109626040528882</v>
+        <v>4.491101449420304</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.109626040528882</v>
+        <v>4.491101449420304</v>
       </c>
     </row>
     <row r="9">
@@ -1327,29 +1327,29 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2977768912470203</v>
+        <v>0.2994745283481771</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3160042679908979</v>
+        <v>0.3158272070456328</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3862188407620817</v>
+        <v>0.3846982646061901</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.09157778919484205</v>
+        <v>0.09005721303895037</v>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.09157778919484205</v>
+        <v>0.09005721303895037</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3862188407620817</v>
+        <v>0.3846982646061901</v>
       </c>
       <c r="Z9" t="n">
         <v>3.2</v>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>5.913164298480501</v>
+        <v>5.176908228830668</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.913164298480501</v>
+        <v>5.176908228830668</v>
       </c>
     </row>
     <row r="10">
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>6.389904151845228</v>
+        <v>5.616400803186471</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.389904151845228</v>
+        <v>5.616400803186471</v>
       </c>
     </row>
     <row r="11">
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>7.89020288480618</v>
+        <v>6.935087094652715</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.89020288480618</v>
+        <v>6.935087094652715</v>
       </c>
     </row>
     <row r="12">
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>6.251474904929034</v>
+        <v>5.494728534700238</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.251474904929034</v>
+        <v>5.494728534700238</v>
       </c>
     </row>
     <row r="13">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>7.31204145391586</v>
+        <v>6.426912598187672</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.31204145391586</v>
+        <v>6.426912598187672</v>
       </c>
     </row>
     <row r="14">
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>8.597172540364665</v>
+        <v>7.556477470306555</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.597172540364665</v>
+        <v>7.556477470306555</v>
       </c>
     </row>
     <row r="15">
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>10.14088564688088</v>
+        <v>8.91332278837341</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.14088564688088</v>
+        <v>8.91332278837341</v>
       </c>
     </row>
     <row r="16">
@@ -2020,29 +2020,29 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5151387301867983</v>
+        <v>0.5132576304200798</v>
       </c>
       <c r="R16" t="n">
-        <v>0.300936599063943</v>
+        <v>0.3017161286840445</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1839246707492587</v>
+        <v>0.1850262408958759</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.08859844582660881</v>
+        <v>0.08671734605989023</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>0.08859844582660881</v>
+        <v>0.08671734605989023</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5151387301867983</v>
+        <v>0.5132576304200798</v>
       </c>
       <c r="Z16" t="n">
         <v>2.2</v>
@@ -2053,10 +2053,10 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>7.886979159521665</v>
+        <v>6.906939528702742</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.886979159521665</v>
+        <v>6.906939528702742</v>
       </c>
     </row>
     <row r="17">
@@ -2119,29 +2119,29 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.6782378990541292</v>
+        <v>0.6781773006802799</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2056992415104</v>
+        <v>0.2055595474375957</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1160628594354707</v>
+        <v>0.1162631518821245</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>-0.01182364343637743</v>
+        <v>-0.01188424181022674</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.01182364343637743</v>
+        <v>-0.01188424181022674</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.6782378990541292</v>
+        <v>0.6781773006802799</v>
       </c>
       <c r="Z17" t="n">
         <v>1.35</v>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>10.38409240380343</v>
+        <v>9.126273683849156</v>
       </c>
       <c r="AC17" t="n">
-        <v>10.38409240380343</v>
+        <v>9.126273683849156</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>8.370656539952014</v>
+        <v>7.357381424979361</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.370656539952014</v>
+        <v>7.357381424979361</v>
       </c>
     </row>
     <row r="19">
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>8.89341366761057</v>
+        <v>7.81685835638296</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.89341366761057</v>
+        <v>7.81685835638296</v>
       </c>
     </row>
     <row r="20">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>9.648065922450336</v>
+        <v>8.480159311998172</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.648065922450336</v>
+        <v>8.480159311998172</v>
       </c>
     </row>
     <row r="21">
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>5.129624520960094</v>
+        <v>4.508679096735082</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.129624520960094</v>
+        <v>4.508679096735082</v>
       </c>
     </row>
     <row r="22">
@@ -2607,10 +2607,10 @@
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>9.705874031254252</v>
+        <v>8.530969699916627</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.705874031254252</v>
+        <v>8.530969699916627</v>
       </c>
     </row>
     <row r="23">
@@ -2659,13 +2659,13 @@
         <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.3013030370092886</v>
+        <v>0.3014346680382699</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3452447177301354</v>
+        <v>0.3455993884842793</v>
       </c>
       <c r="S23" t="n">
-        <v>0.353452245260576</v>
+        <v>0.3529659434774507</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="n">
-        <v>0.6465477547394241</v>
+        <v>0.6470340565225492</v>
       </c>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="AB23" t="n">
-        <v>9.898903670893205</v>
+        <v>8.707177130040463</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.898903670893205</v>
+        <v>8.707177130040463</v>
       </c>
     </row>
     <row r="24">
@@ -2738,13 +2738,13 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.273626796577441</v>
+        <v>0.2752378042204544</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3300062404058863</v>
+        <v>0.3298825206222441</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3963669630166726</v>
+        <v>0.3948796751573014</v>
       </c>
       <c r="T24" t="n">
         <v>1</v>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="n">
-        <v>0.6036330369833274</v>
+        <v>0.6051203248426986</v>
       </c>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="AB24" t="n">
-        <v>9.241862247398695</v>
+        <v>8.143141462615393</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.241862247398695</v>
+        <v>8.143141462615393</v>
       </c>
     </row>
     <row r="25">
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="AB25" t="n">
-        <v>8.119589276859568</v>
+        <v>7.136706068263869</v>
       </c>
       <c r="AC25" t="n">
-        <v>8.119589276859568</v>
+        <v>7.136706068263869</v>
       </c>
     </row>
     <row r="26">
@@ -2923,10 +2923,10 @@
         </is>
       </c>
       <c r="AB26" t="n">
-        <v>9.612945566563537</v>
+        <v>8.449290305151825</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.612945566563537</v>
+        <v>8.449290305151825</v>
       </c>
     </row>
     <row r="27">
@@ -3002,10 +3002,10 @@
         </is>
       </c>
       <c r="AB27" t="n">
-        <v>9.82097492867906</v>
+        <v>8.632137535518275</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.82097492867906</v>
+        <v>8.632137535518275</v>
       </c>
     </row>
     <row r="28">
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="AB28" t="n">
-        <v>10.00229384660702</v>
+        <v>8.79150764375213</v>
       </c>
       <c r="AC28" t="n">
-        <v>10.00229384660702</v>
+        <v>8.79150764375213</v>
       </c>
     </row>
     <row r="29">
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="AB29" t="n">
-        <v>8.778984417366186</v>
+        <v>7.716280864497578</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.778984417366186</v>
+        <v>7.716280864497578</v>
       </c>
     </row>
     <row r="30">
@@ -3239,10 +3239,10 @@
         </is>
       </c>
       <c r="AB30" t="n">
-        <v>6.413266613450864</v>
+        <v>5.636935218884775</v>
       </c>
       <c r="AC30" t="n">
-        <v>6.413266613450864</v>
+        <v>5.636935218884775</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.5</v>
+        <v>45529.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,86 +610,86 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.45</v>
+        <v>1.17</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>7.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>15</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3875</v>
+        <v>0.8103727714748785</v>
       </c>
       <c r="M2" t="n">
-        <v>0.30625</v>
+        <v>0.126418152350081</v>
       </c>
       <c r="N2" t="n">
-        <v>0.30625</v>
+        <v>0.06320907617504051</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05332455562870297</v>
+        <v>0.05470085470085473</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4960972026575808</v>
+        <v>0.6663278450323864</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2607891745786062</v>
+        <v>0.3050264638899211</v>
       </c>
       <c r="S2" t="n">
-        <v>0.243113622763813</v>
+        <v>0.0286456910776924</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1085972026575808</v>
+        <v>-0.1440449264424921</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1085972026575808</v>
+        <v>-0.1440449264424921</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4960972026575808</v>
+        <v>0.6663278450323864</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.45</v>
+        <v>1.17</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>6.67601059590686</v>
+        <v>4.794443759594989</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.67601059590686</v>
+        <v>4.794443759594989</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.58333333334</v>
+        <v>45529.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,86 +709,86 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5848930481283423</v>
+        <v>0.4210526315789474</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2256016042780749</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1895053475935829</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0553791887125219</v>
+        <v>0.05555555555555536</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.719811769747927</v>
+        <v>0.3872285443819356</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1692255006907339</v>
+        <v>0.3413351593230441</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1109627295613389</v>
+        <v>0.2714362962950203</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1349187216195847</v>
+        <v>-0.0338240871970118</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1349187216195847</v>
+        <v>-0.0338240871970118</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.719811769747927</v>
+        <v>0.3872285443819356</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>9.6865512971104</v>
+        <v>3.244176162103757</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.6865512971104</v>
+        <v>3.244176162103757</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.6875</v>
+        <v>45529.59375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,86 +808,86 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2426484187164787</v>
+        <v>0.3875</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2957277603107084</v>
+        <v>0.30625</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4616238209728131</v>
+        <v>0.30625</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05671513445903686</v>
+        <v>0.05332455562870297</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1149527666941144</v>
+        <v>0.3263919874412956</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3746603790699798</v>
+        <v>0.3664227486918926</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5103868542359058</v>
+        <v>0.3071852638668119</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.04876303326309273</v>
+        <v>0.0601727486918926</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.04876303326309273</v>
+        <v>0.0601727486918926</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5103868542359058</v>
+        <v>0.3664227486918926</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>6.868307316867331</v>
+        <v>3.916054014986857</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.868307316867331</v>
+        <v>3.916054014986857</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.6875</v>
+        <v>45529.6875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,68 +907,1709 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>5.75</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3872529245663574</v>
+        <v>0.6174990513369328</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3162565550625252</v>
+        <v>0.2181925054377615</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2964905203711174</v>
+        <v>0.1643084432253056</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05399659863945572</v>
+        <v>0.05845469693718108</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3715621229028541</v>
+        <v>0.5797813497031056</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3391071041207257</v>
+        <v>0.3294347399719734</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2893307729764202</v>
+        <v>0.09078391032492103</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.01569080166350334</v>
+        <v>-0.03771770163382726</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.01569080166350334</v>
+        <v>-0.03771770163382726</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3715621229028541</v>
+        <v>0.5797813497031056</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>5.000134361267992</v>
+        <v>4.976026560098441</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.000134361267992</v>
-      </c>
+        <v>4.976026560098441</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45530.6875</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>148</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4844031193761248</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2721205758848231</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.2434763047390522</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.08083575121974929</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5016740642422536</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3597433105455177</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1385826252122287</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.01727094486612873</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.01727094486612873</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.5016740642422536</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>4.763802475505256</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.763802475505256</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45531.58333333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>148</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.4243156199677939</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.3011272141706924</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.2745571658615137</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.07124374676556844</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.2500778026122632</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3726256843748756</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3772965130128611</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.1027393471513474</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.1027393471513474</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.3772965130128611</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.406624938759072</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.406624938759072</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45531.6875</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>148</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2069849407241269</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2451137455943608</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5479013136815124</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.07361541107671132</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1928398026552932</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3569110152498295</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.4502491820948773</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>-0.0976521315866351</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.0976521315866351</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.4502491820948773</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.236764344170054</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.236764344170054</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45532.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>148</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.607741694196846</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2415383656423362</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.1507199401608178</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06157154673283705</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.532728437829796</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.335739327206231</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.131532234963973</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>-0.07501325636705003</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.07501325636705003</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.532728437829796</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.201725956040891</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.201725956040891</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45532.58333333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>148</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.40822528363047</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3028768233387358</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2888978930307942</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0650555615492503</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5850525782619274</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.2922211885621182</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.1227262331759545</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.1768272946314574</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.1768272946314574</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.5850525782619274</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>6.993891762757316</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>6.993891762757316</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45532.6875</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>148</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6965944272445821</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2058823529411765</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.09752321981424149</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.07936507936507931</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.6290267712561337</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3258733632977319</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.04509986544613449</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-0.06756765598844838</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.06756765598844838</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.6290267712561337</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>5.154072736536484</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.154072736536484</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45532.6875</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>148</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.564516129032258</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2661290322580645</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1693548387096774</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.07359307359307365</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.5720953040503188</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3120385940186546</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.1158661019310265</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.007579175018060824</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.007579175018060824</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.5720953040503188</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>5.321285820086639</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5.321285820086639</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45533.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>148</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5977796754910334</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2234557358383149</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1787645886706519</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06551410373066413</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4204619463354065</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.4135484493303611</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1659896043342324</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.1773177291556269</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.1773177291556269</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4204619463354065</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.232011105947279</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.232011105947279</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45533.6875</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>148</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.1338028169014084</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.1971830985915493</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.6690140845070423</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06766917293233088</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.1095442695736866</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3716008263317628</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.5188549040945507</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.1501591804124915</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.1501591804124915</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.5188549040945507</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.384546667483164</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.384546667483164</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45535.5</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>148</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.6026128975196423</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3283962066268059</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.06899089585355157</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>0.3973871024803577</v>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45535.58333333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>148</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2605763425862341</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3573867830214352</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.3820368743923306</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="n">
+        <v>0.6179631256076694</v>
+      </c>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45535.59375</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>148</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.2907810647806508</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.382296953048974</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3269219821703752</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="n">
+        <v>0.617703046951026</v>
+      </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>148</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2685651950715203</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3112031543727618</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.4202316505557179</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="n">
+        <v>0.5797683494442821</v>
+      </c>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45535.6875</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>148</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2203699945418482</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3530669975460241</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.4265630079121276</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="n">
+        <v>0.5734369920878724</v>
+      </c>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>148</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.3834002009856136</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.307801111427575</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.3087986875868114</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="n">
+        <v>0.6165997990143864</v>
+      </c>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45536.5</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>148</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.4448472741261926</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3287877790099757</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2263649468638317</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="n">
+        <v>0.5551527258738074</v>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45536.58333333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>148</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.4690429896587899</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.3287270855983357</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.2022299247428744</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="n">
+        <v>0.5309570103412101</v>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45536.59375</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>148</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.3131008911554063</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.3965117246275363</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.2903873842170576</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>0.6034882753724637</v>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45536.6875</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>148</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.6619200644201436</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.2801399281488614</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.05794000743099485</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="n">
+        <v>0.3380799355798564</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AD20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,10 +565,15 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>dif_prob_limited</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -577,20 +582,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.5</v>
+        <v>45530.6875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +615,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.17</v>
+        <v>1.9</v>
       </c>
       <c r="J2" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>15</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8103727714748785</v>
+        <v>0.4931506849315069</v>
       </c>
       <c r="M2" t="n">
-        <v>0.126418152350081</v>
+        <v>0.2602739726027398</v>
       </c>
       <c r="N2" t="n">
-        <v>0.06320907617504051</v>
+        <v>0.2465753424657534</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05470085470085473</v>
+        <v>0.06725146198830401</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6663278450323864</v>
+        <v>0.5016720865168708</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3050264638899211</v>
+        <v>0.359648085300758</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0286456910776924</v>
+        <v>0.1386798281823711</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1440449264424921</v>
+        <v>0.008521401585363908</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1440449264424921</v>
+        <v>0.008521401585363908</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6663278450323864</v>
+        <v>0.5016720865168708</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.17</v>
+        <v>1.9</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +672,32 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.794443759594989</v>
+        <v>0.008521401585363908</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.794443759594989</v>
+        <v>4.683465413385414</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.683465413385414</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.58333333334</v>
+        <v>45531.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -712,53 +720,53 @@
         <v>2.25</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4210526315789474</v>
+        <v>0.418835684482416</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3157894736842106</v>
+        <v>0.3039936419630439</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2771706735545401</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05555555555555536</v>
+        <v>0.06114273666455827</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3872285443819356</v>
+        <v>0.2500778026122632</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3413351593230441</v>
+        <v>0.3726256843748756</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2714362962950203</v>
+        <v>0.3772965130128611</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.0338240871970118</v>
+        <v>0.100125839458321</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0338240871970118</v>
+        <v>0.100125839458321</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3872285443819356</v>
+        <v>0.3772965130128611</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +774,32 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.244176162103757</v>
+        <v>0.100125839458321</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.244176162103757</v>
+        <v>4.382633505756986</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>4.382633505756986</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.59375</v>
+        <v>45531.6875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +819,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3875</v>
+        <v>0.2069849407241269</v>
       </c>
       <c r="M4" t="n">
-        <v>0.30625</v>
+        <v>0.2451137455943608</v>
       </c>
       <c r="N4" t="n">
-        <v>0.30625</v>
+        <v>0.5479013136815124</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05332455562870297</v>
+        <v>0.07361541107671132</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3263919874412956</v>
+        <v>0.1843210139632232</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3664227486918926</v>
+        <v>0.3578307310106046</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3071852638668119</v>
+        <v>0.4578482550261723</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.0601727486918926</v>
+        <v>-0.09005305865534013</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0601727486918926</v>
+        <v>-0.09005305865534013</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3664227486918926</v>
+        <v>0.4578482550261723</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +876,32 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>3.916054014986857</v>
+        <v>-0.09005305865534013</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.916054014986857</v>
+        <v>3.376280022348924</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.376280022348924</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ChPK4l66</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45529.6875</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +921,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="J5" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="K5" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6174990513369328</v>
+        <v>0.607741694196846</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2181925054377615</v>
+        <v>0.2415383656423362</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1643084432253056</v>
+        <v>0.1507199401608178</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05845469693718108</v>
+        <v>0.06157154673283705</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5797813497031056</v>
+        <v>0.5327281473088972</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3294347399719734</v>
+        <v>0.3356002045106954</v>
       </c>
       <c r="S5" t="n">
-        <v>0.09078391032492103</v>
+        <v>0.1316716481804073</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.03771770163382726</v>
+        <v>-0.07501354688794881</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.03771770163382726</v>
+        <v>-0.07501354688794881</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5797813497031056</v>
+        <v>0.5327281473088972</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +978,32 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4.976026560098441</v>
+        <v>-0.07501354688794881</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.976026560098441</v>
+        <v>4.201720622203384</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>4.201720622203384</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45530.6875</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1023,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4844031193761248</v>
+        <v>0.40822528363047</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2721205758848231</v>
+        <v>0.3028768233387358</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2434763047390522</v>
+        <v>0.2888978930307942</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08083575121974929</v>
+        <v>0.0650555615492503</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5016740642422536</v>
+        <v>0.4687177755798147</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3597433105455177</v>
+        <v>0.3442596753499815</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1385826252122287</v>
+        <v>0.1870225490702038</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.01727094486612873</v>
+        <v>0.0604924919493447</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01727094486612873</v>
+        <v>0.0604924919493447</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5016740642422536</v>
+        <v>0.4687177755798147</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1080,32 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>4.763802475505256</v>
+        <v>0.0604924919493447</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.763802475505256</v>
+        <v>4.85803531832731</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>4.85803531832731</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45531.58333333334</v>
+        <v>45532.6875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1125,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>9.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4243156199677939</v>
+        <v>0.6965944272445821</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3011272141706924</v>
+        <v>0.2058823529411765</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2745571658615137</v>
+        <v>0.09752321981424149</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07124374676556844</v>
+        <v>0.07936507936507931</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2500778026122632</v>
+        <v>0.6033202767489813</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3726256843748756</v>
+        <v>0.3360877833183922</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3772965130128611</v>
+        <v>0.06059193993262658</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1027393471513474</v>
+        <v>-0.09327415049560084</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1027393471513474</v>
+        <v>-0.09327415049560084</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3772965130128611</v>
+        <v>0.6033202767489813</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>1.33</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1182,32 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.406624938759072</v>
+        <v>-0.09327415049560084</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.406624938759072</v>
+        <v>4.682112663618009</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>4.682112663618009</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45531.6875</v>
+        <v>45532.6875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1227,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.5</v>
+        <v>1.65</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2069849407241269</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2451137455943608</v>
+        <v>0.2661290322580645</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5479013136815124</v>
+        <v>0.1693548387096774</v>
       </c>
       <c r="O8" t="n">
-        <v>0.07361541107671132</v>
+        <v>0.07359307359307365</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1928398026552932</v>
+        <v>0.5915942898402606</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3569110152498295</v>
+        <v>0.3204878649616577</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4502491820948773</v>
+        <v>0.08791784519808173</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.0976521315866351</v>
+        <v>0.02707816080800263</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.0976521315866351</v>
+        <v>0.02707816080800263</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4502491820948773</v>
+        <v>0.5915942898402606</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1284,32 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>3.236764344170054</v>
+        <v>0.02707816080800263</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.236764344170054</v>
+        <v>5.679278729337518</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>5.679278729337518</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45533.58333333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1329,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>6.25</v>
+        <v>5.25</v>
       </c>
       <c r="L9" t="n">
-        <v>0.607741694196846</v>
+        <v>0.5977796754910334</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2415383656423362</v>
+        <v>0.2234557358383149</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1507199401608178</v>
+        <v>0.1787645886706519</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06157154673283705</v>
+        <v>0.06551410373066413</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.532728437829796</v>
+        <v>0.4206086119737436</v>
       </c>
       <c r="R9" t="n">
-        <v>0.335739327206231</v>
+        <v>0.4133716076986076</v>
       </c>
       <c r="S9" t="n">
-        <v>0.131532234963973</v>
+        <v>0.1660197803276488</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.07501325636705003</v>
+        <v>-0.1771710635172898</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.07501325636705003</v>
+        <v>-0.1771710635172898</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.532728437829796</v>
+        <v>0.4206086119737436</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1386,32 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4.201725956040891</v>
+        <v>-0.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.201725956040891</v>
+        <v>2.484128285246358</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.484128285246358</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45533.6875</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1431,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="K10" t="n">
-        <v>3.25</v>
+        <v>1.4</v>
       </c>
       <c r="L10" t="n">
-        <v>0.40822528363047</v>
+        <v>0.1338028169014084</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3028768233387358</v>
+        <v>0.1971830985915493</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2888978930307942</v>
+        <v>0.6690140845070423</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0650555615492503</v>
+        <v>0.06766917293233088</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5850525782619274</v>
+        <v>0.106492155857118</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2922211885621182</v>
+        <v>0.3852108218483214</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1227262331759545</v>
+        <v>0.5082970222945606</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1768272946314574</v>
+        <v>-0.1607170622124816</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1768272946314574</v>
+        <v>-0.1607170622124816</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5850525782619274</v>
+        <v>0.5082970222945606</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,29 +1488,32 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>6.993891762757316</v>
+        <v>-0.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.993891762757316</v>
+        <v>3.289088847208685</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.289088847208685</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45535.5</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1500,87 +1532,64 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.6965944272445821</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.2058823529411765</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.09752321981424149</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.07936507936507931</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6290267712561337</v>
+        <v>0.6568144180861284</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3258733632977319</v>
+        <v>0.281495240464735</v>
       </c>
       <c r="S11" t="n">
-        <v>0.04509986544613449</v>
+        <v>0.06169034144913665</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
-        <v>-0.06756765598844838</v>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-0.06756765598844838</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="n">
-        <v>0.6290267712561337</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.33</v>
-      </c>
+        <v>0.3431855819138716</v>
+      </c>
+      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>5.154072736536484</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5.154072736536484</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45535.58333333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1599,87 +1608,64 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.564516129032258</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.2661290322580645</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.1693548387096774</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.07359307359307365</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5720953040503188</v>
+        <v>0.2974557878448269</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3120385940186546</v>
+        <v>0.4079569661749165</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1158661019310265</v>
+        <v>0.2945872459802565</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>0.007579175018060824</v>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.007579175018060824</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X12" t="inlineStr"/>
       <c r="Y12" t="n">
-        <v>0.5720953040503188</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.65</v>
-      </c>
+        <v>0.5920430338250835</v>
+      </c>
+      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>5.321285820086639</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>5.321285820086639</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45533.58333333334</v>
+        <v>45535.59375</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1698,87 +1684,64 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.5977796754910334</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.2234557358383149</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.1787645886706519</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.06551410373066413</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4204619463354065</v>
+        <v>0.3347767567908629</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4135484493303611</v>
+        <v>0.3892377863620541</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1659896043342324</v>
+        <v>0.2759854568470829</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>-0.1773177291556269</v>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="n">
-        <v>1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>-0.1773177291556269</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="X13" t="inlineStr"/>
       <c r="Y13" t="n">
-        <v>0.4204619463354065</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.57</v>
-      </c>
+        <v>0.6107622136379458</v>
+      </c>
+      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.232011105947279</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.232011105947279</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45533.6875</v>
+        <v>45535.6875</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1797,87 +1760,64 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="K14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.1338028169014084</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.1971830985915493</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.6690140845070423</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.06766917293233088</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1095442695736866</v>
+        <v>0.2934179288736286</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3716008263317628</v>
+        <v>0.3043245867870954</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5188549040945507</v>
+        <v>0.402257484339276</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>-0.1501591804124915</v>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.1501591804124915</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="X14" t="inlineStr"/>
       <c r="Y14" t="n">
-        <v>0.5188549040945507</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.4</v>
-      </c>
+        <v>0.597742515660724</v>
+      </c>
+      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>3.384546667483164</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.384546667483164</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45535.5</v>
+        <v>45535.6875</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1904,16 +1844,16 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6026128975196423</v>
+        <v>0.2203699945418482</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3283962066268059</v>
+        <v>0.3530669975460241</v>
       </c>
       <c r="S15" t="n">
-        <v>0.06899089585355157</v>
+        <v>0.4265630079121276</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
@@ -1921,11 +1861,11 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
-        <v>0.3973871024803577</v>
+        <v>0.5734369920878724</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
@@ -1935,24 +1875,25 @@
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1982,13 +1923,13 @@
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2605763425862341</v>
+        <v>0.3330507231381066</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3573867830214352</v>
+        <v>0.2967069643730315</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3820368743923306</v>
+        <v>0.370242312488862</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
@@ -2000,7 +1941,7 @@
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="n">
-        <v>0.6179631256076694</v>
+        <v>0.629757687511138</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
@@ -2010,24 +1951,25 @@
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45535.59375</v>
+        <v>45536.5</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2054,16 +1996,16 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.2907810647806508</v>
+        <v>0.4394102336995528</v>
       </c>
       <c r="R17" t="n">
-        <v>0.382296953048974</v>
+        <v>0.3408374465484529</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3269219821703752</v>
+        <v>0.2197523197519944</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
@@ -2071,11 +2013,11 @@
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="n">
-        <v>0.617703046951026</v>
+        <v>0.5605897663004472</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
@@ -2085,24 +2027,25 @@
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.58333333334</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2129,16 +2072,16 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2685651950715203</v>
+        <v>0.5090574845087475</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3112031543727618</v>
+        <v>0.353253626848028</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4202316505557179</v>
+        <v>0.1376888886432245</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
@@ -2146,11 +2089,11 @@
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="n">
-        <v>0.5797683494442821</v>
+        <v>0.4909425154912525</v>
       </c>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
@@ -2160,24 +2103,25 @@
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.59375</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2204,16 +2148,16 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.2203699945418482</v>
+        <v>0.3159420830748013</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3530669975460241</v>
+        <v>0.4032714540669728</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4265630079121276</v>
+        <v>0.2807864628582258</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
@@ -2221,11 +2165,11 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="n">
-        <v>0.5734369920878724</v>
+        <v>0.5967285459330272</v>
       </c>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
@@ -2235,24 +2179,25 @@
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.6875</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2282,13 +2227,13 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.3834002009856136</v>
+        <v>0.6587689867531538</v>
       </c>
       <c r="R20" t="n">
-        <v>0.307801111427575</v>
+        <v>0.2770756473041025</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3087986875868114</v>
+        <v>0.06415536594274387</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -2300,7 +2245,7 @@
       </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="n">
-        <v>0.6165997990143864</v>
+        <v>0.3412310132468462</v>
       </c>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
@@ -2310,306 +2255,7 @@
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>osasuna</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>celta vigo</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>148</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.4448472741261926</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.3287877790099757</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.2263649468638317</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="n">
-        <v>0.5551527258738074</v>
-      </c>
-      <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45536.58333333334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>sevilla</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>girona</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>148</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.4690429896587899</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.3287270855983357</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0.2022299247428744</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="n">
-        <v>0.5309570103412101</v>
-      </c>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45536.59375</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>getafe</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>148</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.3131008911554063</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0.3965117246275363</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.2903873842170576</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="n">
-        <v>0.6034882753724637</v>
-      </c>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45536.6875</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>real madrid</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>betis</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>148</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.6619200644201436</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0.2801399281488614</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.05794000743099485</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="n">
-        <v>0.3380799355798564</v>
-      </c>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD20"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,15 +565,10 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>dif_prob_limited</t>
+          <t>multiplier</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>multiplier</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -672,12 +667,9 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0.008521401585363908</v>
+        <v>4.683465413385414</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.683465413385414</v>
-      </c>
-      <c r="AD2" t="n">
         <v>4.683465413385414</v>
       </c>
     </row>
@@ -774,12 +766,9 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0.100125839458321</v>
+        <v>4.382633505756986</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.382633505756986</v>
-      </c>
-      <c r="AD3" t="n">
         <v>4.382633505756986</v>
       </c>
     </row>
@@ -876,12 +865,9 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-0.09005305865534013</v>
+        <v>3.376280022348924</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.376280022348924</v>
-      </c>
-      <c r="AD4" t="n">
         <v>3.376280022348924</v>
       </c>
     </row>
@@ -978,12 +964,9 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-0.07501354688794881</v>
+        <v>4.201720622203384</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.201720622203384</v>
-      </c>
-      <c r="AD5" t="n">
         <v>4.201720622203384</v>
       </c>
     </row>
@@ -1047,29 +1030,29 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4687177755798147</v>
+        <v>0.4687177755798148</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3442596753499815</v>
+        <v>0.3442596753499814</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1870225490702038</v>
+        <v>0.1870225490702039</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.0604924919493447</v>
+        <v>0.06049249194934475</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0604924919493447</v>
+        <v>0.06049249194934475</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4687177755798147</v>
+        <v>0.4687177755798148</v>
       </c>
       <c r="Z6" t="n">
         <v>2.3</v>
@@ -1080,12 +1063,9 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0.0604924919493447</v>
+        <v>4.85803531832731</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.85803531832731</v>
-      </c>
-      <c r="AD6" t="n">
         <v>4.85803531832731</v>
       </c>
     </row>
@@ -1182,12 +1162,9 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>-0.09327415049560084</v>
+        <v>4.682112663618009</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.682112663618009</v>
-      </c>
-      <c r="AD7" t="n">
         <v>4.682112663618009</v>
       </c>
     </row>
@@ -1284,12 +1261,9 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>0.02707816080800263</v>
+        <v>5.679278729337518</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.679278729337518</v>
-      </c>
-      <c r="AD8" t="n">
         <v>5.679278729337518</v>
       </c>
     </row>
@@ -1386,12 +1360,9 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>-0.15</v>
+        <v>2.484128285246358</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.484128285246358</v>
-      </c>
-      <c r="AD9" t="n">
         <v>2.484128285246358</v>
       </c>
     </row>
@@ -1488,12 +1459,9 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>-0.15</v>
+        <v>3.289088847208685</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.289088847208685</v>
-      </c>
-      <c r="AD10" t="n">
         <v>3.289088847208685</v>
       </c>
     </row>
@@ -1543,13 +1511,13 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6568144180861284</v>
+        <v>0.6568144180861283</v>
       </c>
       <c r="R11" t="n">
-        <v>0.281495240464735</v>
+        <v>0.2814952404647352</v>
       </c>
       <c r="S11" t="n">
-        <v>0.06169034144913665</v>
+        <v>0.06169034144913662</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
@@ -1561,7 +1529,7 @@
       </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="n">
-        <v>0.3431855819138716</v>
+        <v>0.3431855819138717</v>
       </c>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
@@ -1571,7 +1539,6 @@
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1647,7 +1614,6 @@
       </c>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1723,7 +1689,6 @@
       </c>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1799,7 +1764,6 @@
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1875,7 +1839,6 @@
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1951,7 +1914,6 @@
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2027,7 +1989,6 @@
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -2103,7 +2064,6 @@
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -2179,7 +2139,6 @@
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2255,7 +2214,6 @@
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45530.6875</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4931506849315069</v>
+        <v>0.5854612684547574</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2602739726027398</v>
+        <v>0.2495913828675545</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2465753424657534</v>
+        <v>0.1649473486776882</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06725146198830401</v>
+        <v>0.05435488883238682</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5016720865168708</v>
+        <v>0.5299375613515956</v>
       </c>
       <c r="R2" t="n">
-        <v>0.359648085300758</v>
+        <v>0.3357546466828741</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1386798281823711</v>
+        <v>0.1343077919655302</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.008521401585363908</v>
+        <v>-0.05552370710316179</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.008521401585363908</v>
+        <v>-0.05552370710316179</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5016720865168708</v>
+        <v>0.5299375613515956</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.683465413385414</v>
+        <v>4.711374581896096</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.683465413385414</v>
+        <v>4.711374581896096</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45531.58333333334</v>
+        <v>45532.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.418835684482416</v>
+        <v>0.4157043879907621</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3039936419630439</v>
+        <v>0.3187066974595842</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2771706735545401</v>
+        <v>0.2655889145496536</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06114273666455827</v>
+        <v>0.04589371980676349</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2500778026122632</v>
+        <v>0.4679788688718871</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3726256843748756</v>
+        <v>0.3424182063032361</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3772965130128611</v>
+        <v>0.1896029248248768</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.100125839458321</v>
+        <v>0.05227448088112496</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.100125839458321</v>
+        <v>0.05227448088112496</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3772965130128611</v>
+        <v>0.4679788688718871</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>4.382633505756986</v>
+        <v>5.16660377057429</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.382633505756986</v>
+        <v>5.16660377057429</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45531.6875</v>
+        <v>45532.6875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>5.25</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2069849407241269</v>
+        <v>0.7321711568938194</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2451137455943608</v>
+        <v>0.1812995245641839</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5479013136815124</v>
+        <v>0.08652931854199684</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07361541107671132</v>
+        <v>0.05061605061605046</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1843210139632232</v>
+        <v>0.6358624453782491</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3578307310106046</v>
+        <v>0.3086115268166349</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4578482550261723</v>
+        <v>0.055526027805116</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.09005305865534013</v>
+        <v>-0.0963087115155703</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.09005305865534013</v>
+        <v>-0.0963087115155703</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4578482550261723</v>
+        <v>0.6358624453782491</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>3.376280022348924</v>
+        <v>5.358274688910284</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.376280022348924</v>
+        <v>5.358274688910284</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45532.6875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.607741694196846</v>
+        <v>0.5885015844273427</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2415383656423362</v>
+        <v>0.2648257129923042</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1507199401608178</v>
+        <v>0.1466727025803531</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06157154673283705</v>
+        <v>0.04890788224121545</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5327281473088972</v>
+        <v>0.5915942898402606</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3356002045106954</v>
+        <v>0.3204878649616577</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1316716481804073</v>
+        <v>0.08791784519808173</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.07501354688794881</v>
+        <v>0.003092705412917951</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.07501354688794881</v>
+        <v>0.003092705412917951</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5327281473088972</v>
+        <v>0.5915942898402606</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4.201720622203384</v>
+        <v>5.905799690564663</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.201720622203384</v>
+        <v>5.905799690564663</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45533.58333333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="L6" t="n">
-        <v>0.40822528363047</v>
+        <v>0.550173120294781</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3028768233387358</v>
+        <v>0.2338235761252819</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2888978930307942</v>
+        <v>0.2160033035799371</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0650555615492503</v>
+        <v>0.06918217633473711</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4687177755798148</v>
+        <v>0.4567177506111351</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3442596753499814</v>
+        <v>0.4011109620053718</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1870225490702039</v>
+        <v>0.142171287383493</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.06049249194934475</v>
+        <v>-0.09345536968364598</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06049249194934475</v>
+        <v>-0.09345536968364598</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4687177755798148</v>
+        <v>0.4567177506111351</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>4.85803531832731</v>
+        <v>3.607536189625261</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.85803531832731</v>
+        <v>3.607536189625261</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45533.6875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.33</v>
+        <v>8</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>9.5</v>
+        <v>1.38</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6965944272445821</v>
+        <v>0.1190887124611667</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2058823529411765</v>
+        <v>0.1905419399378667</v>
       </c>
       <c r="N7" t="n">
-        <v>0.09752321981424149</v>
+        <v>0.6903693476009666</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07936507936507931</v>
+        <v>0.04963768115942035</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6033202767489813</v>
+        <v>0.106492155857118</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3360877833183922</v>
+        <v>0.3852108218483214</v>
       </c>
       <c r="S7" t="n">
-        <v>0.06059193993262658</v>
+        <v>0.5082970222945606</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.09327415049560084</v>
+        <v>-0.1820723253064059</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.09327415049560084</v>
+        <v>-0.1820723253064059</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6033202767489813</v>
+        <v>0.5082970222945606</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1162,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.682112663618009</v>
+        <v>3.23971724605642</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.682112663618009</v>
+        <v>3.23971724605642</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45535.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="L8" t="n">
-        <v>0.564516129032258</v>
+        <v>0.7566826593557231</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2661290322580645</v>
+        <v>0.1644962302947224</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1693548387096774</v>
+        <v>0.07882111034955448</v>
       </c>
       <c r="O8" t="n">
-        <v>0.07359307359307365</v>
+        <v>0.05724637681159428</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5915942898402606</v>
+        <v>0.641325106264287</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3204878649616577</v>
+        <v>0.2969699696794604</v>
       </c>
       <c r="S8" t="n">
-        <v>0.08791784519808173</v>
+        <v>0.06170492405625271</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.02707816080800263</v>
+        <v>-0.1153575530914361</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02707816080800263</v>
+        <v>-0.1153575530914361</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5915942898402606</v>
+        <v>0.641325106264287</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1261,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.679278729337518</v>
+        <v>5.223351170564668</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.679278729337518</v>
+        <v>5.223351170564668</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45533.58333333334</v>
+        <v>45535.58333333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>5.25</v>
+        <v>2.45</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5977796754910334</v>
+        <v>0.3342981186685962</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2234557358383149</v>
+        <v>0.2836468885672938</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1787645886706519</v>
+        <v>0.3820549927641099</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06551410373066413</v>
+        <v>0.06833642547928265</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4206086119737436</v>
+        <v>0.2432746552537438</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4133716076986076</v>
+        <v>0.4059696229824164</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1660197803276488</v>
+        <v>0.3507557217638398</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.1771710635172898</v>
+        <v>0.1223227344151226</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1771710635172898</v>
+        <v>0.1223227344151226</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4206086119737436</v>
+        <v>0.4059696229824164</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.57</v>
+        <v>3.3</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1360,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>2.484128285246358</v>
+        <v>5.024752965335175</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.484128285246358</v>
+        <v>5.024752965335175</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45533.6875</v>
+        <v>45535.59375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>2.63</v>
       </c>
       <c r="J10" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4</v>
+        <v>2.75</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1338028169014084</v>
+        <v>0.3599402826349265</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1971830985915493</v>
+        <v>0.2958259197905802</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6690140845070423</v>
+        <v>0.3442337975744933</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06766917293233088</v>
+        <v>0.05636450051849295</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.106492155857118</v>
+        <v>0.3608103508535314</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3852108218483214</v>
+        <v>0.387361788609618</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5082970222945606</v>
+        <v>0.2518278605368507</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.1607170622124816</v>
+        <v>0.0915358688190378</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607170622124816</v>
+        <v>0.0915358688190378</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5082970222945606</v>
+        <v>0.387361788609618</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,29 +1459,29 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>3.289088847208685</v>
+        <v>4.755902953368276</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.289088847208685</v>
+        <v>4.755902953368276</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45535.5</v>
+        <v>45535.6875</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1500,63 +1500,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3924050632911393</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.3037974683544304</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3037974683544304</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06182795698924726</v>
+      </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6568144180861283</v>
+        <v>0.2850745173118185</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2814952404647352</v>
+        <v>0.3138896305174972</v>
       </c>
       <c r="S11" t="n">
-        <v>0.06169034144913662</v>
+        <v>0.4010358521706843</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.09723838381625388</v>
+      </c>
       <c r="W11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X11" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.09723838381625388</v>
+      </c>
       <c r="Y11" t="n">
-        <v>0.3431855819138717</v>
-      </c>
-      <c r="Z11" t="inlineStr"/>
+        <v>0.4010358521706843</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.1</v>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.948330554050862</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.948330554050862</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45535.6875</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1575,63 +1599,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.3605514316012725</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2788971367974549</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3605514316012725</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.05457392082308221</v>
+      </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2974557878448269</v>
+        <v>0.2680095599457526</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4079569661749165</v>
+        <v>0.3623258091734967</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2945872459802565</v>
+        <v>0.3696646308807507</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.009113199279478179</v>
+      </c>
       <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.009113199279478179</v>
+      </c>
       <c r="Y12" t="n">
-        <v>0.5920430338250835</v>
-      </c>
-      <c r="Z12" t="inlineStr"/>
+        <v>0.3696646308807507</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.63</v>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.761619154292541</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.761619154292541</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45535.59375</v>
+        <v>45536.5</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1650,63 +1698,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.4603234298608499</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2775479503572771</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2621286197818729</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.05970030288538197</v>
+      </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3347767567908629</v>
+        <v>0.3330507231381066</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3892377863620541</v>
+        <v>0.2967069643730315</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2759854568470829</v>
+        <v>0.370242312488862</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.1081136927069891</v>
+      </c>
       <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.1081136927069891</v>
+      </c>
       <c r="Y13" t="n">
-        <v>0.6107622136379458</v>
-      </c>
-      <c r="Z13" t="inlineStr"/>
+        <v>0.370242312488862</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.6</v>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>4.669947259238117</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.669947259238117</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1725,63 +1797,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.4100200400801604</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2857715430861724</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3042084168336673</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06039355688724557</v>
+      </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2934179288736286</v>
+        <v>0.499160581656248</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3043245867870954</v>
+        <v>0.3154350035908005</v>
       </c>
       <c r="S14" t="n">
-        <v>0.402257484339276</v>
+        <v>0.1854044147529515</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.0891405415760877</v>
+      </c>
       <c r="W14" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.0891405415760877</v>
+      </c>
       <c r="Y14" t="n">
-        <v>0.597742515660724</v>
-      </c>
-      <c r="Z14" t="inlineStr"/>
+        <v>0.499160581656248</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.3</v>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>5.842381991328407</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.842381991328407</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.58333333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1800,63 +1896,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.4064516129032258</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2596774193548387</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.3338709677419355</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06970324361628721</v>
+      </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2203699945418482</v>
+        <v>0.5018938258153822</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3530669975460241</v>
+        <v>0.3319952681193868</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4265630079121276</v>
+        <v>0.166110906065231</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.09544221291215643</v>
+      </c>
       <c r="W15" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.09544221291215643</v>
+      </c>
       <c r="Y15" t="n">
-        <v>0.5734369920878724</v>
-      </c>
-      <c r="Z15" t="inlineStr"/>
+        <v>0.5018938258153822</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.3</v>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.932107177118169</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.932107177118169</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.59375</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1875,63 +1995,87 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.2606635071090047</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.3127962085308056</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.4265402843601895</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06565656565656575</v>
+      </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.3330507231381066</v>
+        <v>0.3310321684477963</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2967069643730315</v>
+        <v>0.3868944892678394</v>
       </c>
       <c r="S16" t="n">
-        <v>0.370242312488862</v>
+        <v>0.2820733422843643</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.07409828073703378</v>
+      </c>
       <c r="W16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="X16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.07409828073703378</v>
+      </c>
       <c r="Y16" t="n">
-        <v>0.629757687511138</v>
-      </c>
-      <c r="Z16" t="inlineStr"/>
+        <v>0.3868944892678394</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3</v>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>4.578090626125518</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.578090626125518</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45536.5</v>
+        <v>45536.6875</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1950,270 +2094,69 @@
           <t>laliga</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.725753243897075</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1702221244776776</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1040246316252474</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06812309137890527</v>
+      </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4394102336995528</v>
+        <v>0.6587689867531538</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3408374465484529</v>
+        <v>0.2770756473041025</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2197523197519944</v>
+        <v>0.06415536594274387</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-0.0669842571439212</v>
+      </c>
       <c r="W17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.0669842571439212</v>
+      </c>
       <c r="Y17" t="n">
-        <v>0.5605897663004472</v>
-      </c>
-      <c r="Z17" t="inlineStr"/>
+        <v>0.6587689867531538</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.29</v>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45536.58333333334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>sevilla</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>girona</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>148</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.5090574845087475</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.353253626848028</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.1376888886432245</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="n">
-        <v>0.4909425154912525</v>
-      </c>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45536.59375</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>getafe</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>148</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.3159420830748013</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.4032714540669728</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.2807864628582258</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="n">
-        <v>0.5967285459330272</v>
-      </c>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45536.6875</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>real madrid</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>betis</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>148</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.6587689867531538</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.2770756473041025</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.06415536594274387</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="n">
-        <v>0.3412310132468462</v>
-      </c>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>5.876977470339962</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>5.876977470339962</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45535.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>6.25</v>
       </c>
       <c r="K2" t="n">
-        <v>5.75</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5854612684547574</v>
+        <v>0.7547169811320755</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2495913828675545</v>
+        <v>0.1509433962264151</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1649473486776882</v>
+        <v>0.09433962264150944</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05435488883238682</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5299375613515956</v>
+        <v>0.6508405784276196</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3357546466828741</v>
+        <v>0.2865014175609947</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1343077919655302</v>
+        <v>0.06265800401138578</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.05552370710316179</v>
+        <v>-0.103876402704456</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.05552370710316179</v>
+        <v>-0.103876402704456</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5299375613515956</v>
+        <v>0.6508405784276196</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.711374581896096</v>
+        <v>5.431867327720162</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.711374581896096</v>
+        <v>5.431867327720162</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45532.58333333334</v>
+        <v>45535.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4157043879907621</v>
+        <v>0.3291472554182702</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3187066974595842</v>
+        <v>0.2916751063398825</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2655889145496536</v>
+        <v>0.3791776382418473</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04589371980676349</v>
+        <v>0.05491452991452994</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4679788688718871</v>
+        <v>0.2453936451940474</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3424182063032361</v>
+        <v>0.3459244475367921</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1896029248248768</v>
+        <v>0.4086819072691604</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.05227448088112496</v>
+        <v>0.02950426902731307</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>0.05227448088112496</v>
+        <v>0.02950426902731307</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4679788688718871</v>
+        <v>0.4086819072691604</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.16660377057429</v>
+        <v>4.351599757582885</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.16660377057429</v>
+        <v>4.351599757582885</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45535.59375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>2.8</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7321711568938194</v>
+        <v>0.3409090909090909</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1812995245641839</v>
+        <v>0.3181818181818181</v>
       </c>
       <c r="N4" t="n">
-        <v>0.08652931854199684</v>
+        <v>0.3409090909090909</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05061605061605046</v>
+        <v>0.04761904761904767</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6358624453782491</v>
+        <v>0.3912910675884506</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3086115268166349</v>
+        <v>0.3213656271933518</v>
       </c>
       <c r="S4" t="n">
-        <v>0.055526027805116</v>
+        <v>0.2873433052181975</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.0963087115155703</v>
+        <v>0.05038197667935973</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0963087115155703</v>
+        <v>0.05038197667935973</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6358624453782491</v>
+        <v>0.3912910675884506</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>5.358274688910284</v>
+        <v>4.386227627286668</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.358274688910284</v>
+        <v>4.386227627286668</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45532.6875</v>
+        <v>45535.6875</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5885015844273427</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2648257129923042</v>
+        <v>0.3170731707317074</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1466727025803531</v>
+        <v>0.3170731707317074</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04890788224121545</v>
+        <v>0.0512820512820511</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5915942898402606</v>
+        <v>0.2799594354301689</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3204878649616577</v>
+        <v>0.3087305780185021</v>
       </c>
       <c r="S5" t="n">
-        <v>0.08791784519808173</v>
+        <v>0.4113099865513289</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.003092705412917951</v>
+        <v>0.09423681581962157</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.003092705412917951</v>
+        <v>0.09423681581962157</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5915942898402606</v>
+        <v>0.4113099865513289</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>5.905799690564663</v>
+        <v>5.020553960049551</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.905799690564663</v>
+        <v>5.020553960049551</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45533.58333333334</v>
+        <v>45535.6875</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>2.75</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.550173120294781</v>
+        <v>0.3437815975733064</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2338235761252819</v>
+        <v>0.2780586450960567</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2160033035799371</v>
+        <v>0.3781597573306371</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06918217633473711</v>
+        <v>0.05775401069518704</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4567177506111351</v>
+        <v>0.2925257078685912</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4011109620053718</v>
+        <v>0.3520892050875199</v>
       </c>
       <c r="S6" t="n">
-        <v>0.142171287383493</v>
+        <v>0.3553850870438891</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.09345536968364598</v>
+        <v>-0.02277467028674796</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.09345536968364598</v>
+        <v>-0.02277467028674796</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4567177506111351</v>
+        <v>0.3553850870438891</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>3.607536189625261</v>
+        <v>3.303133433288927</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.607536189625261</v>
+        <v>3.303133433288927</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45533.6875</v>
+        <v>45536.5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>las palmas</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>real madrid</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>1.91</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>1.38</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1190887124611667</v>
+        <v>0.4931894569255263</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1905419399378667</v>
+        <v>0.2770564302140457</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6903693476009666</v>
+        <v>0.2297541128604281</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04963768115942035</v>
+        <v>0.06158029550729749</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.106492155857118</v>
+        <v>0.4653383307022608</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3852108218483214</v>
+        <v>0.3352370726217512</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5082970222945606</v>
+        <v>0.199424596675988</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.1820723253064059</v>
+        <v>-0.02785112622326552</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1820723253064059</v>
+        <v>-0.02785112622326552</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5082970222945606</v>
+        <v>0.4653383307022608</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.38</v>
+        <v>1.91</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1162,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>3.23971724605642</v>
+        <v>4.344658311786481</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.23971724605642</v>
+        <v>4.344658311786481</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="J8" t="n">
-        <v>5.75</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7566826593557231</v>
+        <v>0.3800403225806452</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1644962302947224</v>
+        <v>0.2923387096774194</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07882111034955448</v>
+        <v>0.3276209677419355</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05724637681159428</v>
+        <v>0.0525198938992042</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.641325106264287</v>
+        <v>0.4257474503218577</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2969699696794604</v>
+        <v>0.360667622841149</v>
       </c>
       <c r="S8" t="n">
-        <v>0.06170492405625271</v>
+        <v>0.2135849268369934</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.1153575530914361</v>
+        <v>0.04570712774121249</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1153575530914361</v>
+        <v>0.04570712774121249</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.641325106264287</v>
+        <v>0.4257474503218577</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1261,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.223351170564668</v>
+        <v>4.681986193518147</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.223351170564668</v>
+        <v>4.681986193518147</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.58333333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K9" t="n">
         <v>2.8</v>
       </c>
-      <c r="J9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.45</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.3342981186685962</v>
+        <v>0.4120836560805577</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2836468885672938</v>
+        <v>0.249419054996127</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3820549927641099</v>
+        <v>0.3384972889233152</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06833642547928265</v>
+        <v>0.05508336057535157</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2432746552537438</v>
+        <v>0.4149069107896232</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4059696229824164</v>
+        <v>0.3561979998417794</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3507557217638398</v>
+        <v>0.2288950893685975</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1223227344151226</v>
+        <v>0.002823254709065526</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1223227344151226</v>
+        <v>0.002823254709065526</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4059696229824164</v>
+        <v>0.4149069107896232</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1360,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>5.024752965335175</v>
+        <v>4.14845238223409</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.024752965335175</v>
+        <v>4.14845238223409</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.59375</v>
+        <v>45536.59375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="K10" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3599402826349265</v>
+        <v>0.2719249862107005</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2958259197905802</v>
+        <v>0.3281853281853282</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3442337975744933</v>
+        <v>0.3998896856039714</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05636450051849295</v>
+        <v>0.05070993914807298</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3608103508535314</v>
+        <v>0.3616578616745702</v>
       </c>
       <c r="R10" t="n">
-        <v>0.387361788609618</v>
+        <v>0.3606925673308696</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2518278605368507</v>
+        <v>0.2776495709945602</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.0915358688190378</v>
+        <v>0.08973287546386971</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0915358688190378</v>
+        <v>0.08973287546386971</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.387361788609618</v>
+        <v>0.3616578616745702</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,29 +1459,29 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>4.755902953368276</v>
+        <v>4.482733432872568</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.755902953368276</v>
+        <v>4.482733432872568</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.6875</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1501,56 +1501,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.4</v>
+        <v>1.29</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>5.75</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1</v>
+        <v>9.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3924050632911393</v>
+        <v>0.7352198929977456</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3037974683544304</v>
+        <v>0.164944984689929</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3037974683544304</v>
+        <v>0.09983512231232546</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06182795698924726</v>
+        <v>0.05436999982260993</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2850745173118185</v>
+        <v>0.6602799744141538</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3138896305174972</v>
+        <v>0.2757619916584588</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4010358521706843</v>
+        <v>0.06395803392738757</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.09723838381625388</v>
+        <v>-0.07493991858359184</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>0.09723838381625388</v>
+        <v>-0.07493991858359184</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4010358521706843</v>
+        <v>0.6602799744141538</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.1</v>
+        <v>1.29</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1558,604 +1558,10 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>4.948330554050862</v>
+        <v>5.81297581449131</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.948330554050862</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>EJYZzDn2</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45535.6875</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>valencia</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>villarreal</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>148</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.3605514316012725</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.2788971367974549</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.3605514316012725</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.05457392082308221</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.2680095599457526</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.3623258091734967</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.3696646308807507</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>0.009113199279478179</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.009113199279478179</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.3696646308807507</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>3.761619154292541</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.761619154292541</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>alaves</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>las palmas</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>148</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.4603234298608499</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.2775479503572771</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.2621286197818729</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.05970030288538197</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.3330507231381066</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.2967069643730315</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.370242312488862</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>0.1081136927069891</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.1081136927069891</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.370242312488862</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>4.669947259238117</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.669947259238117</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>osasuna</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>celta vigo</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>148</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.4100200400801604</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2857715430861724</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.3042084168336673</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.06039355688724557</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.499160581656248</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.3154350035908005</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.1854044147529515</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>0.0891405415760877</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.0891405415760877</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.499160581656248</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>5.842381991328407</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>5.842381991328407</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45536.58333333334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>sevilla</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>girona</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>148</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.4064516129032258</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2596774193548387</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.3338709677419355</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.06970324361628721</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.5018938258153822</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.3319952681193868</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.166110906065231</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>0.09544221291215643</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.09544221291215643</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.5018938258153822</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>5.932107177118169</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>5.932107177118169</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45536.59375</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>getafe</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>148</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.2606635071090047</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.3127962085308056</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.4265402843601895</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.06565656565656575</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.3310321684477963</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.3868944892678394</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.2820733422843643</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>0.07409828073703378</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.07409828073703378</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.3868944892678394</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>4.578090626125518</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4.578090626125518</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45536.6875</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>real madrid</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>betis</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>148</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="J17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K17" t="n">
-        <v>9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.725753243897075</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.1702221244776776</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.1040246316252474</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.06812309137890527</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.6587689867531538</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.2770756473041025</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.06415536594274387</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>-0.0669842571439212</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-0.0669842571439212</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.6587689867531538</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB17" t="n">
-        <v>5.876977470339962</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>5.876977470339962</v>
+        <v>5.81297581449131</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45535.5</v>
+        <v>45536.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="J2" t="n">
-        <v>6.25</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>4.33</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7547169811320755</v>
+        <v>0.5140093406910212</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1509433962264151</v>
+        <v>0.2687534552755911</v>
       </c>
       <c r="N2" t="n">
-        <v>0.09433962264150944</v>
+        <v>0.2172372040333877</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06000000000000005</v>
+        <v>0.06310925536306966</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6508405784276196</v>
+        <v>0.4653383307022609</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2865014175609947</v>
+        <v>0.3352370726217512</v>
       </c>
       <c r="S2" t="n">
-        <v>0.06265800401138578</v>
+        <v>0.1994245966759879</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.103876402704456</v>
+        <v>-0.04867100998876034</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.103876402704456</v>
+        <v>-0.04867100998876034</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6508405784276196</v>
+        <v>0.4653383307022609</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5.431867327720162</v>
+        <v>5.911281908164621</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.431867327720162</v>
+        <v>5.911281908164621</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.58333333334</v>
+        <v>45536.5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,53 +709,53 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3291472554182702</v>
+        <v>0.3800403225806452</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2916751063398825</v>
+        <v>0.2923387096774194</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3791776382418473</v>
+        <v>0.3276209677419355</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05491452991452994</v>
+        <v>0.0525198938992042</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2453936451940474</v>
+        <v>0.4257474503218577</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3459244475367921</v>
+        <v>0.360667622841149</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4086819072691604</v>
+        <v>0.2135849268369934</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.02950426902731307</v>
+        <v>0.04570712774121249</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02950426902731307</v>
+        <v>0.04570712774121249</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4086819072691604</v>
+        <v>0.4257474503218577</v>
       </c>
       <c r="Z3" t="n">
         <v>2.5</v>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>4.351599757582885</v>
+        <v>6.688551703678911</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.351599757582885</v>
+        <v>6.688551703678911</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.59375</v>
+        <v>45536.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3409090909090909</v>
+        <v>0.4018014489915802</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3181818181818181</v>
+        <v>0.2484824750342667</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3409090909090909</v>
+        <v>0.3497160759741531</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04761904761904767</v>
+        <v>0.05906018000082947</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3912910675884506</v>
+        <v>0.4149069107896232</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3213656271933518</v>
+        <v>0.3561979998417794</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2873433052181975</v>
+        <v>0.2288950893685975</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.05038197667935973</v>
+        <v>0.01310546179804301</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05038197667935973</v>
+        <v>0.01310546179804301</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3912910675884506</v>
+        <v>0.4149069107896232</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.386227627286668</v>
+        <v>6.072234775253176</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.386227627286668</v>
+        <v>6.072234775253176</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.59375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.2786228983186549</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3170731707317074</v>
+        <v>0.3266613290632506</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3170731707317074</v>
+        <v>0.3947157726180944</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0512820512820511</v>
+        <v>0.05561189993238691</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2799594354301689</v>
+        <v>0.3616578616745701</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3087305780185021</v>
+        <v>0.3606925673308698</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4113099865513289</v>
+        <v>0.2776495709945601</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.09423681581962157</v>
+        <v>0.0830349633559152</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09423681581962157</v>
+        <v>0.0830349633559152</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4113099865513289</v>
+        <v>0.3616578616745701</v>
       </c>
       <c r="Z5" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>5.020553960049551</v>
+        <v>6.308881259974823</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.020553960049551</v>
+        <v>6.308881259974823</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45535.6875</v>
+        <v>45536.6875</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.75</v>
+        <v>1.29</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3437815975733064</v>
+        <v>0.7352198929977456</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2780586450960567</v>
+        <v>0.164944984689929</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3781597573306371</v>
+        <v>0.09983512231232546</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05775401069518704</v>
+        <v>0.05436999982260993</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2925257078685912</v>
+        <v>0.6602799744141538</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3520892050875199</v>
+        <v>0.2757619916584588</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3553850870438891</v>
+        <v>0.06395803392738757</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.02277467028674796</v>
+        <v>-0.07493991858359184</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.02277467028674796</v>
+        <v>-0.07493991858359184</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3553850870438891</v>
+        <v>0.6602799744141538</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.5</v>
+        <v>1.29</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,505 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>3.303133433288927</v>
+        <v>8.304251161886615</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.303133433288927</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>alaves</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>las palmas</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>148</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.4931894569255263</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.2770564302140457</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.2297541128604281</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.06158029550729749</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.4653383307022608</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.3352370726217512</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.199424596675988</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="n">
-        <v>-0.02785112622326552</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.02785112622326552</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.4653383307022608</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>4.344658311786481</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>4.344658311786481</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45536.5</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>osasuna</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>celta vigo</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>148</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.3800403225806452</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.2923387096774194</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.3276209677419355</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.0525198938992042</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.4257474503218577</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.360667622841149</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.2135849268369934</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="n">
-        <v>0.04570712774121249</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.04570712774121249</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.4257474503218577</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>4.681986193518147</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.681986193518147</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45536.58333333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>sevilla</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>girona</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>148</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.4120836560805577</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.249419054996127</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.3384972889233152</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.05508336057535157</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.4149069107896232</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.3561979998417794</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.2288950893685975</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
-        <v>0.002823254709065526</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.002823254709065526</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.4149069107896232</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>4.14845238223409</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.14845238223409</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45536.59375</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>getafe</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>148</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.2719249862107005</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.3281853281853282</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.3998896856039714</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.05070993914807298</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.3616578616745702</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.3606925673308696</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.2776495709945602</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="n">
-        <v>0.08973287546386971</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.08973287546386971</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.3616578616745702</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>4.482733432872568</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>4.482733432872568</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45536.6875</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>real madrid</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>betis</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>148</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="K11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.7352198929977456</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.164944984689929</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.09983512231232546</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.05436999982260993</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.6602799744141538</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.2757619916584588</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.06395803392738757</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
-        <v>-0.07493991858359184</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>-0.07493991858359184</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.6602799744141538</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>5.81297581449131</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>5.81297581449131</v>
+        <v>8.304251161886615</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>YeqTho8m</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.5</v>
+        <v>45548.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5140093406910212</v>
+        <v>0.556783031374282</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2687534552755911</v>
+        <v>0.2629253203711887</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2172372040333877</v>
+        <v>0.1802916482545294</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06310925536306966</v>
+        <v>0.05648926237161533</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4653383307022609</v>
+        <v>0.5408237579470865</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3352370726217512</v>
+        <v>0.3615524487154009</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1994245966759879</v>
+        <v>0.09762379333751255</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.04867100998876034</v>
+        <v>-0.0159592734271955</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.04867100998876034</v>
+        <v>-0.0159592734271955</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4653383307022609</v>
+        <v>0.5408237579470865</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5.911281908164621</v>
+        <v>4.223870462025426</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.911281908164621</v>
+        <v>4.223870462025426</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>08zpk37C</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.5</v>
+        <v>45549.375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3800403225806452</v>
+        <v>0.3889109540074668</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2923387096774194</v>
+        <v>0.2802446580347923</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3276209677419355</v>
+        <v>0.3308443879577409</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0525198938992042</v>
+        <v>0.04950313458716815</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4257474503218577</v>
+        <v>0.3635427190258023</v>
       </c>
       <c r="R3" t="n">
-        <v>0.360667622841149</v>
+        <v>0.3213583571979587</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2135849268369934</v>
+        <v>0.315098923776239</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.04570712774121249</v>
+        <v>-0.02536823498166452</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04570712774121249</v>
+        <v>-0.02536823498166452</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4257474503218577</v>
+        <v>0.3635427190258023</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>6.688551703678911</v>
+        <v>2.72147431631105</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.688551703678911</v>
+        <v>2.72147431631105</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>n1v9mjW7</t>
+          <t>CjIFsr1e</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.58333333334</v>
+        <v>45549.46875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4018014489915802</v>
+        <v>0.3565379226699568</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2484824750342667</v>
+        <v>0.3024821731038665</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3497160759741531</v>
+        <v>0.3409799042261768</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05906018000082947</v>
+        <v>0.06644514567978321</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4149069107896232</v>
+        <v>0.3169196218129969</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3561979998417794</v>
+        <v>0.3507022187981974</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2288950893685975</v>
+        <v>0.3323781593888057</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.01310546179804301</v>
+        <v>0.04822004569433092</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01310546179804301</v>
+        <v>0.04822004569433092</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4149069107896232</v>
+        <v>0.3507022187981974</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>6.072234775253176</v>
+        <v>3.21034480200275</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.072234775253176</v>
+        <v>3.21034480200275</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h4pRxZHk</t>
+          <t>8EcB5Oig</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.59375</v>
+        <v>45549.5625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>getafe</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2786228983186549</v>
+        <v>0.4210526315789474</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3266613290632506</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3947157726180944</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05561189993238691</v>
+        <v>0.05555555555555536</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3616578616745701</v>
+        <v>0.5086470157465942</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3606925673308698</v>
+        <v>0.3446966411013452</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2776495709945601</v>
+        <v>0.1466563431520607</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.0830349633559152</v>
+        <v>0.08759438416764681</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0830349633559152</v>
+        <v>0.08759438416764681</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3616578616745701</v>
+        <v>0.5086470157465942</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>6.308881259974823</v>
+        <v>4.798279387560675</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.308881259974823</v>
+        <v>4.798279387560675</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YN50iYWr</t>
+          <t>jckS1tiI</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45536.6875</v>
+        <v>45549.66666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>real madrid</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>betis</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.29</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>5.75</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>9.5</v>
+        <v>1.8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7352198929977456</v>
+        <v>0.225296442687747</v>
       </c>
       <c r="M6" t="n">
-        <v>0.164944984689929</v>
+        <v>0.2490118577075099</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09983512231232546</v>
+        <v>0.5256916996047432</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05436999982260993</v>
+        <v>0.05680868838763575</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6602799744141538</v>
+        <v>0.1580652015175366</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2757619916584588</v>
+        <v>0.3814853224737154</v>
       </c>
       <c r="S6" t="n">
-        <v>0.06395803392738757</v>
+        <v>0.4604494760087481</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.07493991858359184</v>
+        <v>-0.06524222359599507</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.07493991858359184</v>
+        <v>-0.06524222359599507</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6602799744141538</v>
+        <v>0.4604494760087481</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,11 +1063,1778 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>8.304251161886615</v>
+        <v>3.180448075795062</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.304251161886615</v>
-      </c>
+        <v>3.180448075795062</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfxxiPx0</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45550.375</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>148</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5601138393532957</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2528081383027037</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1870780223440008</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.06907266547985103</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.5151835965605692</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3276896967481894</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1571267066912415</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>-0.0449302427927265</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.0449302427927265</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.5151835965605692</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.78438493979127</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.78438493979127</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>na927pNt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45550.46875</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>148</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2295302013422819</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2476510067114094</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5228187919463088</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.06261588931678785</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.3829614090198032</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3719523333067951</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.2450862576734018</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.1534312076775213</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.1534312076775213</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.3829614090198032</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.886653583968334</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.886653583968334</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>dzUhmsxP</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45550.5625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>148</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2547063253012047</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2855798192771084</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.4597138554216867</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06110545134935386</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.3335524440995426</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3616304132524664</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.3048171426479911</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.07605059397535802</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.07605059397535802</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.3616304132524664</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>3.522257521215618</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.522257521215618</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SdHeBgOE</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45550.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>148</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="K10" t="n">
+        <v>11</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7138221933809216</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.199870214146658</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.08630759247242052</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.05331510594668476</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.6565807566644134</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.2916274638089241</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.05179177952666242</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>-0.05724143671650817</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.05724143671650817</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.6565807566644134</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>4.823210037871069</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.823210037871069</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fVeJ32M5</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45551.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>148</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4600259692079391</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.3042107215729919</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.2357633092190688</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06038552321007096</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4151306465495382</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3224973564283026</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2623719970221592</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-0.04489532265840096</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.04489532265840096</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4151306465495382</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.979485361850438</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.979485361850438</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>AyPaTn1c</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45552.58333333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>148</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.3245679939894816</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.3268219383921863</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3486100676183321</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.06242017879948913</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.2965792592856386</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3445562982105717</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3588644425037897</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.01025437488545766</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.01025437488545766</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.3588644425037897</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.970500225738007</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.970500225738007</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45553.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>148</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3119999999999999</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06837606837606858</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4422252091985586</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3883910837396296</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1693837070618118</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.03777479080144136</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.03777479080144136</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4422252091985586</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>3.254832868305203</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.254832868305203</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45554.58333333334</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>148</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.208955223880597</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2686567164179104</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.5223880597014926</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06349206349206349</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3301669595915413</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3492848139985578</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.3205482264099009</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.08062809758064737</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.08062809758064737</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.3492848139985578</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.459743423340612</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.459743423340612</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45555.66666666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>148</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.2663509252691808</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3618180399645478</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.3718310347662715</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>0.6281689652337286</v>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.375</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>148</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2100740410609028</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.4183288400888595</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.3715971188502378</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="n">
+        <v>0.5816711599111405</v>
+      </c>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45556.46875</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>148</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.388732365765533</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3757975799571122</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2354700542773547</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="n">
+        <v>0.611267634234467</v>
+      </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>148</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2327138858602685</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3729693726841714</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.3943167414555601</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="n">
+        <v>0.6056832585444399</v>
+      </c>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45556.66666666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>148</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.7146328854622647</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2545268912782049</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.03084022325953037</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="n">
+        <v>0.2853671145377353</v>
+      </c>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45557.375</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>148</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.5263894953141612</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.2926881126705307</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.180922392015308</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="n">
+        <v>0.4736105046858388</v>
+      </c>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45557.46875</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>148</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.5297042887441316</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3271959817897341</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1430997294661343</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="n">
+        <v>0.4702957112558684</v>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45557.5625</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>148</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.2106175458071911</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.3945102348228192</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.3948722193699897</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="n">
+        <v>0.6051277806300103</v>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45557.66666666666</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>148</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.110058351419676</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.3603205081976079</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.529621140382716</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>0.470378859617284</v>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45558.66666666666</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>148</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.459131819493858</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.4105091994513775</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1303589810547647</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="n">
+        <v>0.540868180506142</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>148</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.6471130004378093</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.2439125900907494</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.1089744094714413</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="n">
+        <v>0.3528869995621907</v>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>148</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.5436494193973515</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.2854397854933181</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.1709107951093306</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="n">
+        <v>0.4563505806026485</v>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45559.66666666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>148</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.661252887441468</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.2739927372662763</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.06475437529225557</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="n">
+        <v>0.338747112558532</v>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>AyPaTn1c</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.375</v>
+        <v>45552.58333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.67</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5717651950932151</v>
+        <v>0.3253012048192772</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2546261002148451</v>
+        <v>0.3493975903614458</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1736087046919398</v>
+        <v>0.3253012048192772</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04728724369442938</v>
+        <v>0.06002554278416339</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5151835965605692</v>
+        <v>0.3038775323776441</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3276896967481894</v>
+        <v>0.3260887468638929</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1571267066912415</v>
+        <v>0.3700337207584629</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.05658159853264588</v>
+        <v>0.04473251593918576</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.05658159853264588</v>
+        <v>0.04473251593918576</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5151835965605692</v>
+        <v>0.3700337207584629</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.67</v>
+        <v>2.9</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>3.690620132295459</v>
+        <v>2.903363656883541</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.690620132295459</v>
+        <v>2.903363656883541</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>8b5vHIeT</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.46875</v>
+        <v>45553.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.33</v>
+        <v>1.91</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2194529351830081</v>
+        <v>0.4953764861294584</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2375578023356062</v>
+        <v>0.3153896961690885</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5429892624813857</v>
+        <v>0.1892338177014531</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05237545364566154</v>
+        <v>0.05689354275741709</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3660422094723063</v>
+        <v>0.5130448986285744</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3873991836204663</v>
+        <v>0.3439539366377966</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2465586069072275</v>
+        <v>0.143001164733629</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.14984138128486</v>
+        <v>0.01766841249911599</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.14984138128486</v>
+        <v>0.01766841249911599</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3873991836204663</v>
+        <v>0.5130448986285744</v>
       </c>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>1.91</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,24 +766,24 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.922366773954915</v>
+        <v>3.714993177893833</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.922366773954915</v>
+        <v>3.714993177893833</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>xjut9IFr</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45550.5625</v>
+        <v>45554.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2524533384644987</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2918991725995767</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4556474889359247</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.07057514831905065</v>
+      </c>
+      <c r="P4" t="n">
         <v>2</v>
       </c>
-      <c r="L4" t="n">
-        <v>0.2489019033674963</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.2781844802342606</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.472913616398243</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.05727554179566563</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q4" t="n">
-        <v>0.3451201674674726</v>
+        <v>0.3081264710248656</v>
       </c>
       <c r="R4" t="n">
-        <v>0.359610867684535</v>
+        <v>0.3410526958975341</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2952689648479924</v>
+        <v>0.3508208330776003</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.08142638745027442</v>
+        <v>-0.1048266558583243</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>0.08142638745027442</v>
+        <v>-0.1048266558583243</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.359610867684535</v>
+        <v>0.3508208330776003</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>3.549267076664043</v>
+        <v>1.721959240534932</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.549267076664043</v>
+        <v>1.721959240534932</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>IRBb0lXA</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45550.66666666666</v>
+        <v>45555.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>11</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.705983027882764</v>
+        <v>0.4733044733044733</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2086572060186836</v>
+        <v>0.2958152958152958</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08535976609855238</v>
+        <v>0.2308802308802309</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06501101237943341</v>
+        <v>0.05640243902439024</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6610999215929115</v>
+        <v>0.2955692398207646</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2857149172780823</v>
+        <v>0.3582281953308562</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05318516112900619</v>
+        <v>0.3462025648483793</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.04488310628985248</v>
+        <v>0.06241289951556039</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.04488310628985248</v>
+        <v>0.06241289951556039</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6610999215929115</v>
+        <v>0.3582281953308562</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.33</v>
+        <v>3.2</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4.95903243814038</v>
+        <v>2.944487663924916</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.95903243814038</v>
+        <v>2.944487663924916</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>dYbQEmn4</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45551.66666666666</v>
+        <v>45556.375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.05</v>
+        <v>3.75</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4600259692079391</v>
+        <v>0.2503639010189229</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3042107215729919</v>
+        <v>0.3129548762736535</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2357633092190688</v>
+        <v>0.4366812227074235</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06038552321007096</v>
+        <v>0.06511627906976747</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4231976610958293</v>
+        <v>0.2302723557428013</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3026865854237436</v>
+        <v>0.3941719934379102</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2741157534804272</v>
+        <v>0.3755556508192885</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.03682830811210985</v>
+        <v>0.08121711716425667</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.03682830811210985</v>
+        <v>0.08121711716425667</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4231976610958293</v>
+        <v>0.3941719934379102</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>3.109324684051775</v>
+        <v>3.327723774215168</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.109324684051775</v>
+        <v>3.327723774215168</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>4b2YCRGG</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45552.58333333334</v>
+        <v>45556.46875</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="J7" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3404830265157913</v>
+        <v>0.4903728275762602</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3251140010133423</v>
+        <v>0.2754741472560756</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3344029724708664</v>
+        <v>0.2341530251676643</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06800144300144306</v>
+        <v>0.06767785648290725</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3381802367837627</v>
+        <v>0.3552488147706522</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3589371178961235</v>
+        <v>0.4106293533892554</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3028826453201138</v>
+        <v>0.2341218318400923</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.03382311688278122</v>
+        <v>0.1351552061331798</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03382311688278122</v>
+        <v>0.1351552061331798</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3589371178961235</v>
+        <v>0.4106293533892554</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,11 +1162,2246 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>3.160755591718678</v>
+        <v>3.574405473724788</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.160755591718678</v>
-      </c>
+        <v>3.574405473724788</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>148</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.3419288292934502</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2893243940175348</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.368746776689015</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.06348553407376945</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.2629645108075909</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2948168206995281</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.4422186684928809</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.07347189180386593</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.07347189180386593</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.4422186684928809</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.609833922077227</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.609833922077227</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45556.66666666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>148</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>17</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.8007536504945832</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.144135657089025</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0551106924163919</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06737053795877324</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.7368379582987926</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.2366905793687715</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.02647146233243584</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>-0.06391569219579063</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.06391569219579063</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.7368379582987926</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.710455862721014</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.710455862721014</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45557.375</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>148</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.4533946635253641</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.3319496643667844</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2146556721078514</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.07589461740872783</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5233880880306984</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3015549935932244</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.1750569183760773</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.06999342450533425</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.06999342450533425</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.5233880880306984</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>4.153670587752229</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.153670587752229</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45557.46875</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>148</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.562008242787561</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2502810041213938</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1877107530910453</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06546906187624746</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4737486347178122</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.366530167715227</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1597211975669608</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-0.08825960806974881</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.08825960806974881</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4737486347178122</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.698423186536444</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.698423186536444</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45557.5625</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>148</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2324080051646223</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2382182052937379</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.5293737895416398</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.04945799457994582</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.2507046793823956</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3709651643172087</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3783301563003957</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.1510436332412441</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.1510436332412441</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.3783301563003957</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.591005661414061</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.591005661414061</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45557.66666666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>148</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.1969169567379413</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2834410740924913</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.5196419691695674</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06911217437533224</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1285895232304305</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3173101967236326</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.5541002800459369</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.03445831087636952</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.03445831087636952</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.5541002800459369</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>4.119910136456145</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.119910136456145</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45558.66666666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>148</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5027055332518764</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2906266364112411</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.2066678303368825</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.07526276276276267</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.556506492338731</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3264410547157682</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1170524529455008</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.05380095908685456</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.05380095908685456</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.556506492338731</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>4.272152159979099</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.272152159979099</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>148</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5430668211664735</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2568559289300889</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2000772499034376</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.05222515748831524</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.6213740375428063</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.2485348279441947</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.130091134512999</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.07830721637633276</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.07830721637633276</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.6213740375428063</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.897768777433973</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.897768777433973</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45559.58333333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>148</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4512126339537507</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2961082910321489</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.2526790750141004</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.05535714285714288</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.5235896220069213</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3219494520289805</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.1544609259640982</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.07237698805317061</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.07237698805317061</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.5235896220069213</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>4.171766270420643</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.171766270420643</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45559.66666666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>148</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K17" t="n">
+        <v>12</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.7710892921400297</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1505166298257338</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.07839407803423636</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06300546448087441</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.671235036845339</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.2495628059475588</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.0792021572071023</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-0.09985425529469072</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.09985425529469072</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.671235036845339</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.999665470854538</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.999665470854538</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ddsD5q9j</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45560.58333333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>148</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.5539358600583091</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2478134110787172</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.1982507288629737</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.0619195046439629</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.4531193573796735</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3397053496194653</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2071752930008612</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-0.1008165026786356</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.1008165026786356</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.4531193573796735</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.466119982907266</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.466119982907266</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>QDjsB5oT</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45560.66666666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>148</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.6849315068493151</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.189041095890411</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.126027397260274</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.05797101449275366</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.6080551208158098</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3286825897071574</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.06326228947703277</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>-0.07687638603350533</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.07687638603350533</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.6080551208158098</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.718251143476131</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.718251143476131</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>148</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.2754847379535419</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2676137454405836</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.4569015166058745</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.06763681082188966</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.2156791523858561</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.3774645115221197</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.4068563360920243</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>-0.05004518051385026</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.05004518051385026</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.4068563360920243</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.497678089047218</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.497678089047218</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>148</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2771706735545401</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.3039936419630439</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.418835684482416</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.06114273666455827</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.2466565802176182</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3572940034513991</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.3960494163309827</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>-0.02278626815143336</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.02278626815143336</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.3960494163309827</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.612842037256845</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.612842037256845</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45561.66666666666</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>148</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.2697368421052632</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.2697368421052632</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.4605263157894737</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.05923344947735187</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.137897114616033</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.3532096323943336</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.5088932529896336</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.04836693720015989</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.04836693720015989</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.5088932529896336</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>3.900821331328555</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.900821331328555</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45562.66666666666</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>148</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.1931088486274787</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.4630939717141869</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.3437971796583345</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>0.5369060282858131</v>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45563.375</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>148</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.3400277736580923</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.2893197158072343</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.3706525105346735</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="n">
+        <v>0.6293474894653266</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45563.46875</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>148</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.6226109998452241</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.2531883238678656</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.1242006762869104</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="n">
+        <v>0.3773890001547759</v>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>148</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.4539732864747946</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.3203498219442718</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.2256768915809337</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="n">
+        <v>0.5460267135252054</v>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45563.66666666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>148</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.09247865477222025</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.3698392455581102</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.5376820996696695</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="n">
+        <v>0.4623179003303305</v>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45564.375</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>148</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.4125993691371009</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.3320119233196372</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.2553887075432619</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>0.5874006308628991</v>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45564.46875</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>148</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.3331069212213456</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.4249323266922443</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.2419607520864101</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="n">
+        <v>0.5750676733077558</v>
+      </c>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45564.5625</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>148</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.5718040506452212</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.2768546304995587</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.1513413188552201</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="n">
+        <v>0.4281959493547788</v>
+      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45564.66666666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>148</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.3377536886118352</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.3690975235860555</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.2931487878021093</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="n">
+        <v>0.6309024764139446</v>
+      </c>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45565.66666666666</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>148</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.4449453100929817</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.3580719443051698</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.1969827456018485</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="n">
+        <v>0.5550546899070183</v>
+      </c>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>445r4WXo</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.375</v>
+        <v>45558.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,86 +610,86 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5717651950932151</v>
+        <v>0.5411140583554376</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2546261002148451</v>
+        <v>0.2785145888594164</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1736087046919398</v>
+        <v>0.1803713527851459</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04728724369442938</v>
+        <v>0.05602240896358546</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5151835965605692</v>
+        <v>0.5408109176634674</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3276896967481894</v>
+        <v>0.3944881060949174</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1571267066912415</v>
+        <v>0.06470097624161518</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.05658159853264588</v>
+        <v>-0.0003031406919701274</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.05658159853264588</v>
+        <v>-0.0003031406919701274</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5151835965605692</v>
+        <v>0.5408109176634674</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>3.690620132295459</v>
+        <v>4.376545042026021</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.690620132295459</v>
+        <v>4.376545042026021</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>rkN7RQV9</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.46875</v>
+        <v>45559.58333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,86 +709,86 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.33</v>
+        <v>1.7</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2194529351830081</v>
+        <v>0.5557224391709222</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2375578023356062</v>
+        <v>0.2553319315109642</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5429892624813857</v>
+        <v>0.1889456293181136</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05237545364566154</v>
+        <v>0.05850556438791732</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3660422094723063</v>
+        <v>0.5081509698904012</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3873991836204663</v>
+        <v>0.417731030004452</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2465586069072275</v>
+        <v>0.07411800010514685</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.14984138128486</v>
+        <v>-0.04757146928052103</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.14984138128486</v>
+        <v>-0.04757146928052103</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3873991836204663</v>
+        <v>0.5081509698904012</v>
       </c>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.922366773954915</v>
+        <v>3.729357866314824</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.922366773954915</v>
+        <v>3.729357866314824</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>bwZsTw7E</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45550.5625</v>
+        <v>45559.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,86 +808,86 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2489019033674963</v>
+        <v>0.4512126339537507</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2781844802342606</v>
+        <v>0.2961082910321489</v>
       </c>
       <c r="N4" t="n">
-        <v>0.472913616398243</v>
+        <v>0.2526790750141004</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05727554179566563</v>
+        <v>0.05535714285714288</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3451201674674726</v>
+        <v>0.3344448302385079</v>
       </c>
       <c r="R4" t="n">
-        <v>0.359610867684535</v>
+        <v>0.3424000685835993</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2952689648479924</v>
+        <v>0.3231551011778929</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.08142638745027442</v>
+        <v>0.04629177755145036</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.08142638745027442</v>
+        <v>0.04629177755145036</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.359610867684535</v>
+        <v>0.3424000685835993</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>3.549267076664043</v>
+        <v>2.772447291961801</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.549267076664043</v>
+        <v>2.772447291961801</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>f5SjRHyR</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45550.66666666666</v>
+        <v>45559.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,86 +907,86 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="K5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
-        <v>0.705983027882764</v>
+        <v>0.783132530120482</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2086572060186836</v>
+        <v>0.1445783132530121</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08535976609855238</v>
+        <v>0.07228915662650603</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06501101237943341</v>
+        <v>0.0641025641025641</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6610999215929115</v>
+        <v>0.6847641344606475</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2857149172780823</v>
+        <v>0.2397935592263166</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05318516112900619</v>
+        <v>0.07544230631303583</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.04488310628985248</v>
+        <v>-0.09836839565983446</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.04488310628985248</v>
+        <v>-0.09836839565983446</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6610999215929115</v>
+        <v>0.6847641344606475</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4.95903243814038</v>
+        <v>4.74810441709744</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.95903243814038</v>
+        <v>4.74810441709744</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>ddsD5q9j</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45551.66666666666</v>
+        <v>45560.58333333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>rayo vallecano</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>osasuna</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,86 +1006,86 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4600259692079391</v>
+        <v>0.5399533013361008</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3042107215729919</v>
+        <v>0.2524646517057984</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2357633092190688</v>
+        <v>0.2075820469581009</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06038552321007096</v>
+        <v>0.07052717457341728</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4231976610958293</v>
+        <v>0.4551515200405018</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3026865854237436</v>
+        <v>0.45805835461747</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2741157534804272</v>
+        <v>0.08679012534202812</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.03682830811210985</v>
+        <v>0.2055937029116716</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.03682830811210985</v>
+        <v>0.2055937029116716</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4231976610958293</v>
+        <v>0.45805835461747</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.05</v>
+        <v>3.7</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>3.109324684051775</v>
+        <v>3.708943897333415</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.109324684051775</v>
+        <v>3.708943897333415</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>QDjsB5oT</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45552.58333333334</v>
+        <v>45560.66666666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,68 +1105,2105 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.75</v>
+        <v>1.25</v>
       </c>
       <c r="J7" t="n">
-        <v>2.88</v>
+        <v>6.25</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3404830265157913</v>
+        <v>0.7547169811320755</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3251140010133423</v>
+        <v>0.1509433962264151</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3344029724708664</v>
+        <v>0.09433962264150944</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06800144300144306</v>
+        <v>0.06000000000000005</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3381802367837627</v>
+        <v>0.6285554208465365</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3589371178961235</v>
+        <v>0.3277309695226326</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3028826453201138</v>
+        <v>0.0437136096308308</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.03382311688278122</v>
+        <v>-0.126161560285539</v>
       </c>
       <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.126161560285539</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.6285554208465365</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.067932883227492</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.067932883227492</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>148</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2906808305166586</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.269917914051183</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.4394012554321584</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0585228724763609</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.3604871467035078</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3100354078201349</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.3294774454763573</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.06980631618684924</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.06980631618684924</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.3604871467035078</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.918900156181361</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.918900156181361</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>148</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.3037974683544304</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.3037974683544304</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3924050632911393</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06182795698924726</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.1229073394296955</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3658289508101885</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.511263709760116</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.1188586464689768</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.1188586464689768</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.511263709760116</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.139752931318989</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.139752931318989</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45561.66666666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>148</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2547632008709852</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2618399564507349</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.4833968426782798</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.06086856086856107</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1661497387236976</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.4027355240033786</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.4311147372729238</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>-0.05228210540535594</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.05228210540535594</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.4311147372729238</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.067445367849172</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.067445367849172</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45562.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>148</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3366583541147132</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.314214463840399</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3491271820448877</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06084656084656093</v>
+      </c>
+      <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="X7" t="n">
-        <v>0.03382311688278122</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.3589371178961235</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>3.160755591718678</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.160755591718678</v>
-      </c>
+      <c r="Q11" t="n">
+        <v>0.3503245575112786</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.4602492737597988</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1894261687289225</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.1460348099193999</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1460348099193999</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4602492737597988</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.726683986779611</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.726683986779611</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45563.375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>148</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.3997567403202919</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.323940806811271</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2763024528684371</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.06447714815933714</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.2580355187292688</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.2854832990992498</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.4564811821714815</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1801787293030445</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1801787293030445</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4564811821714815</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.696173375718376</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.696173375718376</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.46875</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>148</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.4904913518630066</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3122794940194475</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1972291541175458</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06741985854689081</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.6185229515125987</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3144900159986573</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.06698703248874409</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.1280315996495921</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.1280315996495921</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.6185229515125987</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>5.008241642681329</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.008241642681329</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>148</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5439668439257036</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2767831294092551</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.1792500266650414</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06262851961593885</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4916837424854436</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.4236096024691185</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.08470665504543799</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.05228310144026005</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.05228310144026005</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.4916837424854436</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.557870541297988</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.557870541297988</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.66666666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>148</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.1361218733007069</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2200584556824361</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.643819671016857</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.0494797007499086</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.1367878370483812</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.2824706381613762</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.5807415247902425</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.06307814622661445</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.06307814622661445</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.5807415247902425</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.1915716839178</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.1915716839178</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45564.375</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>148</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4664634146341464</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2591463414634146</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.274390243902439</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.07189542483660127</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.3065355097973315</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3817064870898392</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.3117580031128292</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1225601456264246</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.1225601456264246</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.3817064870898392</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.09071525842319</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.09071525842319</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45564.46875</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>148</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.5557224391709222</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2553319315109642</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1889456293181136</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.05850556438791732</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.4763735152800625</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3957119312550064</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.1279145534649311</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-0.07934892389085973</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.07934892389085973</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.4763735152800625</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.214747467173726</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.214747467173726</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45564.5625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>148</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.5960720381078533</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2599536388414805</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.1439743230506661</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06856660678316739</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.6082259867265751</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3281564338314107</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.06361757944201411</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.01215394861872188</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.01215394861872188</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.6082259867265751</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>4.924866098235528</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.924866098235528</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45564.66666666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>148</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.3067869752844252</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2797175362887406</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.413495488426834</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.05148090091576618</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2611593032482083</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.4156629691983781</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.3231777275534136</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.1359454329096375</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.1359454329096375</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4156629691983781</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>3.365664259618797</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.365664259618797</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45565.66666666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>148</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.6106870229007634</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.233587786259542</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.1557251908396947</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.0702614379084967</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.5468963056995511</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.3267484368818821</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.1263552574185668</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>-0.06379071720121232</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.06379071720121232</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.5468963056995511</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>3.911753832598348</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.911753832598348</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QmPfsURO</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45569.66666666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>148</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.4256642360700815</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3982294511643811</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1761063127655375</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="n">
+        <v>0.5743357639299185</v>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>0AJjqex0</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45570.375</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>148</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.3647594496461781</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.4586169653408992</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.1766235850129228</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="n">
+        <v>0.5413830346591008</v>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>40FWnYcm</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45570.46875</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>148</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.4545384437128644</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.3444309532001786</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.2010306030869569</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>0.5454615562871357</v>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>KApUeTtI</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>148</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.2683675776041386</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.3637864018196887</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.3678460205761727</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="n">
+        <v>0.6321539794238273</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>EB22wLQj</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>148</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.2969499861157854</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.4909456141240842</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.2121043997601303</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="n">
+        <v>0.5090543858759158</v>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45570.66666666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>148</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.744151399906815</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.2003635295287127</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.05548507056447213</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="n">
+        <v>0.255848600093185</v>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45571.375</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>148</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.4741021754920535</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.3518987645354678</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.1739990599724787</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="n">
+        <v>0.5258978245079465</v>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45571.46875</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>148</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.2509885528074592</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.3180380645265662</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.4309733826659747</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>0.5690266173340253</v>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45571.5625</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>148</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.258492267271013</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.3871427701810209</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.3543649625479661</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="n">
+        <v>0.6128572298189791</v>
+      </c>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>CvbDaBsg</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45571.66666666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>148</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.1457162461664724</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.4079395198484711</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.4463442339850565</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="n">
+        <v>0.5536557660149435</v>
+      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>06X4YYrf</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45562.66666666666</v>
+        <v>45564.375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3149440475698889</v>
+        <v>0.4365343242714649</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3258041871412644</v>
+        <v>0.2607079992176805</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3592517652888467</v>
+        <v>0.3027576765108547</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05838905642235925</v>
+        <v>0.06547470200883554</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.344755057870832</v>
+        <v>0.3075734332755365</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4548837251050513</v>
+        <v>0.3613253426882873</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2003612170241167</v>
+        <v>0.3311012240361761</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1290795379637869</v>
+        <v>0.1006173434706068</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1290795379637869</v>
+        <v>0.1006173434706068</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4548837251050513</v>
+        <v>0.3613253426882873</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>3.683238607521131</v>
+        <v>1.024259339190042</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.683238607521131</v>
+        <v>1.024259339190042</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hMoEUjrJ</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45563.375</v>
+        <v>45564.46875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.55</v>
+        <v>1.7</v>
       </c>
       <c r="J3" t="n">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3692765851842661</v>
+        <v>0.5607678983833718</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3269636431319022</v>
+        <v>0.2576501154734411</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3037597716838317</v>
+        <v>0.181581986143187</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06195973012861056</v>
+        <v>0.04898175486410783</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2477382617935671</v>
+        <v>0.4723314448101529</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2652125607268025</v>
+        <v>0.3958814778167427</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4870491774796303</v>
+        <v>0.1317870773731044</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1832894057957986</v>
+        <v>-0.08843645357321894</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1832894057957986</v>
+        <v>-0.08843645357321894</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4870491774796303</v>
+        <v>0.4723314448101529</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.943685463444743</v>
+        <v>1.088238170943705</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.943685463444743</v>
+        <v>1.088238170943705</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KSw0hfzQ</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.46875</v>
+        <v>45564.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4966887417218543</v>
+        <v>0.5837224816544363</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3145695364238411</v>
+        <v>0.266844563042028</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1887417218543047</v>
+        <v>0.1494329553035357</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05964912280701751</v>
+        <v>0.07071428571428573</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6092155805078786</v>
+        <v>0.568550612357935</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3332298660930402</v>
+        <v>0.3771098722274021</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05755455339908105</v>
+        <v>0.05433951541466282</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1125268387860243</v>
+        <v>-0.01517186929650127</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1125268387860243</v>
+        <v>-0.01517186929650127</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6092155805078786</v>
+        <v>0.568550612357935</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.93287893716534</v>
+        <v>1.568678635915382</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.93287893716534</v>
+        <v>1.568678635915382</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YemQuHjK</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45563.5625</v>
+        <v>45564.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.85</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>4.75</v>
+        <v>2.38</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5105415460934271</v>
+        <v>0.3154977102916365</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2906159570070277</v>
+        <v>0.2868161002651242</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1988424968995453</v>
+        <v>0.3976861894432394</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05875916402232173</v>
+        <v>0.05653170359052706</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4944318212772806</v>
+        <v>0.2572251179354655</v>
       </c>
       <c r="R5" t="n">
-        <v>0.405101695376402</v>
+        <v>0.4003157084634431</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1004664833463173</v>
+        <v>0.3424591736010914</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.01610972481614642</v>
+        <v>0.1134996081983189</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.01610972481614642</v>
+        <v>0.1134996081983189</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4944318212772806</v>
+        <v>0.4003157084634431</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>3.873021423462073</v>
+        <v>1.134786450259835</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.873021423462073</v>
+        <v>1.134786450259835</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4vvdzeEs</t>
+          <t>YJVCWCD6</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45563.66666666666</v>
+        <v>45565.66666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,53 +1006,53 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>1.45</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="K6" t="n">
-        <v>1.45</v>
+        <v>6.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1354436948624805</v>
+        <v>0.6418691631412705</v>
       </c>
       <c r="M6" t="n">
-        <v>0.210690192008303</v>
+        <v>0.2149446389272153</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6538661131292164</v>
+        <v>0.1431861979315142</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05473453749315826</v>
+        <v>0.07444820847703704</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1181839643591437</v>
+        <v>0.5589428789668156</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3240164093069302</v>
+        <v>0.33385099860105</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5577996263339261</v>
+        <v>0.1072061224321343</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.09606648679529028</v>
+        <v>-0.08292628417445491</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.09606648679529028</v>
+        <v>-0.08292628417445491</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5577996263339261</v>
+        <v>0.5589428789668156</v>
       </c>
       <c r="Z6" t="n">
         <v>1.45</v>
@@ -1063,406 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>3.738698995062727</v>
+        <v>1.349377929591105</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.738698995062727</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45564.375</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>celta vigo</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>girona</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>148</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.4485336400230017</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.261644623346751</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.2898217366302473</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.06166056166056166</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.3075734332755365</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.3613253426882873</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.3311012240361761</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="n">
-        <v>0.09968071934153622</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.09968071934153622</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.3613253426882873</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.925687112147077</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.925687112147077</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45564.46875</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ath bilbao</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>sevilla</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>148</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.5557224391709222</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.2553319315109642</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.1889456293181136</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.05850556438791732</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.4723314448101529</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.3958814778167427</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.1317870773731044</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="n">
-        <v>-0.08339099436076935</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-0.08339099436076935</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.4723314448101529</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>3.149289376732464</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.149289376732464</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45564.5625</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>betis</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>espanyol</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>148</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.5642542752002309</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.2738292806118767</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.1619164441878923</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.07409129659769054</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.568550612357935</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.3771098722274021</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.05433951541466282</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
-        <v>0.004296337157704166</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.004296337157704166</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.568550612357935</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>4.603610659587593</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.603610659587593</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45564.66666666666</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>atl  madrid</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>real madrid</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>148</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.3368721927317272</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.2858309514087382</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.3772968558595345</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.06017316017316032</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.2572251179354655</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.4003157084634431</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.3424591736010914</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="n">
-        <v>0.1144847570547048</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.1144847570547048</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.4003157084634431</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>3.241395968319627</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.241395968319627</v>
+        <v>1.349377929591105</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,12 +510,12 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>prob_class_0</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>prob_class_1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>prob_class_0</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
+          <t>QmPfsURO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.375</v>
+        <v>45569.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,58 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4365343242714649</v>
+        <v>0.3286599282686665</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2607079992176805</v>
+        <v>0.3309422888816433</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3027576765108547</v>
+        <v>0.3403977828496902</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06547470200883554</v>
+        <v>0.04919266557197588</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3075734332755365</v>
+        <v>0.3541646301746368</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3613253426882873</v>
+        <v>0.392652839422226</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3311012240361761</v>
+        <v>0.2531825304031372</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
       <c r="V2" t="n">
-        <v>0.1006173434706068</v>
+        <v>0.06399291115355948</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1006173434706068</v>
+        <v>0.06399291115355948</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3613253426882873</v>
+        <v>0.392652839422226</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +669,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>1.024259339190042</v>
+        <v>2.961643709260271</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.024259339190042</v>
+        <v>2.961643709260271</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>0AJjqex0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.46875</v>
+        <v>45570.375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +711,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>5.25</v>
+        <v>2.55</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5607678983833718</v>
+        <v>0.3077851538925769</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2576501154734411</v>
+        <v>0.3180446590223295</v>
       </c>
       <c r="N3" t="n">
-        <v>0.181581986143187</v>
+        <v>0.3741701870850936</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04898175486410783</v>
+        <v>0.04807084123972172</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4723314448101529</v>
+        <v>0.4293501377105713</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3958814778167427</v>
+        <v>0.1342028975486755</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1317870773731044</v>
+        <v>0.4364469349384308</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.08843645357321894</v>
+        <v>0.0622767478533372</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.08843645357321894</v>
+        <v>0.0622767478533372</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4723314448101529</v>
+        <v>0.4364469349384308</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.7</v>
+        <v>2.55</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +768,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>1.088238170943705</v>
+        <v>3.291967329685794</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.088238170943705</v>
+        <v>3.291967329685794</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
+          <t>40FWnYcm</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45564.5625</v>
+        <v>45570.46875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +810,58 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="K4" t="n">
-        <v>6.25</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5837224816544363</v>
+        <v>0.4305291206699657</v>
       </c>
       <c r="M4" t="n">
-        <v>0.266844563042028</v>
+        <v>0.3266082984392844</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1494329553035357</v>
+        <v>0.2428625808907499</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07071428571428573</v>
+        <v>0.05578329716260755</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.568550612357935</v>
+        <v>0.3340967893600464</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3771098722274021</v>
+        <v>0.3853948414325714</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05433951541466282</v>
+        <v>0.2805083990097046</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
       <c r="V4" t="n">
-        <v>-0.01517186929650127</v>
+        <v>-0.04513427923739433</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.01517186929650127</v>
+        <v>-0.04513427923739433</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.568550612357935</v>
+        <v>0.3853948414325714</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +869,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>1.568678635915382</v>
+        <v>2.566466996692415</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.568678635915382</v>
+        <v>2.566466996692415</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
+          <t>KApUeTtI</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45564.66666666666</v>
+        <v>45570.5625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +911,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3154977102916365</v>
+        <v>0.306420233463035</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2868161002651242</v>
+        <v>0.2714007782101167</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3976861894432394</v>
+        <v>0.4221789883268482</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05653170359052706</v>
+        <v>0.05273937532002049</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2572251179354655</v>
+        <v>0.3563001751899719</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4003157084634431</v>
+        <v>0.3340717256069183</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3424591736010914</v>
+        <v>0.3096279799938202</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1134996081983189</v>
+        <v>0.08489939697985521</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1134996081983189</v>
+        <v>0.08489939697985521</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4003157084634431</v>
+        <v>0.3563001751899719</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +968,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>1.134786450259835</v>
+        <v>2.687448215101285</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.134786450259835</v>
+        <v>2.687448215101285</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YJVCWCD6</t>
+          <t>EB22wLQj</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45565.66666666666</v>
+        <v>45570.5625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1010,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.45</v>
+        <v>3.1</v>
       </c>
       <c r="J6" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6418691631412705</v>
+        <v>0.3054989816700611</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2149446389272153</v>
+        <v>0.3156822810590631</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1431861979315142</v>
+        <v>0.3788187372708758</v>
       </c>
       <c r="O6" t="n">
-        <v>0.07444820847703704</v>
+        <v>0.05591397849462365</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5589428789668156</v>
+        <v>0.3665012717247009</v>
       </c>
       <c r="R6" t="n">
-        <v>0.33385099860105</v>
+        <v>0.2284272313117981</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1072061224321343</v>
+        <v>0.4050714671611786</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.08292628417445491</v>
+        <v>0.02625272989030281</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.08292628417445491</v>
+        <v>0.02625272989030281</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5589428789668156</v>
+        <v>0.4050714671611786</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.45</v>
+        <v>2.5</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,10 +1067,812 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>1.349377929591105</v>
+        <v>3.055313096128411</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.349377929591105</v>
+        <v>3.055313096128411</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45570.66666666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>148</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.7393104408029781</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1502278815711652</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1104616776258567</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0650486336266789</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1944294422864914</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.655281126499176</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1502895206212997</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>-0.08402931430380212</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.08402931430380212</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.655281126499176</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.308753601480241</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.308753601480241</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.375</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>148</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.4048278591214879</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2882865057380293</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.3068856351404828</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.05114286308521043</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.3445629477500916</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3163427412509918</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.339094340801239</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.05627644201206228</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.05627644201206228</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.3445629477500916</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.598918393535169</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.598918393535169</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.46875</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>148</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1814679252552495</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2117125794644577</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.6068194952802928</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.04964108785764831</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.3858337104320526</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.1373360604047775</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.4768302440643311</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.1299892512159617</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.1299892512159617</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.4768302440643311</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.61610089486294</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.61610089486294</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.5625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>148</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3872529245663574</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2964905203711174</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.3162565550625252</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.05399659863945572</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.3961144983768463</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1816236972808838</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.4222618043422699</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.1060052492797447</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.1060052492797447</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.4222618043422699</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.18497382657762</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.18497382657762</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CvbDaBsg</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45571.66666666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>148</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.2885143081144649</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.297530380243042</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4139553116424932</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05031291172595509</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3452627956867218</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2492374777793884</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.4054996371269226</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-0.00845567451557061</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.00845567451557061</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4054996371269226</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.994764423193725</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.994764423193725</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45583.66666666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>148</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5342465753424658</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2328767123287671</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2328767123287671</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.10105580693816</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.3700679242610931</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.4630305171012878</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.166901558637619</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-0.07121605824117794</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.07121605824117794</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4630305171012878</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.955320096469362</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.955320096469362</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45584.375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>148</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5955320570548761</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2222351334863318</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1822328094587921</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.09749721026622038</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.3308404684066772</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.4720935821533203</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1970659643411636</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0.1234384749015558</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.1234384749015558</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4720935821533203</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.629784128425187</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.629784128425187</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45584.46875</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>148</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3389830508474576</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2542372881355933</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.4067796610169491</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.09259259259259256</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.387969970703125</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.2082197368144989</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.4038102030754089</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-0.002969457941540188</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.002969457941540188</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.4038102030754089</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.023402232332676</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.023402232332676</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QmPfsURO</t>
+          <t>4Ef51XCt</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45569.66666666666</v>
+        <v>45571.375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,58 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J2" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3286599282686665</v>
+        <v>0.3956834532374101</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3309422888816433</v>
+        <v>0.2877697841726619</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3403977828496902</v>
+        <v>0.316546762589928</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04919266557197588</v>
+        <v>0.05303030303030298</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3541646301746368</v>
+        <v>0.3445629477500916</v>
       </c>
       <c r="R2" t="n">
-        <v>0.392652839422226</v>
+        <v>0.3163427412509918</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2531825304031372</v>
+        <v>0.3390943109989166</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.06399291115355948</v>
+        <v>0.05679316357742964</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.06399291115355948</v>
+        <v>0.05679316357742964</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.392652839422226</v>
+        <v>0.3445629477500916</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -669,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>2.961643709260271</v>
+        <v>1.720877682351181</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.961643709260271</v>
+        <v>1.720877682351181</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0AJjqex0</t>
+          <t>hzRnqjcC</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45570.375</v>
+        <v>45571.46875</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -711,56 +709,58 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="K3" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3077851538925769</v>
+        <v>0.1820710973724884</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3180446590223295</v>
+        <v>0.2012364760432767</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3741701870850936</v>
+        <v>0.616692426584235</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04807084123972172</v>
+        <v>0.04616379658824465</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4293501377105713</v>
+        <v>0.3824627697467804</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1342028975486755</v>
+        <v>0.1398172825574875</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4364469349384308</v>
+        <v>0.4777199625968933</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
       <c r="V3" t="n">
-        <v>0.0622767478533372</v>
+        <v>-0.1389724639873416</v>
       </c>
       <c r="W3" t="n">
         <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0622767478533372</v>
+        <v>-0.1389724639873416</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4364469349384308</v>
+        <v>0.4777199625968933</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -768,29 +768,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.291967329685794</v>
+        <v>1.69183312981252</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.291967329685794</v>
+        <v>1.69183312981252</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
+          <t>YgnMckC5</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.46875</v>
+        <v>45571.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -810,37 +810,37 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4305291206699657</v>
+        <v>0.3872529245663574</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3266082984392844</v>
+        <v>0.2964905203711174</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2428625808907499</v>
+        <v>0.3162565550625252</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05578329716260755</v>
+        <v>0.05399659863945572</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3340967893600464</v>
+        <v>0.4029093980789185</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3853948414325714</v>
+        <v>0.176955059170723</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2805083990097046</v>
+        <v>0.4201355278491974</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -849,19 +849,19 @@
         <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.04513427923739433</v>
+        <v>0.1038789727866722</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.04513427923739433</v>
+        <v>0.1038789727866722</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3853948414325714</v>
+        <v>0.4201355278491974</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -869,29 +869,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2.566466996692415</v>
+        <v>2.098315730578506</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.566466996692415</v>
+        <v>2.098315730578506</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.5625</v>
+        <v>45571.66666666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -911,56 +911,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="L5" t="n">
-        <v>0.306420233463035</v>
+        <v>0.3162565550625252</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2714007782101167</v>
+        <v>0.2964905203711174</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4221789883268482</v>
+        <v>0.3872529245663574</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05273937532002049</v>
+        <v>0.05399659863945572</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3563001751899719</v>
+        <v>0.3452627956867218</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3340717256069183</v>
+        <v>0.2492374777793884</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3096279799938202</v>
+        <v>0.4054996371269226</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.08489939697985521</v>
+        <v>0.0182467125605652</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.08489939697985521</v>
+        <v>0.0182467125605652</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3563001751899719</v>
+        <v>0.4054996371269226</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.5</v>
+        <v>2.45</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -968,29 +968,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2.687448215101285</v>
+        <v>2.025218556695605</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.687448215101285</v>
+        <v>2.025218556695605</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45570.5625</v>
+        <v>45583.66666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>valladolid</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1010,56 +1010,58 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3054989816700611</v>
+        <v>0.5342465753424658</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3156822810590631</v>
+        <v>0.2328767123287671</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3788187372708758</v>
+        <v>0.2328767123287671</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05591397849462365</v>
+        <v>0.10105580693816</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3665012717247009</v>
+        <v>0.3518827855587006</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2284272313117981</v>
+        <v>0.4924307763576508</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4050714671611786</v>
+        <v>0.1556863039731979</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
       <c r="V6" t="n">
-        <v>0.02625272989030281</v>
+        <v>-0.04181579898481502</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02625272989030281</v>
+        <v>-0.04181579898481502</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4050714671611786</v>
+        <v>0.4924307763576508</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1067,29 +1069,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>3.055313096128411</v>
+        <v>2.250541629497913</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.055313096128411</v>
+        <v>2.250541629497913</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45570.66666666666</v>
+        <v>45584.375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1109,56 +1111,58 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="K7" t="n">
-        <v>8.5</v>
+        <v>5.25</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7393104408029781</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1502278815711652</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1104616776258567</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0650486336266789</v>
+        <v>0.09523809523809512</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1944294422864914</v>
+        <v>0.3346075117588043</v>
       </c>
       <c r="R7" t="n">
-        <v>0.655281126499176</v>
+        <v>0.4842695593833923</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1502895206212997</v>
+        <v>0.1811229437589645</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
       <c r="V7" t="n">
-        <v>-0.08402931430380212</v>
+        <v>-0.1244260927905207</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.08402931430380212</v>
+        <v>-0.1244260927905207</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.655281126499176</v>
+        <v>0.4842695593833923</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1166,29 +1170,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.308753601480241</v>
+        <v>1.797194372880422</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.308753601480241</v>
+        <v>1.797194372880422</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.375</v>
+        <v>45584.46875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1208,56 +1212,58 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4048278591214879</v>
+        <v>0.3389830508474576</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2882865057380293</v>
+        <v>0.2542372881355933</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3068856351404828</v>
+        <v>0.4067796610169491</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05114286308521043</v>
+        <v>0.09259259259259256</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3445629477500916</v>
+        <v>0.3800272047519684</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3163427412509918</v>
+        <v>0.1932994276285172</v>
       </c>
       <c r="S8" t="n">
-        <v>0.339094340801239</v>
+        <v>0.4266733527183533</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
       <c r="V8" t="n">
-        <v>0.05627644201206228</v>
+        <v>0.01989369170140415</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0.05627644201206228</v>
+        <v>0.01989369170140415</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3445629477500916</v>
+        <v>0.4266733527183533</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1265,29 +1271,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>2.598918393535169</v>
+        <v>2.130968100724268</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.598918393535169</v>
+        <v>2.130968100724268</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.46875</v>
+        <v>45584.5625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1307,37 +1313,37 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5.25</v>
+        <v>2.35</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>1.57</v>
+        <v>2.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1814679252552495</v>
+        <v>0.3862613848348514</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2117125794644577</v>
+        <v>0.283660704488094</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6068194952802928</v>
+        <v>0.3300779106770548</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04964108785764831</v>
+        <v>0.1016682785299805</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3858337104320526</v>
+        <v>0.3630355894565582</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1373360604047775</v>
+        <v>0.3644575178623199</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4768302440643311</v>
+        <v>0.2725068926811218</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
@@ -1346,19 +1352,19 @@
         <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1299892512159617</v>
+        <v>-0.02180386697253145</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1299892512159617</v>
+        <v>-0.02180386697253145</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4768302440643311</v>
+        <v>0.3644575178623199</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.57</v>
+        <v>2.35</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1366,29 +1372,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>2.61610089486294</v>
+        <v>1.711341931692751</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.61610089486294</v>
+        <v>1.711341931692751</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.5625</v>
+        <v>45584.66666666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1408,37 +1414,37 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.45</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3872529245663574</v>
+        <v>0.2275204359673025</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2964905203711174</v>
+        <v>0.2275204359673025</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3162565550625252</v>
+        <v>0.5449591280653951</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05399659863945572</v>
+        <v>0.0988023952095809</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3961144983768463</v>
+        <v>0.3327634036540985</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1816236972808838</v>
+        <v>0.1142840981483459</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4222618043422699</v>
+        <v>0.5529524683952332</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
@@ -1447,19 +1453,19 @@
         <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1060052492797447</v>
+        <v>0.007993340329838006</v>
       </c>
       <c r="W10" t="n">
         <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1060052492797447</v>
+        <v>0.007993340329838006</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4222618043422699</v>
+        <v>0.5529524683952332</v>
       </c>
       <c r="Z10" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1467,29 +1473,29 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>3.18497382657762</v>
+        <v>2.761653765954296</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.18497382657762</v>
+        <v>2.761653765954296</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45571.66666666666</v>
+        <v>45585.375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1509,56 +1515,58 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2885143081144649</v>
+        <v>0.4825469888761029</v>
       </c>
       <c r="M11" t="n">
-        <v>0.297530380243042</v>
+        <v>0.2696586114307634</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4139553116424932</v>
+        <v>0.2477943996931339</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05031291172595509</v>
+        <v>0.09070370680277784</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3452627956867218</v>
+        <v>0.3684016764163971</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2492374777793884</v>
+        <v>0.4138889014720917</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4054996371269226</v>
+        <v>0.2177094221115112</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
       <c r="V11" t="n">
-        <v>-0.00845567451557061</v>
+        <v>-0.06865808740401119</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.00845567451557061</v>
+        <v>-0.06865808740401119</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4054996371269226</v>
+        <v>0.4138889014720917</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1566,29 +1574,29 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>2.994764423193725</v>
+        <v>1.724213259344952</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.994764423193725</v>
+        <v>1.724213259344952</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45583.66666666666</v>
+        <v>45585.46875</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1608,37 +1616,37 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9</v>
+        <v>7.5</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5342465753424658</v>
+        <v>0.6578947368421053</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2328767123287671</v>
+        <v>0.2192982456140351</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2328767123287671</v>
+        <v>0.1228070175438597</v>
       </c>
       <c r="O12" t="n">
-        <v>0.10105580693816</v>
+        <v>0.08571428571428563</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3700679242610931</v>
+        <v>0.2112197279930115</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4630305171012878</v>
+        <v>0.5492725372314453</v>
       </c>
       <c r="S12" t="n">
-        <v>0.166901558637619</v>
+        <v>0.2395076304674149</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1647,19 +1655,19 @@
         <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.07121605824117794</v>
+        <v>-0.10862219961066</v>
       </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.07121605824117794</v>
+        <v>-0.10862219961066</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4630305171012878</v>
+        <v>0.5492725372314453</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1667,29 +1675,29 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>2.955320096469362</v>
+        <v>2.200774449730198</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.955320096469362</v>
+        <v>2.200774449730198</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45584.375</v>
+        <v>45585.5625</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1709,37 +1717,37 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="J13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K13" t="n">
         <v>4.1</v>
       </c>
-      <c r="K13" t="n">
-        <v>5</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.5955320570548761</v>
+        <v>0.5227554453692225</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2222351334863318</v>
+        <v>0.2541172303878165</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1822328094587921</v>
+        <v>0.2231273242429609</v>
       </c>
       <c r="O13" t="n">
-        <v>0.09749721026622038</v>
+        <v>0.09310878823073954</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3308404684066772</v>
+        <v>0.3667539060115814</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4720935821533203</v>
+        <v>0.4507032334804535</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1970659643411636</v>
+        <v>0.1825428605079651</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
@@ -1748,19 +1756,19 @@
         <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1234384749015558</v>
+        <v>-0.07205221188876898</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1234384749015558</v>
+        <v>-0.07205221188876898</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4720935821533203</v>
+        <v>0.4507032334804535</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1768,29 +1776,29 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>2.629784128425187</v>
+        <v>1.891126415975561</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.629784128425187</v>
+        <v>1.891126415975561</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45584.46875</v>
+        <v>45585.66666666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1810,37 +1818,37 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.25</v>
+        <v>7</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3389830508474576</v>
+        <v>0.7031963470319634</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2542372881355933</v>
+        <v>0.1662100456621005</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4067796610169491</v>
+        <v>0.1305936073059361</v>
       </c>
       <c r="O14" t="n">
-        <v>0.09259259259259256</v>
+        <v>0.09390609390609383</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.387969970703125</v>
+        <v>0.2606417536735535</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2082197368144989</v>
+        <v>0.6414506435394287</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4038102030754089</v>
+        <v>0.09790761023759842</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
@@ -1849,19 +1857,19 @@
         <v>1</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.002969457941540188</v>
+        <v>-0.06174570349253472</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.002969457941540188</v>
+        <v>-0.06174570349253472</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.4038102030754089</v>
+        <v>0.6414506435394287</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.25</v>
+        <v>1.3</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1869,10 +1877,10 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>3.023402232332676</v>
+        <v>2.895265727756023</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.023402232332676</v>
+        <v>2.895265727756023</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,14 +510,14 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>prob_class_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>prob_class_0</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>prob_class_1</t>
-        </is>
-      </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>prob_class_2</t>
@@ -564,11 +564,6 @@
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>multiplier</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -577,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45571.375</v>
+        <v>45583.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +605,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3956834532374101</v>
+        <v>0.5546995377503853</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2877697841726619</v>
+        <v>0.2357473035439137</v>
       </c>
       <c r="N2" t="n">
-        <v>0.316546762589928</v>
+        <v>0.2095531587057011</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05303030303030298</v>
+        <v>0.06045751633986929</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3445629477500916</v>
+        <v>0.6673498749732971</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3163427412509918</v>
+        <v>0.2307066023349762</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3390943109989166</v>
+        <v>0.1019435897469521</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.05679316357742964</v>
+        <v>0.1126503372229118</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.05679316357742964</v>
+        <v>0.1126503372229118</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3445629477500916</v>
+        <v>0.6673498749732971</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +662,26 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>1.720877682351181</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.720877682351181</v>
+        <v>7.725158059933142</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45571.46875</v>
+        <v>45584.375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,58 +701,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5.25</v>
+        <v>1.5</v>
       </c>
       <c r="J3" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>1.55</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1820710973724884</v>
+        <v>0.6292134831460674</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2012364760432767</v>
+        <v>0.2359550561797753</v>
       </c>
       <c r="N3" t="n">
-        <v>0.616692426584235</v>
+        <v>0.1348314606741573</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04616379658824465</v>
+        <v>0.05952380952380953</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3824627697467804</v>
+        <v>0.5714911818504333</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1398172825574875</v>
+        <v>0.267119973897934</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4777199625968933</v>
+        <v>0.1613888591527939</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.1389724639873416</v>
+        <v>-0.05772230129563405</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1389724639873416</v>
+        <v>-0.05772230129563405</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4777199625968933</v>
+        <v>0.5714911818504333</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -768,24 +758,21 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>1.69183312981252</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.69183312981252</v>
+        <v>6.615509907496792</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45571.5625</v>
+        <v>45584.46875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>osasuna</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -810,58 +797,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3872529245663574</v>
+        <v>0.3617021276595744</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2964905203711174</v>
+        <v>0.2765957446808511</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3162565550625252</v>
+        <v>0.3617021276595744</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05399659863945572</v>
+        <v>0.06334841628959276</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4029093980789185</v>
+        <v>0.2678379118442535</v>
       </c>
       <c r="R4" t="n">
-        <v>0.176955059170723</v>
+        <v>0.332794189453125</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4201355278491974</v>
+        <v>0.3993678987026215</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1038789727866722</v>
+        <v>0.03766577104304702</v>
       </c>
       <c r="W4" t="n">
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1038789727866722</v>
+        <v>0.03766577104304702</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4201355278491974</v>
+        <v>0.3993678987026215</v>
       </c>
       <c r="Z4" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -869,29 +854,26 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2.098315730578506</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.098315730578506</v>
+        <v>4.62303247103263</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45571.66666666666</v>
+        <v>45584.5625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>atl  madrid</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -911,56 +893,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3162565550625252</v>
+        <v>0.3938223938223938</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2964905203711174</v>
+        <v>0.277992277992278</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3872529245663574</v>
+        <v>0.3281853281853282</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05399659863945572</v>
+        <v>0.05800653594771243</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3452627956867218</v>
+        <v>0.4895497262477875</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2492374777793884</v>
+        <v>0.3255585432052612</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4054996371269226</v>
+        <v>0.1848916709423065</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.0182467125605652</v>
+        <v>0.09572733242539366</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0182467125605652</v>
+        <v>0.09572733242539366</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4054996371269226</v>
+        <v>0.4895497262477875</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -968,29 +950,26 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2.025218556695605</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.025218556695605</v>
+        <v>5.666965942883383</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45583.66666666666</v>
+        <v>45584.66666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1010,58 +989,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>4.33</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>1.67</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5342465753424658</v>
+        <v>0.2177314211212516</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2328767123287671</v>
+        <v>0.2177314211212516</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2328767123287671</v>
+        <v>0.5645371577574968</v>
       </c>
       <c r="O6" t="n">
-        <v>0.10105580693816</v>
+        <v>0.06069615964376096</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3518827855587006</v>
+        <v>0.1781003326177597</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4924307763576508</v>
+        <v>0.3033130168914795</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1556863039731979</v>
+        <v>0.5185866355895996</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.04181579898481502</v>
+        <v>-0.04595052216789719</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.04181579898481502</v>
+        <v>-0.04595052216789719</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4924307763576508</v>
+        <v>0.5185866355895996</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1069,29 +1046,26 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>2.250541629497913</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.250541629497913</v>
+        <v>6.003093546483254</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45584.375</v>
+        <v>45585.375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1111,58 +1085,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.472913616398243</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.2781844802342606</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.2489019033674963</v>
       </c>
       <c r="O7" t="n">
-        <v>0.09523809523809512</v>
+        <v>0.05727554179566563</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3346075117588043</v>
+        <v>0.3904880583286285</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4842695593833923</v>
+        <v>0.358215719461441</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1811229437589645</v>
+        <v>0.2512962818145752</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.1244260927905207</v>
+        <v>-0.08242555806961449</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1244260927905207</v>
+        <v>-0.08242555806961449</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4842695593833923</v>
+        <v>0.3904880583286285</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1170,29 +1142,26 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>1.797194372880422</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.797194372880422</v>
+        <v>4.520240557811974</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45584.46875</v>
+        <v>45585.46875</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1212,37 +1181,37 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>1.33</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="K8" t="n">
-        <v>2.25</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3389830508474576</v>
+        <v>0.7077140835102618</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2542372881355933</v>
+        <v>0.1981599433828733</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4067796610169491</v>
+        <v>0.09412597310686482</v>
       </c>
       <c r="O8" t="n">
-        <v>0.09259259259259256</v>
+        <v>0.06240601503759402</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3800272047519684</v>
+        <v>0.726938784122467</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1932994276285172</v>
+        <v>0.1874948590993881</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4266733527183533</v>
+        <v>0.08556638658046722</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1251,19 +1220,19 @@
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01989369170140415</v>
+        <v>0.01922470061220527</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01989369170140415</v>
+        <v>0.01922470061220527</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4266733527183533</v>
+        <v>0.726938784122467</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>1.33</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1271,29 +1240,26 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>2.130968100724268</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.130968100724268</v>
+        <v>8.41495176344549</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h2NyhKup</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45584.5625</v>
+        <v>45585.5625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1313,58 +1279,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3862613848348514</v>
+        <v>0.5370967741935485</v>
       </c>
       <c r="M9" t="n">
-        <v>0.283660704488094</v>
+        <v>0.2540322580645161</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3300779106770548</v>
+        <v>0.2088709677419355</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1016682785299805</v>
+        <v>0.06392106392106367</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3630355894565582</v>
+        <v>0.5907658934593201</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3644575178623199</v>
+        <v>0.2744113206863403</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2725068926811218</v>
+        <v>0.1348228305578232</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.02180386697253145</v>
+        <v>0.05366911926577156</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.02180386697253145</v>
+        <v>0.05366911926577156</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3644575178623199</v>
+        <v>0.5907658934593201</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1372,29 +1336,26 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>1.711341931692751</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.711341931692751</v>
+        <v>6.838631540274855</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8Uo5ctIM</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45584.66666666666</v>
+        <v>45585.66666666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>real madrid</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1414,58 +1375,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>1.67</v>
+        <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2275204359673025</v>
+        <v>0.7250755287009064</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2275204359673025</v>
+        <v>0.1570996978851964</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5449591280653951</v>
+        <v>0.1178247734138973</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0988023952095809</v>
+        <v>0.06089743589743568</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3327634036540985</v>
+        <v>0.7515518665313721</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1142840981483459</v>
+        <v>0.170487567782402</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5529524683952332</v>
+        <v>0.07796047627925873</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.007993340329838006</v>
+        <v>0.02647633783046566</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.007993340329838006</v>
+        <v>0.02647633783046566</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5529524683952332</v>
+        <v>0.7515518665313721</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1473,29 +1432,26 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>2.761653765954296</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.761653765954296</v>
+        <v>8.699869703916461</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>QqTA4cPk</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45585.375</v>
+        <v>45586.66666666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1515,58 +1471,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4825469888761029</v>
+        <v>0.5392195506503745</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2696586114307634</v>
+        <v>0.2621206148994876</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2477943996931339</v>
+        <v>0.198659834450138</v>
       </c>
       <c r="O11" t="n">
-        <v>0.09070370680277784</v>
+        <v>0.05973266499582275</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3684016764163971</v>
+        <v>0.4497665762901306</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4138889014720917</v>
+        <v>0.3399279117584229</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2177094221115112</v>
+        <v>0.2103055566549301</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>1</v>
-      </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-0.06865808740401119</v>
+        <v>-0.08945297436024391</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.06865808740401119</v>
+        <v>-0.08945297436024391</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4138889014720917</v>
+        <v>0.4497665762901306</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1574,29 +1528,26 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>1.724213259344952</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.724213259344952</v>
+        <v>5.206441212048274</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45585.46875</v>
+        <v>45590.66666666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1616,58 +1567,56 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>7.5</v>
+        <v>2.45</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6578947368421053</v>
+        <v>0.3480113636363636</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2192982456140351</v>
+        <v>0.2684659090909091</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1228070175438597</v>
+        <v>0.3835227272727272</v>
       </c>
       <c r="O12" t="n">
-        <v>0.08571428571428563</v>
+        <v>0.06424792139077851</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2112197279930115</v>
+        <v>0.3013800978660583</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5492725372314453</v>
+        <v>0.3700269460678101</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2395076304674149</v>
+        <v>0.3285929262638092</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>-0.10862219961066</v>
+        <v>0.101561036976901</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.10862219961066</v>
+        <v>0.101561036976901</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5492725372314453</v>
+        <v>0.3700269460678101</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1675,29 +1624,26 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>2.200774449730198</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.200774449730198</v>
+        <v>4.283385300585495</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>x88gL4RQ</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45585.5625</v>
+        <v>45591.375</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>villarreal</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>getafe</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1717,58 +1663,56 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1</v>
+        <v>1.95</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5227554453692225</v>
+        <v>0.2627324171382376</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2541172303878165</v>
+        <v>0.2522231204527081</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2231273242429609</v>
+        <v>0.4850444624090541</v>
       </c>
       <c r="O13" t="n">
-        <v>0.09310878823073954</v>
+        <v>0.05726495726495751</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3667539060115814</v>
+        <v>0.2713927626609802</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4507032334804535</v>
+        <v>0.3275697231292725</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1825428605079651</v>
+        <v>0.4010374546051025</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>-0.07205221188876898</v>
+        <v>-0.08400700780395159</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.07205221188876898</v>
+        <v>-0.08400700780395159</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4507032334804535</v>
+        <v>0.4010374546051025</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1776,29 +1720,26 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>1.891126415975561</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.891126415975561</v>
+        <v>4.642359039779012</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>dhkQFrkl</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45585.66666666666</v>
+        <v>45591.46875</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1818,58 +1759,56 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="J14" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7031963470319634</v>
+        <v>0.4365343242714649</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1662100456621005</v>
+        <v>0.3027576765108547</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1305936073059361</v>
+        <v>0.2607079992176805</v>
       </c>
       <c r="O14" t="n">
-        <v>0.09390609390609383</v>
+        <v>0.06547470200883554</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2606417536735535</v>
+        <v>0.5210584402084351</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6414506435394287</v>
+        <v>0.2715503573417664</v>
       </c>
       <c r="S14" t="n">
-        <v>0.09790761023759842</v>
+        <v>0.207391157746315</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>-0.06174570349253472</v>
+        <v>0.08452411593697018</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.06174570349253472</v>
+        <v>0.08452411593697018</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.6414506435394287</v>
+        <v>0.5210584402084351</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1877,10 +1816,681 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>2.895265727756023</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.895265727756023</v>
+        <v>6.031706845278793</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>8Sp1FEw8</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45591.5625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>148</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.2611940298507463</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2686567164179104</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.4701492537313433</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06349206349206349</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.2521133720874786</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3590907752513885</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.3887958228588104</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.08135343087253288</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.08135343087253288</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.3887958228588104</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.500651453251951</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4zlpJdvq</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45591.66666666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>148</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.54584017471928</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2360758755660886</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.2180839497146315</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.05898156429801493</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.5270339846611023</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2914429605007172</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.1815229505300522</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>-0.01880619005817774</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.01880619005817774</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.5270339846611023</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>6.100878994884513</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45592.41666666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>148</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.3236326109391125</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2932920536635707</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.3830753353973168</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06549085151301903</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.313975602388382</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3678199052810669</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3182044327259064</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.0745278516174962</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.0745278516174962</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.3678199052810669</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.257836874547366</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45592.51041666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>148</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.4378536585365854</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2768780487804878</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.2852682926829269</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06226422915889396</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.5595535039901733</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.2826571762561798</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.157789409160614</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.121699845453588</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.121699845453588</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.5595535039901733</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>6.477320852853209</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45592.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>148</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.3271028037383177</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2770753161077515</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.3958218801539307</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.06150793650793651</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.3088712990283966</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3722001910209656</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.3189284801483154</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.09512487491321403</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.09512487491321403</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.3722001910209656</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>4.308542510312627</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45592.70833333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>148</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.5681070410177671</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2533450318052204</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.1785479271770125</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.06680706680706683</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.4601970016956329</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.3222656846046448</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.2175373435020447</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>-0.1079100393221342</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.1079100393221342</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.4601970016956329</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>4.702605993479978</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45593.70833333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>148</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.3156822810590631</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.3054989816700611</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.3788187372708758</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.05591397849462365</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.3670017123222351</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3658300042152405</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2671682834625244</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.05131943126317201</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.05131943126317201</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.3670017123222351</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>4.248365575956424</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>7.725158059933142</v>
+        <v>6.910764987531603</v>
       </c>
     </row>
     <row r="3">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>6.615509907496792</v>
+        <v>5.918096935843527</v>
       </c>
     </row>
     <row r="4">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.62303247103263</v>
+        <v>4.135668252891451</v>
       </c>
     </row>
     <row r="5">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>5.666965942883383</v>
+        <v>5.069549324399381</v>
       </c>
     </row>
     <row r="6">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>6.003093546483254</v>
+        <v>5.370242055380344</v>
       </c>
     </row>
     <row r="7">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.520240557811974</v>
+        <v>4.043712755104155</v>
       </c>
     </row>
     <row r="8">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>8.41495176344549</v>
+        <v>7.527840021837651</v>
       </c>
     </row>
     <row r="9">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>6.838631540274855</v>
+        <v>6.11769688652426</v>
       </c>
     </row>
     <row r="10">
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>8.699869703916461</v>
+        <v>7.782721658180952</v>
       </c>
     </row>
     <row r="11">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>5.206441212048274</v>
+        <v>4.657573522602617</v>
       </c>
     </row>
     <row r="12">
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>4.283385300585495</v>
+        <v>3.831826990948319</v>
       </c>
     </row>
     <row r="13">
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>4.642359039779012</v>
+        <v>4.152957397474051</v>
       </c>
     </row>
     <row r="14">
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>6.031706845278793</v>
+        <v>5.395838914623856</v>
       </c>
     </row>
     <row r="15">
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>4.500651453251951</v>
+        <v>4.026188751468212</v>
       </c>
     </row>
     <row r="16">
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>6.100878994884513</v>
+        <v>5.457718874347508</v>
       </c>
     </row>
     <row r="17">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>4.257836874547366</v>
+        <v>3.808971902834773</v>
       </c>
     </row>
     <row r="18">
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>6.477320852853209</v>
+        <v>5.794475894942879</v>
       </c>
     </row>
     <row r="19">
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>4.308542510312627</v>
+        <v>3.854332105124294</v>
       </c>
     </row>
     <row r="20">
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>4.702605993479978</v>
+        <v>4.206853063428317</v>
       </c>
     </row>
     <row r="21">
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>4.248365575956424</v>
+        <v>3.800499077012837</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -605,56 +605,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5546995377503853</v>
+        <v>0.5689677299756157</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2357473035439137</v>
+        <v>0.2500463444892837</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2095531587057011</v>
+        <v>0.1809859255351006</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06045751633986929</v>
+        <v>0.0524364804226134</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6673498749732971</v>
+        <v>0.669661283493042</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2307066023349762</v>
+        <v>0.2293326407670975</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1019435897469521</v>
+        <v>0.1010061129927635</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1126503372229118</v>
+        <v>0.1006935535174263</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1126503372229118</v>
+        <v>0.1006935535174263</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6673498749732971</v>
+        <v>0.669661283493042</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>6.910764987531603</v>
+        <v>6.934700859357118</v>
       </c>
     </row>
     <row r="3">
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6292134831460674</v>
+        <v>0.6417212738428149</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2359550561797753</v>
+        <v>0.2316457281188698</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1348314606741573</v>
+        <v>0.1266329980383155</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05952380952380953</v>
+        <v>0.0529114480333992</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -738,19 +738,19 @@
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.05772230129563405</v>
+        <v>-0.0702300919923815</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.05772230129563405</v>
+        <v>-0.0702300919923815</v>
       </c>
       <c r="Y3" t="n">
         <v>0.5714911818504333</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -821,29 +821,29 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2678379118442535</v>
+        <v>0.2668277025222778</v>
       </c>
       <c r="R4" t="n">
-        <v>0.332794189453125</v>
+        <v>0.3323536515235901</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3993678987026215</v>
+        <v>0.4008186161518097</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.03766577104304702</v>
+        <v>0.03911648849223526</v>
       </c>
       <c r="W4" t="n">
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03766577104304702</v>
+        <v>0.03911648849223526</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3993678987026215</v>
+        <v>0.4008186161518097</v>
       </c>
       <c r="Z4" t="n">
         <v>2.6</v>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.135668252891451</v>
+        <v>4.15069120821163</v>
       </c>
     </row>
     <row r="5">
@@ -899,19 +899,19 @@
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3938223938223938</v>
+        <v>0.3947157726180945</v>
       </c>
       <c r="M5" t="n">
-        <v>0.277992277992278</v>
+        <v>0.2786228983186549</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3281853281853282</v>
+        <v>0.3266613290632506</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05800653594771243</v>
+        <v>0.05561189993238669</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -930,13 +930,13 @@
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.09572733242539366</v>
+        <v>0.09483395362969294</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09572733242539366</v>
+        <v>0.09483395362969294</v>
       </c>
       <c r="Y5" t="n">
         <v>0.4895497262477875</v>
@@ -989,56 +989,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2177314211212516</v>
+        <v>0.2077922077922078</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2177314211212516</v>
+        <v>0.2077922077922078</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5645371577574968</v>
+        <v>0.5844155844155844</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06069615964376096</v>
+        <v>0.06944444444444442</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1781003326177597</v>
+        <v>0.178535208106041</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3033130168914795</v>
+        <v>0.3037036061286926</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5185866355895996</v>
+        <v>0.5177611708641052</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.04595052216789719</v>
+        <v>-0.06665441355147916</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.04595052216789719</v>
+        <v>-0.06665441355147916</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5185866355895996</v>
+        <v>0.5177611708641052</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>5.370242055380344</v>
+        <v>5.361693926524222</v>
       </c>
     </row>
     <row r="7">
@@ -1088,22 +1088,22 @@
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="L7" t="n">
-        <v>0.472913616398243</v>
+        <v>0.4745960470954284</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2781844802342606</v>
+        <v>0.3061909981260828</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2489019033674963</v>
+        <v>0.2192129547784888</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05727554179566563</v>
+        <v>0.0535275273783804</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1122,13 +1122,13 @@
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.08242555806961449</v>
+        <v>-0.08410798876679981</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.08242555806961449</v>
+        <v>-0.08410798876679981</v>
       </c>
       <c r="Y7" t="n">
         <v>0.3904880583286285</v>
@@ -1205,13 +1205,13 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.726938784122467</v>
+        <v>0.7285870909690857</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1874948590993881</v>
+        <v>0.1864692121744156</v>
       </c>
       <c r="S8" t="n">
-        <v>0.08556638658046722</v>
+        <v>0.08494370430707932</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1220,16 +1220,16 @@
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.01922470061220527</v>
+        <v>0.02087300745882392</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01922470061220527</v>
+        <v>0.02087300745882392</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.726938784122467</v>
+        <v>0.7285870909690857</v>
       </c>
       <c r="Z8" t="n">
         <v>1.33</v>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>7.527840021837651</v>
+        <v>7.54490912107855</v>
       </c>
     </row>
     <row r="9">
@@ -1378,50 +1378,50 @@
         <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="K10" t="n">
         <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7250755287009064</v>
+        <v>0.7201565557729942</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1570996978851964</v>
+        <v>0.1628180039138943</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1178247734138973</v>
+        <v>0.1170254403131116</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06089743589743568</v>
+        <v>0.06814381270902992</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7515518665313721</v>
+        <v>0.7510959506034851</v>
       </c>
       <c r="R10" t="n">
-        <v>0.170487567782402</v>
+        <v>0.1708084046840668</v>
       </c>
       <c r="S10" t="n">
-        <v>0.07796047627925873</v>
+        <v>0.07809565961360931</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.02647633783046566</v>
+        <v>0.03093939483049091</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.02647633783046566</v>
+        <v>0.03093939483049091</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.7515518665313721</v>
+        <v>0.7510959506034851</v>
       </c>
       <c r="Z10" t="n">
         <v>1.3</v>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>7.782721658180952</v>
+        <v>7.778000404832661</v>
       </c>
     </row>
     <row r="11">
@@ -1495,29 +1495,29 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4497665762901306</v>
+        <v>0.4499695599079132</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3399279117584229</v>
+        <v>0.3398557603359222</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2103055566549301</v>
+        <v>0.2101746201515198</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-0.08945297436024391</v>
+        <v>-0.08924999074246132</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.08945297436024391</v>
+        <v>-0.08924999074246132</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4497665762901306</v>
+        <v>0.4499695599079132</v>
       </c>
       <c r="Z11" t="n">
         <v>1.75</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>4.657573522602617</v>
+        <v>4.659675526560992</v>
       </c>
     </row>
     <row r="12">
@@ -1567,53 +1567,53 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="J12" t="n">
         <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3480113636363636</v>
+        <v>0.3411167512690355</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2684659090909091</v>
+        <v>0.2680203045685279</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3835227272727272</v>
+        <v>0.3908629441624366</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06424792139077851</v>
+        <v>0.06601731601731609</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3013800978660583</v>
+        <v>0.3017470240592957</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3700269460678101</v>
+        <v>0.3700113892555237</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3285929262638092</v>
+        <v>0.3282416462898254</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.101561036976901</v>
+        <v>0.1019910846869958</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.101561036976901</v>
+        <v>0.1019910846869958</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.3700269460678101</v>
+        <v>0.3700113892555237</v>
       </c>
       <c r="Z12" t="n">
         <v>3.5</v>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>3.831826990948319</v>
+        <v>3.831665891834199</v>
       </c>
     </row>
     <row r="13">
@@ -1663,56 +1663,56 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2627324171382376</v>
+        <v>0.2705667276051188</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2522231204527081</v>
+        <v>0.2559414990859232</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4850444624090541</v>
+        <v>0.473491773308958</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05726495726495751</v>
+        <v>0.05598455598455598</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2713927626609802</v>
+        <v>0.2713698446750641</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3275697231292725</v>
+        <v>0.3275195956230164</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4010374546051025</v>
+        <v>0.4011105298995972</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>-0.08400700780395159</v>
+        <v>-0.07238124340936081</v>
       </c>
       <c r="W13" t="n">
         <v>2</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.08400700780395159</v>
+        <v>-0.07238124340936081</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4010374546051025</v>
+        <v>0.4011105298995972</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>4.152957397474051</v>
+        <v>4.153714131243825</v>
       </c>
     </row>
     <row r="14">
@@ -1759,56 +1759,56 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4365343242714649</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3027576765108547</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2607079992176805</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="O14" t="n">
-        <v>0.06547470200883554</v>
+        <v>0.0625</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5210584402084351</v>
+        <v>0.5164309144020081</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2715503573417664</v>
+        <v>0.2730623781681061</v>
       </c>
       <c r="S14" t="n">
-        <v>0.207391157746315</v>
+        <v>0.2105065882205963</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.08452411593697018</v>
+        <v>0.04584267910789042</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>0.08452411593697018</v>
+        <v>0.04584267910789042</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.5210584402084351</v>
+        <v>0.5164309144020081</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>5.395838914623856</v>
+        <v>5.347918409171998</v>
       </c>
     </row>
     <row r="15">
@@ -1879,29 +1879,29 @@
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2521133720874786</v>
+        <v>0.2520309388637543</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3590907752513885</v>
+        <v>0.3590537309646606</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3887958228588104</v>
+        <v>0.3889154195785522</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>-0.08135343087253288</v>
+        <v>-0.08123383415279106</v>
       </c>
       <c r="W15" t="n">
         <v>2</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.08135343087253288</v>
+        <v>-0.08123383415279106</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.3887958228588104</v>
+        <v>0.3889154195785522</v>
       </c>
       <c r="Z15" t="n">
         <v>2</v>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>4.026188751468212</v>
+        <v>4.027427239485383</v>
       </c>
     </row>
     <row r="16">
@@ -1951,56 +1951,56 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
-        <v>0.54584017471928</v>
+        <v>0.4918386424102969</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.2472136334220176</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.2609477241676853</v>
       </c>
       <c r="O16" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.06449588193870381</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5270339846611023</v>
+        <v>0.5266638994216919</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2914429605007172</v>
+        <v>0.291552871465683</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1815229505300522</v>
+        <v>0.1817832738161087</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>-0.01880619005817774</v>
+        <v>0.03482525701139499</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.01880619005817774</v>
+        <v>0.03482525701139499</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5270339846611023</v>
+        <v>0.5266638994216919</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>5.457718874347508</v>
+        <v>5.45388644369781</v>
       </c>
     </row>
     <row r="17">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
         <v>3.2</v>
@@ -2056,28 +2056,28 @@
         <v>2.45</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3236326109391125</v>
+        <v>0.3162565550625252</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2932920536635707</v>
+        <v>0.2964905203711174</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3830753353973168</v>
+        <v>0.3872529245663574</v>
       </c>
       <c r="O17" t="n">
-        <v>0.06549085151301903</v>
+        <v>0.05399659863945572</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.313975602388382</v>
+        <v>0.3127180337905884</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3678199052810669</v>
+        <v>0.3681450188159943</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3182044327259064</v>
+        <v>0.3191368877887726</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
@@ -2086,16 +2086,16 @@
         <v>1</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0745278516174962</v>
+        <v>0.07165449844487687</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0745278516174962</v>
+        <v>0.07165449844487687</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.3678199052810669</v>
+        <v>0.3681450188159943</v>
       </c>
       <c r="Z17" t="n">
         <v>3.2</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>3.808971902834773</v>
+        <v>3.812338627424687</v>
       </c>
     </row>
     <row r="18">
@@ -2145,56 +2145,56 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4378536585365854</v>
+        <v>0.415347137637028</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2768780487804878</v>
+        <v>0.2831912302070646</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2852682926829269</v>
+        <v>0.3014616321559074</v>
       </c>
       <c r="O18" t="n">
-        <v>0.06226422915889396</v>
+        <v>0.07005539263603766</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5595535039901733</v>
+        <v>0.5595623254776001</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2826571762561798</v>
+        <v>0.282652735710144</v>
       </c>
       <c r="S18" t="n">
-        <v>0.157789409160614</v>
+        <v>0.1577849239110947</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.121699845453588</v>
+        <v>0.1442151878405721</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>0.121699845453588</v>
+        <v>0.1442151878405721</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.5595535039901733</v>
+        <v>0.5595623254776001</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>5.794475894942879</v>
+        <v>5.79456724616468</v>
       </c>
     </row>
     <row r="19">
@@ -2241,25 +2241,25 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
         <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3271028037383177</v>
+        <v>0.3211498973305955</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2770753161077515</v>
+        <v>0.2739219712525667</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3958218801539307</v>
+        <v>0.4049281314168378</v>
       </c>
       <c r="O19" t="n">
-        <v>0.06150793650793651</v>
+        <v>0.0737278419613725</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2278,13 +2278,13 @@
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.09512487491321403</v>
+        <v>0.0982782197683989</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.09512487491321403</v>
+        <v>0.0982782197683989</v>
       </c>
       <c r="Y19" t="n">
         <v>0.3722001910209656</v>
@@ -2337,56 +2337,56 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5681070410177671</v>
+        <v>0.5223880597014926</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2533450318052204</v>
+        <v>0.2686567164179104</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1785479271770125</v>
+        <v>0.208955223880597</v>
       </c>
       <c r="O20" t="n">
-        <v>0.06680706680706683</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.4601970016956329</v>
+        <v>0.4631039500236511</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3222656846046448</v>
+        <v>0.3212946355342865</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2175373435020447</v>
+        <v>0.2156014740467072</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>-0.1079100393221342</v>
+        <v>-0.05928410967784148</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1079100393221342</v>
+        <v>-0.05928410967784148</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.4601970016956329</v>
+        <v>0.4631039500236511</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>4.206853063428317</v>
+        <v>4.79568916310817</v>
       </c>
     </row>
     <row r="21">

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K3" t="n">
         <v>7.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6417212738428149</v>
+        <v>0.6499535747446611</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2316457281188698</v>
+        <v>0.2243887341380377</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1266329980383155</v>
+        <v>0.1256576911173011</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0529114480333992</v>
+        <v>0.06108374384236459</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -738,19 +738,19 @@
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.0702300919923815</v>
+        <v>-0.07846239289422774</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0702300919923815</v>
+        <v>-0.07846239289422774</v>
       </c>
       <c r="Y3" t="n">
         <v>0.5714911818504333</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3617021276595744</v>
+        <v>0.3677036001398113</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2765957446808511</v>
+        <v>0.2757777001048585</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3617021276595744</v>
+        <v>0.3565186997553303</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06334841628959276</v>
+        <v>0.06650264668605077</v>
       </c>
       <c r="P4" t="n">
         <v>2</v>
@@ -834,19 +834,19 @@
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.03911648849223526</v>
+        <v>0.04429991639647934</v>
       </c>
       <c r="W4" t="n">
         <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03911648849223526</v>
+        <v>0.04429991639647934</v>
       </c>
       <c r="Y4" t="n">
         <v>0.4008186161518097</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="J6" t="n">
         <v>4.5</v>
@@ -998,16 +998,16 @@
         <v>1.6</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2077922077922078</v>
+        <v>0.1990324809951624</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2077922077922078</v>
+        <v>0.2100898410504492</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5844155844155844</v>
+        <v>0.5908776779543885</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06944444444444442</v>
+        <v>0.05774853801169577</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
@@ -1026,13 +1026,13 @@
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.06665441355147916</v>
+        <v>-0.07311650709028328</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.06665441355147916</v>
+        <v>-0.07311650709028328</v>
       </c>
       <c r="Y6" t="n">
         <v>0.5177611708641052</v>
@@ -1085,25 +1085,25 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="J7" t="n">
         <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4745960470954284</v>
+        <v>0.4600259692079391</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3061909981260828</v>
+        <v>0.3042107215729919</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2192129547784888</v>
+        <v>0.2357633092190688</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0535275273783804</v>
+        <v>0.06038552321007096</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1122,19 +1122,19 @@
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.08410798876679981</v>
+        <v>-0.0695379108793106</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.08410798876679981</v>
+        <v>-0.0695379108793106</v>
       </c>
       <c r="Y7" t="n">
         <v>0.3904880583286285</v>
       </c>
       <c r="Z7" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1205,13 +1205,13 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7285870909690857</v>
+        <v>0.7285851240158081</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1864692121744156</v>
+        <v>0.1864701211452484</v>
       </c>
       <c r="S8" t="n">
-        <v>0.08494370430707932</v>
+        <v>0.08494473248720169</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1220,16 +1220,16 @@
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.02087300745882392</v>
+        <v>0.02087104050554633</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02087300745882392</v>
+        <v>0.02087104050554633</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.7285870909690857</v>
+        <v>0.7285851240158081</v>
       </c>
       <c r="Z8" t="n">
         <v>1.33</v>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>7.54490912107855</v>
+        <v>7.544888752225041</v>
       </c>
     </row>
     <row r="9">
@@ -1399,29 +1399,29 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7510959506034851</v>
+        <v>0.7480214834213257</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1708084046840668</v>
+        <v>0.1728740930557251</v>
       </c>
       <c r="S10" t="n">
-        <v>0.07809565961360931</v>
+        <v>0.07910438627004623</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.03093939483049091</v>
+        <v>0.02786492764833148</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03093939483049091</v>
+        <v>0.02786492764833148</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.7510959506034851</v>
+        <v>0.7480214834213257</v>
       </c>
       <c r="Z10" t="n">
         <v>1.3</v>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>7.778000404832661</v>
+        <v>7.746162652321457</v>
       </c>
     </row>
     <row r="11">
@@ -1495,29 +1495,29 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4499695599079132</v>
+        <v>0.4536928236484528</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3398557603359222</v>
+        <v>0.3383599817752838</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2101746201515198</v>
+        <v>0.207947164773941</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-0.08924999074246132</v>
+        <v>-0.08552672700192177</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.08924999074246132</v>
+        <v>-0.08552672700192177</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4499695599079132</v>
+        <v>0.4536928236484528</v>
       </c>
       <c r="Z11" t="n">
         <v>1.75</v>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>4.659675526560992</v>
+        <v>4.69823191454038</v>
       </c>
     </row>
     <row r="12">
@@ -1567,53 +1567,53 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="J12" t="n">
         <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3411167512690355</v>
+        <v>0.3359683794466403</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2680203045685279</v>
+        <v>0.2687747035573123</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3908629441624366</v>
+        <v>0.3952569169960474</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06601731601731609</v>
+        <v>0.06302521008403361</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3017470240592957</v>
+        <v>0.301744818687439</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3700113892555237</v>
+        <v>0.3700104951858521</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3282416462898254</v>
+        <v>0.3282446563243866</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1019910846869958</v>
+        <v>0.1012357916285398</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1019910846869958</v>
+        <v>0.1012357916285398</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.3700113892555237</v>
+        <v>0.3700104951858521</v>
       </c>
       <c r="Z12" t="n">
         <v>3.5</v>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>3.831665891834199</v>
+        <v>3.831656633264422</v>
       </c>
     </row>
     <row r="13">
@@ -1765,19 +1765,19 @@
         <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4733044733044733</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2958152958152958</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2308802308802309</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0625</v>
+        <v>0.05640243902439024</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -1796,13 +1796,13 @@
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.04584267910789042</v>
+        <v>0.04312644109753477</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>0.04584267910789042</v>
+        <v>0.04312644109753477</v>
       </c>
       <c r="Y14" t="n">
         <v>0.5164309144020081</v>
@@ -1879,29 +1879,29 @@
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2520309388637543</v>
+        <v>0.2520247101783752</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3590537309646606</v>
+        <v>0.3590483963489532</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3889154195785522</v>
+        <v>0.3889268934726715</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>-0.08123383415279106</v>
+        <v>-0.0812223602586718</v>
       </c>
       <c r="W15" t="n">
         <v>2</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.08123383415279106</v>
+        <v>-0.0812223602586718</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.3889154195785522</v>
+        <v>0.3889268934726715</v>
       </c>
       <c r="Z15" t="n">
         <v>2</v>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>4.027427239485383</v>
+        <v>4.027546057797522</v>
       </c>
     </row>
     <row r="16">
@@ -1975,29 +1975,29 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5266638994216919</v>
+        <v>0.5309537649154663</v>
       </c>
       <c r="R16" t="n">
-        <v>0.291552871465683</v>
+        <v>0.2891775071620941</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1817832738161087</v>
+        <v>0.1798686534166336</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.03482525701139499</v>
+        <v>0.03911512250516941</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03482525701139499</v>
+        <v>0.03911512250516941</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5266638994216919</v>
+        <v>0.5309537649154663</v>
       </c>
       <c r="Z16" t="n">
         <v>1.91</v>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>5.45388644369781</v>
+        <v>5.498310295963884</v>
       </c>
     </row>
     <row r="17">
@@ -2071,13 +2071,13 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.3127180337905884</v>
+        <v>0.3127173781394958</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3681450188159943</v>
+        <v>0.3681437373161316</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3191368877887726</v>
+        <v>0.3191388547420502</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
@@ -2086,16 +2086,16 @@
         <v>1</v>
       </c>
       <c r="V17" t="n">
-        <v>0.07165449844487687</v>
+        <v>0.0716532169450142</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.07165449844487687</v>
+        <v>0.0716532169450142</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.3681450188159943</v>
+        <v>0.3681437373161316</v>
       </c>
       <c r="Z17" t="n">
         <v>3.2</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>3.812338627424687</v>
+        <v>3.812325356808007</v>
       </c>
     </row>
     <row r="18">
@@ -2151,47 +2151,47 @@
         <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L18" t="n">
-        <v>0.415347137637028</v>
+        <v>0.4192972007147112</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2831912302070646</v>
+        <v>0.2858844550327576</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3014616321559074</v>
+        <v>0.2948183442525313</v>
       </c>
       <c r="O18" t="n">
-        <v>0.07005539263603766</v>
+        <v>0.0599747474747474</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5595623254776001</v>
+        <v>0.5567981600761414</v>
       </c>
       <c r="R18" t="n">
-        <v>0.282652735710144</v>
+        <v>0.2840888202190399</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1577849239110947</v>
+        <v>0.1591130346059799</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1442151878405721</v>
+        <v>0.1375009593614302</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1442151878405721</v>
+        <v>0.1375009593614302</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.5595623254776001</v>
+        <v>0.5567981600761414</v>
       </c>
       <c r="Z18" t="n">
         <v>2.25</v>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>5.79456724616468</v>
+        <v>5.765942834604084</v>
       </c>
     </row>
     <row r="19">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
         <v>3.4</v>
@@ -2250,16 +2250,16 @@
         <v>2.3</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3211498973305955</v>
+        <v>0.3138041733547351</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2739219712525667</v>
+        <v>0.2768860353130016</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4049281314168378</v>
+        <v>0.4093097913322633</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0737278419613725</v>
+        <v>0.06223358908780918</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2278,13 +2278,13 @@
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.0982782197683989</v>
+        <v>0.09531415570796398</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0982782197683989</v>
+        <v>0.09531415570796398</v>
       </c>
       <c r="Y19" t="n">
         <v>0.3722001910209656</v>
@@ -2337,25 +2337,25 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="J20" t="n">
         <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5223880597014926</v>
+        <v>0.5140093406910212</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2686567164179104</v>
+        <v>0.2687534552755911</v>
       </c>
       <c r="N20" t="n">
-        <v>0.208955223880597</v>
+        <v>0.2172372040333877</v>
       </c>
       <c r="O20" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.06310925536306966</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
@@ -2374,19 +2374,19 @@
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>-0.05928410967784148</v>
+        <v>-0.0509053906673701</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.05928410967784148</v>
+        <v>-0.0509053906673701</v>
       </c>
       <c r="Y20" t="n">
         <v>0.4631039500236511</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.375</v>
+        <v>45590.66666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -605,56 +605,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4512877939529675</v>
+        <v>0.3254437869822485</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3057110862262038</v>
+        <v>0.2840236686390532</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2430011198208287</v>
+        <v>0.3905325443786982</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05518137776202292</v>
+        <v>0.06691919191919204</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3883452713489532</v>
+        <v>0.4918189644813538</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3590740859508514</v>
+        <v>0.2627890408039093</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2525806725025177</v>
+        <v>0.2453919500112534</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.06294252260401423</v>
+        <v>0.1663751774991053</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.06294252260401423</v>
+        <v>0.1663751774991053</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3883452713489532</v>
+        <v>0.4918189644813538</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -662,26 +662,26 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.021523049538582</v>
+        <v>5.193119500154384</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>x88gL4RQ</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.46875</v>
+        <v>45591.375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -701,58 +701,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.33</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7077140835102618</v>
+        <v>0.2705667276051188</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1981599433828733</v>
+        <v>0.2559414990859232</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09412597310686482</v>
+        <v>0.473491773308958</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06240601503759402</v>
+        <v>0.05598455598455598</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7302388548851013</v>
+        <v>0.2011553347110748</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1859939247369766</v>
+        <v>0.4505351781845093</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08376725763082504</v>
+        <v>0.3483094871044159</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.02252477137483955</v>
+        <v>0.1945936790985861</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.02252477137483955</v>
+        <v>0.1945936790985861</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7302388548851013</v>
+        <v>0.4505351781845093</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.33</v>
+        <v>3.7</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -760,26 +758,26 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>7.562014020122588</v>
+        <v>4.75720374427369</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>dhkQFrkl</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45585.5625</v>
+        <v>45591.46875</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>villarreal</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -799,56 +797,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.4616238209728131</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2957277603107084</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.2426484187164787</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.05671513445903686</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5909121632575989</v>
+        <v>0.602658748626709</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2742571830749512</v>
+        <v>0.3123294413089752</v>
       </c>
       <c r="S4" t="n">
-        <v>0.13483065366745</v>
+        <v>0.08501177281141281</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.0645963737839147</v>
+        <v>0.1410349276538959</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0645963737839147</v>
+        <v>0.1410349276538959</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5909121632575989</v>
+        <v>0.602658748626709</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -856,26 +854,26 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>6.119211588539779</v>
+        <v>6.363477469260249</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>8Sp1FEw8</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45585.66666666666</v>
+        <v>45591.5625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -895,56 +893,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J5" t="n">
-        <v>5.75</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>2.1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7201565557729942</v>
+        <v>0.2763157894736842</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1628180039138943</v>
+        <v>0.2763157894736842</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1170254403131116</v>
+        <v>0.4473684210526316</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06814381270902992</v>
+        <v>0.06442577030812324</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7480214834213257</v>
+        <v>0.2109206914901733</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1728741079568863</v>
+        <v>0.6664647459983826</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07910440862178802</v>
+        <v>0.1226145178079605</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.02786492764833148</v>
+        <v>0.3901489565246983</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02786492764833148</v>
+        <v>0.3901489565246983</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.7480214834213257</v>
+        <v>0.6664647459983826</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -952,26 +950,26 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>7.746162652321457</v>
+        <v>7.037205391742994</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>QqTA4cPk</t>
+          <t>4zlpJdvq</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45586.66666666666</v>
+        <v>45591.66666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>real madrid</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -991,64 +989,1506 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>5.25</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5607678983833718</v>
+        <v>0.486111111111111</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2576501154734411</v>
+        <v>0.2430555555555555</v>
       </c>
       <c r="N6" t="n">
-        <v>0.181581986143187</v>
+        <v>0.2708333333333333</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04898175486410783</v>
+        <v>0.05494505494505519</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4536928236484528</v>
+        <v>0.2025911659002304</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3383599817752838</v>
+        <v>0.3295104801654816</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2079471498727798</v>
+        <v>0.4678983986377716</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1070750747349191</v>
+        <v>0.1970650653044383</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1070750747349191</v>
+        <v>0.1970650653044383</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4536928236484528</v>
+        <v>0.4678983986377716</v>
       </c>
       <c r="Z6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>4.940542096865286</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45592.41666666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>148</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3055305530553056</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2914291429142915</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.4030403040304031</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.05580486774721494</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.6026957035064697</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.2977534234523773</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.09955088794231415</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.2971651504511642</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.2971651504511642</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.6026957035064697</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>6.363867676065133</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.51041666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>148</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.4266958424507659</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2844638949671772</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2888402625820569</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.06526806526806528</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4333268105983734</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.5103562474250793</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.05631694570183754</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.2258923524579021</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.2258923524579021</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.5103562474250793</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>5.388854785873709</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.60416666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>148</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.3028768233387358</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2888978930307942</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.40822528363047</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0650555615492503</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2445476204156876</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.6924266219139099</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.06302576512098312</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.4035287288831158</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.4035287288831158</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.6924266219139099</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>7.311337000758297</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.70833333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>148</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2592592592592593</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2074074074074074</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.6056564450263977</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.365974634885788</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.02836891636252403</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.07232311169306438</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.07232311169306438</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.6056564450263977</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>6.395130164160257</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45593.70833333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>148</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3156822810590631</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.3054989816700611</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3788187372708758</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05591397849462365</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4351615011692047</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2708008885383606</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2940376102924347</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.1194792201101416</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1194792201101416</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4351615011692047</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.594872993198555</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>02cHDDPH</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45597.70833333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>148</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.3890274314214464</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.3177057356608479</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2932668329177058</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.04918890633176343</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.6766632795333862</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.1422071754932404</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.1811295747756958</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.2876358481119399</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.2876358481119399</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.6766632795333862</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>7.144891770671991</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4z48FZf5</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.41666666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>148</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="J13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5560235888795282</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2864363942712721</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1575400168491996</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.05793226381461691</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.6004839539527893</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.383495420217514</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.01602063328027725</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.04446036507326112</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.04446036507326112</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.6004839539527893</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA13" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AB6" t="n">
-        <v>4.143822072517845</v>
+      <c r="AB13" t="n">
+        <v>6.340513798792856</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>dA00HeQh</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.51041666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>148</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.620779043590968</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.243536394024149</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.135684562384883</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.05286217050922937</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.7548649311065674</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.2029409557580948</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.04219407588243484</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.1340858875155994</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.1340858875155994</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.7548649311065674</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.970623495265467</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YFePBifU</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.60416666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>148</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5430668211664735</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2568559289300889</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2000772499034376</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.05222515748831524</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.8779269456863403</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.1048725694417953</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.01720048673450947</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.3348601245198668</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.3348601245198668</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.8779269456863403</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>9.2700360714284</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zHmSVfun</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45598.70833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>148</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1720368389470114</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2252863367163244</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.6026768243366641</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.05685609507265554</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1793296337127686</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3234343230724335</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4972361028194427</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>-0.1054407215172214</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.1054407215172214</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4972361028194427</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>4.693644480863084</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QXtsC0lD</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45599.41666666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>148</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>13</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.7803121248499399</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.1464585834333733</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.07322929171668667</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.05044136191677184</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.8148378133773804</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.1376583725214005</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.04750380292534828</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.03452568852744042</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.03452568852744042</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.8148378133773804</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.603877531594581</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>UaS8aGMt</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45599.51041666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>148</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>17</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.8267477203647416</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.1178115501519757</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.05544072948328267</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06101651186790513</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.8382400870323181</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.117514006793499</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.0442458763718605</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.01149236666757647</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.01149236666757647</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.8382400870323181</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>8.850982284445188</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>rsizUY9b</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45599.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>148</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.3409090909090909</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.3181818181818181</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.3409090909090909</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.04761904761904767</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.380384236574173</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.5099872350692749</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1096285358071327</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.1918054168874568</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.1918054168874568</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.5099872350692749</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>5.384958382117203</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>U5mYDMJ0</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45599.70833333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>148</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.5446293494704992</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.264750378214826</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.1906202723146747</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.04920634920634925</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.5452058911323547</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.1867503374814987</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.2680437564849854</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.0005765416618555008</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.0005765416618555008</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.5452058911323547</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>5.756832390195117</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zeCiJHet</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45600.70833333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>148</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.4855025490986177</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2958531158569702</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.2186443350444121</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.05626739503760292</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.531012237071991</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3763866126537323</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.09260117262601852</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.04550968797337324</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.04550968797337324</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.531012237071991</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>5.606961508829145</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB21"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
@@ -614,16 +614,16 @@
         <v>2.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3254437869822485</v>
+        <v>0.3239263803680982</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2840236686390532</v>
+        <v>0.2846625766871166</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3905325443786982</v>
+        <v>0.3914110429447853</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06691919191919204</v>
+        <v>0.0645245559038663</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -642,19 +642,19 @@
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1663751774991053</v>
+        <v>0.1678925841132556</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1663751774991053</v>
+        <v>0.1678925841132556</v>
       </c>
       <c r="Y2" t="n">
         <v>0.4918189644813538</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -704,22 +704,22 @@
         <v>3.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2705667276051188</v>
+        <v>0.2714932126696832</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2559414990859232</v>
+        <v>0.253393665158371</v>
       </c>
       <c r="N3" t="n">
-        <v>0.473491773308958</v>
+        <v>0.4751131221719457</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05598455598455598</v>
+        <v>0.05238095238095242</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -738,19 +738,19 @@
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1945936790985861</v>
+        <v>0.1971415130261382</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1945936790985861</v>
+        <v>0.1971415130261382</v>
       </c>
       <c r="Y3" t="n">
         <v>0.4505351781845093</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -803,19 +803,19 @@
         <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4616238209728131</v>
+        <v>0.4644412191582004</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2957277603107084</v>
+        <v>0.297532656023222</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2426484187164787</v>
+        <v>0.2380261248185777</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05671513445903686</v>
+        <v>0.05030487804878048</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -834,13 +834,13 @@
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1410349276538959</v>
+        <v>0.1382175294685086</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1410349276538959</v>
+        <v>0.1382175294685086</v>
       </c>
       <c r="Y4" t="n">
         <v>0.602658748626709</v>
@@ -893,25 +893,25 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2763157894736842</v>
+        <v>0.3266613290632506</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2763157894736842</v>
+        <v>0.2786228983186549</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.3947157726180944</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06442577030812324</v>
+        <v>0.05561189993238691</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -930,13 +930,13 @@
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3901489565246983</v>
+        <v>0.3878418476797277</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3901489565246983</v>
+        <v>0.3878418476797277</v>
       </c>
       <c r="Y5" t="n">
         <v>0.6664647459983826</v>
@@ -989,56 +989,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="L6" t="n">
-        <v>0.486111111111111</v>
+        <v>0.4754683318465656</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2430555555555555</v>
+        <v>0.231935771632471</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2708333333333333</v>
+        <v>0.2925958965209635</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05494505494505519</v>
+        <v>0.05159474671669795</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2025911659002304</v>
+        <v>0.2054202705621719</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3295104801654816</v>
+        <v>0.3581646382808685</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4678983986377716</v>
+        <v>0.4364151060581207</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1970650653044383</v>
+        <v>0.1438192095371573</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1970650653044383</v>
+        <v>0.1438192095371573</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4678983986377716</v>
+        <v>0.4364151060581207</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>4.940542096865286</v>
+        <v>4.608109815005506</v>
       </c>
     </row>
     <row r="7">
@@ -1085,56 +1085,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
         <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3055305530553056</v>
+        <v>0.2929936305732484</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2914291429142915</v>
+        <v>0.2929936305732484</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4030403040304031</v>
+        <v>0.4140127388535031</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05580486774721494</v>
+        <v>0.05016722408026775</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6026957035064697</v>
+        <v>0.6555163264274597</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2977534234523773</v>
+        <v>0.2581678628921509</v>
       </c>
       <c r="S7" t="n">
-        <v>0.09955088794231415</v>
+        <v>0.08631584793329239</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2971651504511642</v>
+        <v>0.3625226958542113</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2971651504511642</v>
+        <v>0.3625226958542113</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6026957035064697</v>
+        <v>0.6555163264274597</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>6.363867676065133</v>
+        <v>6.921600961503934</v>
       </c>
     </row>
     <row r="8">
@@ -1184,53 +1184,53 @@
         <v>2.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4266958424507659</v>
+        <v>0.4308880308880308</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2844638949671772</v>
+        <v>0.3057915057915058</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2888402625820569</v>
+        <v>0.2633204633204633</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06526806526806528</v>
+        <v>0.05490387748452275</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4333268105983734</v>
+        <v>0.4426423907279968</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5103562474250793</v>
+        <v>0.4998300075531006</v>
       </c>
       <c r="S8" t="n">
-        <v>0.05631694570183754</v>
+        <v>0.05752763897180557</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2258923524579021</v>
+        <v>0.1940385017615948</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2258923524579021</v>
+        <v>0.1940385017615948</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5103562474250793</v>
+        <v>0.4998300075531006</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.388854785873709</v>
+        <v>5.277708153697536</v>
       </c>
     </row>
     <row r="9">
@@ -1277,25 +1277,25 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3028768233387358</v>
+        <v>0.3165610142630745</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2888978930307942</v>
+        <v>0.2793185419968304</v>
       </c>
       <c r="N9" t="n">
-        <v>0.40822528363047</v>
+        <v>0.4041204437400951</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0650555615492503</v>
+        <v>0.05298289528577382</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1314,19 +1314,19 @@
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4035287288831158</v>
+        <v>0.4131080799170795</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4035287288831158</v>
+        <v>0.4131080799170795</v>
       </c>
       <c r="Y9" t="n">
         <v>0.6924266219139099</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1379,19 +1379,19 @@
         <v>3.6</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5446293494704992</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2592592592592593</v>
+        <v>0.264750378214826</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2074074074074074</v>
+        <v>0.1906202723146747</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.04920634920634925</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
@@ -1410,13 +1410,13 @@
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.07232311169306438</v>
+        <v>0.06102709555589847</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.07232311169306438</v>
+        <v>0.06102709555589847</v>
       </c>
       <c r="Y10" t="n">
         <v>0.6056564450263977</v>
@@ -1469,25 +1469,25 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="J11" t="n">
         <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3156822810590631</v>
+        <v>0.3254425689584192</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3054989816700611</v>
+        <v>0.3044462741869082</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3788187372708758</v>
+        <v>0.3701111568546728</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05591397849462365</v>
+        <v>0.05956509411328481</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1506,19 +1506,19 @@
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1194792201101416</v>
+        <v>0.1097189322107855</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1194792201101416</v>
+        <v>0.1097189322107855</v>
       </c>
       <c r="Y11" t="n">
         <v>0.4351615011692047</v>
       </c>
       <c r="Z11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1527,968 +1527,6 @@
       </c>
       <c r="AB11" t="n">
         <v>4.594872993198555</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>02cHDDPH</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45597.70833333334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>alaves</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>mallorca</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>148</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.3890274314214464</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.3177057356608479</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.2932668329177058</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.04918890633176343</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.6766632795333862</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.1422071754932404</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.1811295747756958</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>0.2876358481119399</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0.2876358481119399</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.6766632795333862</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>7.144891770671991</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>4z48FZf5</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45598.41666666666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>osasuna</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>valladolid</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>148</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.5560235888795282</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.2864363942712721</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.1575400168491996</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.05793226381461691</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.6004839539527893</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.383495420217514</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.01602063328027725</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>0.04446036507326112</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.04446036507326112</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.6004839539527893</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>6.340513798792856</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dA00HeQh</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45598.51041666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>girona</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>leganes</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>148</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K14" t="n">
-        <v>7</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.620779043590968</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.243536394024149</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.135684562384883</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.05286217050922937</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.7548649311065674</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.2029409557580948</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.04219407588243484</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>0.1340858875155994</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.1340858875155994</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.7548649311065674</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>7.970623495265467</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YFePBifU</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45598.60416666666</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>villarreal</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>rayo vallecano</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>148</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.5430668211664735</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2568559289300889</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.2000772499034376</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.05222515748831524</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.8779269456863403</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.1048725694417953</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.01720048673450947</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>0.3348601245198668</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.3348601245198668</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.8779269456863403</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>9.2700360714284</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zHmSVfun</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45598.70833333334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>valencia</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>real madrid</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>148</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.1720368389470114</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.2252863367163244</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.6026768243366641</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.05685609507265554</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.1793296337127686</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.3234343230724335</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.4972361028194427</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>-0.1054407215172214</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-0.1054407215172214</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.4972361028194427</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>4.693644480863084</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QXtsC0lD</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45599.41666666666</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>atl  madrid</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>las palmas</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>148</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="J17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K17" t="n">
-        <v>13</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.7803121248499399</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.1464585834333733</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.07322929171668667</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.05044136191677184</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.8148378133773804</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.1376583725214005</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.04750380292534828</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>0.03452568852744042</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.03452568852744042</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.8148378133773804</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB17" t="n">
-        <v>8.603877531594581</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>UaS8aGMt</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45599.51041666666</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>barcelona</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>espanyol</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>148</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="J18" t="n">
-        <v>8</v>
-      </c>
-      <c r="K18" t="n">
-        <v>17</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.8267477203647416</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.1178115501519757</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.05544072948328267</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.06101651186790513</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.8382400870323181</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.117514006793499</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.0442458763718605</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="n">
-        <v>0.01149236666757647</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.01149236666757647</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0.8382400870323181</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB18" t="n">
-        <v>8.850982284445188</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>rsizUY9b</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45599.60416666666</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>sevilla</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>real sociedad</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>148</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.3409090909090909</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.3181818181818181</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.3409090909090909</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.04761904761904767</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.380384236574173</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.5099872350692749</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.1096285358071327</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="n">
-        <v>0.1918054168874568</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0.1918054168874568</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.5099872350692749</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB19" t="n">
-        <v>5.384958382117203</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45599.70833333334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ath bilbao</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>betis</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>148</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>5</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.5446293494704992</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.264750378214826</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.1906202723146747</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.04920634920634925</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.5452058911323547</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.1867503374814987</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0.2680437564849854</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.0005765416618555008</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0.0005765416618555008</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0.5452058911323547</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB20" t="n">
-        <v>5.756832390195117</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>zeCiJHet</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45600.70833333334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>celta vigo</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>getafe</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>148</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1481</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>laliga</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.4855025490986177</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.2958531158569702</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.2186443350444121</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.05626739503760292</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.531012237071991</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.3763866126537323</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.09260117262601852</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="n">
-        <v>0.04550968797337324</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0.04550968797337324</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0.531012237071991</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB21" t="n">
-        <v>5.606961508829145</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vymauDyP</t>
+          <t>02cHDDPH</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45590.66666666666</v>
+        <v>45597.70833333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -605,56 +605,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3239263803680982</v>
+        <v>0.3835842441740565</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2846625766871166</v>
+        <v>0.3132604660754795</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3914110429447853</v>
+        <v>0.303155289750464</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0645245559038663</v>
+        <v>0.06407724380074598</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4918189644813538</v>
+        <v>0.3737311065196991</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2627890408039093</v>
+        <v>0.5810516476631165</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2453919500112534</v>
+        <v>0.04521721228957176</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1678925841132556</v>
+        <v>0.2677911815876369</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1678925841132556</v>
+        <v>0.2677911815876369</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4918189644813538</v>
+        <v>0.5810516476631165</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -662,26 +662,26 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5.193119500154384</v>
+        <v>6.425090336077273</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>x88gL4RQ</t>
+          <t>4z48FZf5</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45591.375</v>
+        <v>45598.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>valladolid</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>villarreal</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -701,56 +701,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2714932126696832</v>
+        <v>0.5915065722952477</v>
       </c>
       <c r="M3" t="n">
-        <v>0.253393665158371</v>
+        <v>0.262891809908999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4751131221719457</v>
+        <v>0.1456016177957533</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05238095238095242</v>
+        <v>0.05662393162393164</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2011553347110748</v>
+        <v>0.6523409485816956</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4505351781845093</v>
+        <v>0.278348445892334</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3483094871044159</v>
+        <v>0.06931064277887344</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1971415130261382</v>
+        <v>0.06083437628644783</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1971415130261382</v>
+        <v>0.06083437628644783</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4505351781845093</v>
+        <v>0.6523409485816956</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>1.6</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -758,26 +758,26 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>4.75720374427369</v>
+        <v>7.21338549062992</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dhkQFrkl</t>
+          <t>dA00HeQh</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45591.46875</v>
+        <v>45598.51041666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rayo vallecano</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -797,56 +797,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>6.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4644412191582004</v>
+        <v>0.5850690381465014</v>
       </c>
       <c r="M4" t="n">
-        <v>0.297532656023222</v>
+        <v>0.2632810671659256</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2380261248185777</v>
+        <v>0.1516498946875731</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05030487804878048</v>
+        <v>0.05506172839506163</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.602658748626709</v>
+        <v>0.7645300626754761</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3123294413089752</v>
+        <v>0.1337324231863022</v>
       </c>
       <c r="S4" t="n">
-        <v>0.08501177281141281</v>
+        <v>0.1017375588417053</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1382175294685086</v>
+        <v>0.1794610245289747</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1382175294685086</v>
+        <v>0.1794610245289747</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.602658748626709</v>
+        <v>0.7645300626754761</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -854,26 +854,26 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>6.363477469260249</v>
+        <v>8.45393819481043</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Sp1FEw8</t>
+          <t>YFePBifU</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45591.5625</v>
+        <v>45598.60416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -893,56 +893,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.9</v>
+        <v>1.73</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4</v>
+        <v>4.75</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3266613290632506</v>
+        <v>0.5477819635580841</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2786228983186549</v>
+        <v>0.2527100791881294</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3947157726180944</v>
+        <v>0.1995079572537864</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05561189993238691</v>
+        <v>0.05522766453706529</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2109206914901733</v>
+        <v>0.5801128149032593</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6664647459983826</v>
+        <v>0.3120748400688171</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1226145178079605</v>
+        <v>0.107812374830246</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3878418476797277</v>
+        <v>0.03233085134517522</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3878418476797277</v>
+        <v>0.03233085134517522</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.6664647459983826</v>
+        <v>0.5801128149032593</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.4</v>
+        <v>1.73</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -950,26 +950,26 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>7.037205391742994</v>
+        <v>6.414709012288224</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4zlpJdvq</t>
+          <t>zHmSVfun</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45591.66666666666</v>
+        <v>45598.70833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>real madrid</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>barcelona</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -989,56 +989,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="J6" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.25</v>
+        <v>1.48</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4754683318465656</v>
+        <v>0.1462771798813969</v>
       </c>
       <c r="M6" t="n">
-        <v>0.231935771632471</v>
+        <v>0.2112892598286844</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2925958965209635</v>
+        <v>0.6424335602899187</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05159474671669795</v>
+        <v>0.05174405174405172</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2054202705621719</v>
+        <v>0.1213208362460136</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3581646382808685</v>
+        <v>0.3430830240249634</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4364151060581207</v>
+        <v>0.5355961322784424</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1438192095371573</v>
+        <v>-0.1068374280114763</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1438192095371573</v>
+        <v>-0.1068374280114763</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4364151060581207</v>
+        <v>0.5355961322784424</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.25</v>
+        <v>1.48</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1046,26 +1046,26 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>4.608109815005506</v>
+        <v>5.331769530089735</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>02sgHz9e</t>
+          <t>QXtsC0lD</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45592.41666666666</v>
+        <v>45599.41666666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1085,56 +1085,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>1.27</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2929936305732484</v>
+        <v>0.7470119521912351</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2929936305732484</v>
+        <v>0.1581175298804781</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4140127388535031</v>
+        <v>0.09487051792828687</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05016722408026775</v>
+        <v>0.05406824146981615</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6555163264274597</v>
+        <v>0.7349386811256409</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2581678628921509</v>
+        <v>0.2185675650835037</v>
       </c>
       <c r="S7" t="n">
-        <v>0.08631584793329239</v>
+        <v>0.04649371281266212</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3625226958542113</v>
+        <v>-0.01207327106559419</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3625226958542113</v>
+        <v>-0.01207327106559419</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6555163264274597</v>
+        <v>0.7349386811256409</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.25</v>
+        <v>1.27</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1142,26 +1142,26 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>6.921600961503934</v>
+        <v>8.126725802604541</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>naHJ2yf2</t>
+          <t>UaS8aGMt</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45592.51041666666</v>
+        <v>45599.51041666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1181,56 +1181,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.2</v>
+        <v>1.14</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>17</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4308880308880308</v>
+        <v>0.8267477203647416</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3057915057915058</v>
+        <v>0.1178115501519757</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2633204633204633</v>
+        <v>0.05544072948328267</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05490387748452275</v>
+        <v>0.06101651186790513</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4426423907279968</v>
+        <v>0.7846553921699524</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4998300075531006</v>
+        <v>0.0993356853723526</v>
       </c>
       <c r="S8" t="n">
-        <v>0.05752763897180557</v>
+        <v>0.1160089671611786</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1940385017615948</v>
+        <v>-0.04209232819478925</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1940385017615948</v>
+        <v>-0.04209232819478925</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4998300075531006</v>
+        <v>0.7846553921699524</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.1</v>
+        <v>1.14</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1238,26 +1238,26 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.277708153697536</v>
+        <v>8.676477895997717</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>842EOIGL</t>
+          <t>rsizUY9b</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45592.60416666666</v>
+        <v>45599.60416666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1277,56 +1277,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3165610142630745</v>
+        <v>0.3044462741869082</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2793185419968304</v>
+        <v>0.3254425689584192</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4041204437400951</v>
+        <v>0.3701111568546728</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05298289528577382</v>
+        <v>0.05956509411328481</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2445476204156876</v>
+        <v>0.2442575842142105</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6924266219139099</v>
+        <v>0.5261193513870239</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06302576512098312</v>
+        <v>0.2296231091022491</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4131080799170795</v>
+        <v>0.2006767824286048</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4131080799170795</v>
+        <v>0.2006767824286048</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.6924266219139099</v>
+        <v>0.5261193513870239</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1334,26 +1334,26 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>7.311337000758297</v>
+        <v>5.817665905974482</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>jiAoNQdE</t>
+          <t>U5mYDMJ0</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45592.70833333334</v>
+        <v>45599.70833333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>osasuna</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1373,56 +1373,58 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
         <v>3.6</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5446293494704992</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="M10" t="n">
-        <v>0.264750378214826</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1906202723146747</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04920634920634925</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6056564450263977</v>
+        <v>0.3944540321826935</v>
       </c>
       <c r="R10" t="n">
-        <v>0.365974634885788</v>
+        <v>0.378147304058075</v>
       </c>
       <c r="S10" t="n">
-        <v>0.02836891636252403</v>
+        <v>0.2273987084627151</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
       <c r="V10" t="n">
-        <v>0.06102709555589847</v>
+        <v>-0.1318617572909907</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.06102709555589847</v>
+        <v>-0.1318617572909907</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.6056564450263977</v>
+        <v>0.3944540321826935</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1430,26 +1432,26 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>6.395130164160257</v>
+        <v>3.632707948525225</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E595Qvn9</t>
+          <t>zeCiJHet</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45593.70833333334</v>
+        <v>45600.70833333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1469,64 +1471,1026 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>2.55</v>
+        <v>4.33</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3254425689584192</v>
+        <v>0.4855025490986177</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3044462741869082</v>
+        <v>0.2958531158569702</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3701111568546728</v>
+        <v>0.2186443350444121</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05956509411328481</v>
+        <v>0.05626739503760292</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4351615011692047</v>
+        <v>0.1505251973867416</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2708008885383606</v>
+        <v>0.7217757701873779</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2940376102924347</v>
+        <v>0.1276990473270416</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1097189322107855</v>
+        <v>0.4259226543304078</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1097189322107855</v>
+        <v>0.4259226543304078</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4351615011692047</v>
+        <v>0.7217757701873779</v>
       </c>
       <c r="Z11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>7.981174383545296</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rPc4X7Gj</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45604.70833333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>rayo vallecano</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>148</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5352112676056339</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2676056338028169</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1971830985915493</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.06766917293233066</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.6666247844696045</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.2667141556739807</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.06666098535060883</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1314135168639706</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1314135168639706</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.6666247844696045</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>7.371331752884953</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>nucZxUhT</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45605.41666666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>osasuna</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>148</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>17</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.8130636786007106</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.13241322765783</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.05452309374145942</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.07887365472504793</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.7465993165969849</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.1827520281076431</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.07064859569072723</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.06646436200372574</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.06646436200372574</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.7465993165969849</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>8.255665521785735</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bXuieB8c</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45605.51041666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>villarreal</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>148</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5682242990654205</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.234392523364486</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.1973831775700934</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06658692185007986</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4053020477294922</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.486274242401123</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1084236800670624</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.2518817190366371</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.2518817190366371</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.486274242401123</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>5.377070950749975</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>jFGHcfig</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45605.60416666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>148</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>2.9</v>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="J15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3235973944105905</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.3351544442109687</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.3412481613784409</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06560680698611732</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3307887315750122</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.4629528820514679</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2062583863735199</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.1277984378404992</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.1277984378404992</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4629528820514679</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA15" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="AB11" t="n">
-        <v>4.594872993198555</v>
+      <c r="AB15" t="n">
+        <v>5.119190523752853</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>CMriQj9N</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45605.70833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>getafe</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>148</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4063908234330192</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.3015157722244981</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.2920934043424825</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06986325385694259</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.43308025598526</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.4003770351409912</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.1665426641702652</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.02668943255224077</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.02668943255224077</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.43308025598526</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>4.788868216221041</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4duqSCvB</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45606.41666666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>celta vigo</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>148</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.4926019487549621</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2674124864669794</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2399855647780585</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06844033159822627</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.7504268884658813</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.1278888881206512</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.1216841861605644</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.2578249397109192</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.2578249397109192</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.7504268884658813</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.297989633806404</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Ia5ItCg4</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45606.51041666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>148</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2771706735545401</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.3039936419630439</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.418835684482416</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06114273666455827</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.372621476650238</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3085712790489197</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.3188072144985199</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.09545080309569798</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.09545080309569798</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.372621476650238</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>4.120333636896182</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>UwPNKUWp</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45606.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>leganes</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>sevilla</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>148</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.3355537052456287</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.3030807660283097</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.3613655287260616</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.06433888691953205</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.4044583439826965</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.4087279736995697</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.186813697218895</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.10564720767126</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.10564720767126</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4087279736995697</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>4.519588171659614</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MXB9rYOi</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45606.60416666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>148</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.2074674181049665</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.3011623811201127</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.4913702007749207</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.07111865685719687</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1360205411911011</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.707152247428894</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.1568271517753601</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.4059898663087814</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.4059898663087814</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.707152247428894</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>7.819471968393699</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QP8QvjOG</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45606.70833333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>148</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.253366100169603</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2343636426568828</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.5122702571735143</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0667183577019641</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.286826103925705</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.481096088886261</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2320778071880341</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.2467324462293782</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.2467324462293782</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.481096088886261</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>5.319812522448685</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB9"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>02cHDDPH</t>
+          <t>rPc4X7Gj</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45597.70833333334</v>
+        <v>45604.70833333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>alaves</t>
+          <t>rayo vallecano</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>las palmas</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -605,56 +605,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4041204437400951</v>
+        <v>0.5405405405405405</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3165610142630745</v>
+        <v>0.2702702702702702</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2793185419968304</v>
+        <v>0.1891891891891892</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05298289528577382</v>
+        <v>0.05714285714285716</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3781879246234894</v>
+        <v>0.6303389668464661</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4276520907878876</v>
+        <v>0.245873898267746</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1941599696874619</v>
+        <v>0.1237871721386909</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1110910765248131</v>
+        <v>0.0897984263059256</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1110910765248131</v>
+        <v>0.0897984263059256</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4276520907878876</v>
+        <v>0.6303389668464661</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -662,26 +662,26 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.728845235660646</v>
+        <v>7.133388347319908</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4z48FZf5</t>
+          <t>nucZxUhT</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45598.41666666666</v>
+        <v>45605.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>real madrid</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>osasuna</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>valladolid</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -701,56 +701,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="K3" t="n">
-        <v>6.25</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5922653348700219</v>
+        <v>0.7935216082037927</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2561147394032527</v>
+        <v>0.1440546919508424</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1516199257267256</v>
+        <v>0.06242369984536501</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05527027027027009</v>
+        <v>0.06797044763146465</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6896823048591614</v>
+        <v>0.7477745413780212</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2511809170246124</v>
+        <v>0.1773705929517746</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05913680791854858</v>
+        <v>0.07485481351613998</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.09741696998913951</v>
+        <v>-0.04574706682577145</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.09741696998913951</v>
+        <v>-0.04574706682577145</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6896823048591614</v>
+        <v>0.7477745413780212</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.6</v>
+        <v>1.18</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -758,26 +758,26 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>7.626294718784225</v>
+        <v>7.94466924918703</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dA00HeQh</t>
+          <t>bXuieB8c</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.51041666666</v>
+        <v>45605.51041666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>villarreal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>alaves</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -797,56 +797,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.557163531114327</v>
+        <v>0.5835764902042518</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2706222865412445</v>
+        <v>0.236348478532722</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1722141823444284</v>
+        <v>0.1800750312630263</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05576776165011466</v>
+        <v>0.05776014109347427</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7702642679214478</v>
+        <v>0.5775689482688904</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1505039632320404</v>
+        <v>0.279651403427124</v>
       </c>
       <c r="S4" t="n">
-        <v>0.07923176884651184</v>
+        <v>0.142779678106308</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2131007368071207</v>
+        <v>-0.00600754193536146</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2131007368071207</v>
+        <v>-0.00600754193536146</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.7702642679214478</v>
+        <v>0.5775689482688904</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -854,26 +854,26 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>8.517345272062773</v>
+        <v>6.468217403907484</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
+          <t>jFGHcfig</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45599.41666666666</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>espanyol</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>las palmas</t>
+          <t>valencia</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -893,56 +893,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.27</v>
+        <v>2.63</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="K5" t="n">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7433005150942166</v>
+        <v>0.3592517652888467</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1573319423616092</v>
+        <v>0.3258041871412644</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09936754254417422</v>
+        <v>0.3149440475698889</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05933139936455301</v>
+        <v>0.05838905642235925</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5737866759300232</v>
+        <v>0.5252802968025208</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3702729642391205</v>
+        <v>0.3036795258522034</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05594033747911453</v>
+        <v>0.1710400879383087</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.1695138391641934</v>
+        <v>0.1660285315136741</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1695138391641934</v>
+        <v>0.1660285315136741</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5737866759300232</v>
+        <v>0.5252802968025208</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.27</v>
+        <v>2.63</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -950,26 +950,26 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>5.407540576129641</v>
+        <v>5.944465669057267</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45599.51041666666</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -989,56 +989,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.13</v>
+        <v>2.88</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>19</v>
+        <v>2.55</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8438610343466245</v>
+        <v>0.3300970873786407</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1059514409790762</v>
+        <v>0.2970873786407767</v>
       </c>
       <c r="N6" t="n">
-        <v>0.05018752467429925</v>
+        <v>0.3728155339805825</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04869844227086895</v>
+        <v>0.0518790849673203</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7338781356811523</v>
+        <v>0.279819667339325</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1434898376464844</v>
+        <v>0.3650146722793579</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1226320117712021</v>
+        <v>0.3551656901836395</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1099828986654722</v>
+        <v>0.06792729363858124</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1099828986654722</v>
+        <v>0.06792729363858124</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.7338781356811523</v>
+        <v>0.3650146722793579</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.13</v>
+        <v>3.2</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1046,26 +1046,26 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>7.506920090996264</v>
+        <v>4.130779702332097</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45599.60416666666</v>
+        <v>45606.41666666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1085,56 +1085,58 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.55</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3148148148148148</v>
+        <v>0.4822695035460994</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3148148148148148</v>
+        <v>0.2765957446808511</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3703703703703704</v>
+        <v>0.2411347517730497</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05882352941176472</v>
+        <v>0.06334841628959276</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1991524398326874</v>
+        <v>0.4491502046585083</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5480133891105652</v>
+        <v>0.3417275846004486</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2528342008590698</v>
+        <v>0.2091221958398819</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
       <c r="V7" t="n">
-        <v>0.2331985742957504</v>
+        <v>-0.03311929888759108</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2331985742957504</v>
+        <v>-0.03311929888759108</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5480133891105652</v>
+        <v>0.4491502046585083</v>
       </c>
       <c r="Z7" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1142,26 +1144,26 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>6.059763438544935</v>
+        <v>4.70811765009296</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>U5mYDMJ0</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45599.70833333334</v>
+        <v>45606.51041666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1181,58 +1183,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.85</v>
+        <v>3.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>2.35</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5088777796931563</v>
+        <v>0.2882865057380293</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2615066367867609</v>
+        <v>0.3068856351404828</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2296155835200828</v>
+        <v>0.4048278591214879</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06222075734270849</v>
+        <v>0.05114286308521043</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3262371718883514</v>
+        <v>0.3025104105472565</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4136055111885071</v>
+        <v>0.3739364445209503</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2601573765277863</v>
+        <v>0.3235531151294708</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1520988744017461</v>
+        <v>0.06705080938046754</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1520988744017461</v>
+        <v>0.06705080938046754</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4136055111885071</v>
+        <v>0.3739364445209503</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1240,26 +1240,26 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>4.573522480442774</v>
+        <v>4.231745166142808</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zeCiJHet</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45600.70833333334</v>
+        <v>45606.60416666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1279,56 +1279,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4855025490986177</v>
+        <v>0.3875</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2958531158569702</v>
+        <v>0.30625</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2186443350444121</v>
+        <v>0.30625</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05626739503760292</v>
+        <v>0.05332455562870297</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.168166920542717</v>
+        <v>0.3117114901542664</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7154298424720764</v>
+        <v>0.3761576414108276</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1164032220840454</v>
+        <v>0.3121309876441956</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4195767266151063</v>
+        <v>0.06990764141082761</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4195767266151063</v>
+        <v>0.06990764141082761</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.7154298424720764</v>
+        <v>0.3761576414108276</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1336,7 +1336,199 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>7.911003067447991</v>
+        <v>4.256881895497528</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>MXB9rYOi</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45606.60416666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>valladolid</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ath bilbao</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>148</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2001588562351072</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2716441620333598</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.5281969817315331</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.05179615705931484</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.2408535778522491</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.340700089931488</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.418446272611618</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>-0.109750709119915</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.109750709119915</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.418446272611618</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.493430441874344</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>QP8QvjOG</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45606.70833333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>real sociedad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>barcelona</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>148</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.2532040348910872</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2192875590858145</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.5275084060230983</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05316910443931233</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.1872458159923553</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3025525510311127</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.510201632976532</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-0.01730677304656636</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.01730677304656636</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.510201632976532</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>5.577967784331351</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>7.133388347319908</v>
+        <v>7.02978622343648</v>
       </c>
     </row>
     <row r="3">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>7.94466924918703</v>
+        <v>7.829284446384814</v>
       </c>
     </row>
     <row r="4">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>6.468217403907484</v>
+        <v>6.374275923623946</v>
       </c>
     </row>
     <row r="5">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>5.944465669057267</v>
+        <v>5.858130923396344</v>
       </c>
     </row>
     <row r="6">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>4.130779702332097</v>
+        <v>4.070786115887732</v>
       </c>
     </row>
     <row r="7">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.70811765009296</v>
+        <v>4.639739066971805</v>
       </c>
     </row>
     <row r="8">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>4.231745166142808</v>
+        <v>4.170285202714552</v>
       </c>
     </row>
     <row r="9">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4.256881895497528</v>
+        <v>4.195056857518185</v>
       </c>
     </row>
     <row r="10">
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>3.493430441874344</v>
+        <v>3.442693429420341</v>
       </c>
     </row>
     <row r="11">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>5.577967784331351</v>
+        <v>5.496955889103862</v>
       </c>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/predicciones.xlsx
+++ b/data/spain/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,64 +605,64 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5405405405405405</v>
+        <v>0.5114491057997661</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2702702702702702</v>
+        <v>0.2782884840381081</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1891891891891892</v>
+        <v>0.2102624101621261</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05714285714285716</v>
+        <v>0.05688040982158604</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6303389668464661</v>
+        <v>0.4278689274643216</v>
       </c>
       <c r="R2" t="n">
-        <v>0.245873898267746</v>
+        <v>0.3629548310488862</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1237871721386909</v>
+        <v>0.2091762414867922</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.0897984263059256</v>
+        <v>-0.08358017833544445</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0897984263059256</v>
+        <v>-0.08358017833544445</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6303389668464661</v>
+        <v>0.4278689274643216</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>7.02978622343648</v>
+        <v>4.278689274643217</v>
       </c>
     </row>
     <row r="3">
@@ -701,64 +701,64 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="J3" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7935216082037927</v>
+        <v>0.7913043478260869</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1440546919508424</v>
+        <v>0.1356521739130435</v>
       </c>
       <c r="N3" t="n">
-        <v>0.06242369984536501</v>
+        <v>0.07304347826086957</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06797044763146465</v>
+        <v>0.05311355311355315</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7477745413780212</v>
+        <v>0.6756412174164625</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1773705929517746</v>
+        <v>0.2876177085514129</v>
       </c>
       <c r="S3" t="n">
-        <v>0.07485481351613998</v>
+        <v>0.03674107403212467</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.04574706682577145</v>
+        <v>-0.1156631304096244</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.04574706682577145</v>
+        <v>-0.1156631304096244</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7477745413780212</v>
+        <v>0.6756412174164625</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>7.829284446384814</v>
+        <v>6.756412174164625</v>
       </c>
     </row>
     <row r="4">
@@ -803,77 +803,77 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5835764902042518</v>
+        <v>0.5883926183471516</v>
       </c>
       <c r="M4" t="n">
-        <v>0.236348478532722</v>
+        <v>0.2382990104305964</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1800750312630263</v>
+        <v>0.173308371222252</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05776014109347427</v>
+        <v>0.04910213243546568</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5775689482688904</v>
+        <v>0.3760498972198434</v>
       </c>
       <c r="R4" t="n">
-        <v>0.279651403427124</v>
+        <v>0.3622639674720201</v>
       </c>
       <c r="S4" t="n">
-        <v>0.142779678106308</v>
+        <v>0.2616861353081363</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.00600754193536146</v>
+        <v>-0.2123427211273082</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.00600754193536146</v>
+        <v>-0.2123427211273082</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5775689482688904</v>
+        <v>0.3760498972198434</v>
       </c>
       <c r="Z4" t="n">
         <v>1.62</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>6.374275923623946</v>
+        <v>3.760498972198434</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jFGHcfig</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45605.60416666666</v>
+        <v>45605.70833333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>espanyol</t>
+          <t>leganes</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>valencia</t>
+          <t>sevilla</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -893,83 +893,83 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3592517652888467</v>
+        <v>0.3300970873786407</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3258041871412644</v>
+        <v>0.2970873786407767</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3149440475698889</v>
+        <v>0.3728155339805825</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05838905642235925</v>
+        <v>0.0518790849673203</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5252802968025208</v>
+        <v>0.2549275904880438</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3036795258522034</v>
+        <v>0.3827680317442166</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1710400879383087</v>
+        <v>0.3623043777677396</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1660285315136741</v>
+        <v>0.08568065310343997</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1660285315136741</v>
+        <v>0.08568065310343997</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5252802968025208</v>
+        <v>0.3827680317442166</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>5.858130923396344</v>
+        <v>3.827680317442166</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UwPNKUWp</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45605.70833333334</v>
+        <v>45606.41666666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>leganes</t>
+          <t>betis</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>sevilla</t>
+          <t>celta vigo</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -989,83 +989,83 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3300970873786407</v>
+        <v>0.4851944345344275</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2970873786407767</v>
+        <v>0.2782732786300393</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3728155339805825</v>
+        <v>0.2365322868355333</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0518790849673203</v>
+        <v>0.05693815987933637</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.279819667339325</v>
+        <v>0.5124871616120684</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3650146722793579</v>
+        <v>0.2662130224057716</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3551656901836395</v>
+        <v>0.2212998159821599</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.06792729363858124</v>
+        <v>0.02729272707764097</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06792729363858124</v>
+        <v>0.02729272707764097</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3650146722793579</v>
+        <v>0.5124871616120684</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>4.070786115887732</v>
+        <v>5.124871616120684</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4duqSCvB</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45606.41666666666</v>
+        <v>45606.51041666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>betis</t>
+          <t>mallorca</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>celta vigo</t>
+          <t>atl  madrid</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1085,85 +1085,83 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4822695035460994</v>
+        <v>0.2797175362887406</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2765957446808511</v>
+        <v>0.3067869752844252</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2411347517730497</v>
+        <v>0.413495488426834</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06334841628959276</v>
+        <v>0.05148090091576618</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4491502046585083</v>
+        <v>0.2084941196855593</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3417275846004486</v>
+        <v>0.2497989324274281</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2091221958398819</v>
+        <v>0.5417069478870126</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.03311929888759108</v>
+        <v>0.1282114594601785</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.03311929888759108</v>
+        <v>0.1282114594601785</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4491502046585083</v>
+        <v>0.5417069478870126</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.639739066971805</v>
+        <v>5.417069478870125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Ia5ItCg4</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45606.51041666666</v>
+        <v>45606.60416666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mallorca</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>atl  madrid</t>
+          <t>girona</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1183,70 +1181,70 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="J8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K8" t="n">
         <v>3.1</v>
       </c>
-      <c r="K8" t="n">
-        <v>2.35</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.2882865057380293</v>
+        <v>0.3981697037810067</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3068856351404828</v>
+        <v>0.2961387171871237</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4048278591214879</v>
+        <v>0.3056915790318696</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05114286308521043</v>
+        <v>0.05524871238818108</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3025104105472565</v>
+        <v>0.1902676964861811</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3739364445209503</v>
+        <v>0.3783058884736485</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3235531151294708</v>
+        <v>0.4314264150401704</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.06705080938046754</v>
+        <v>0.1257348360083008</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0.06705080938046754</v>
+        <v>0.1257348360083008</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3739364445209503</v>
+        <v>0.4314264150401704</v>
       </c>
       <c r="Z8" t="n">
         <v>3.1</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>4.170285202714552</v>
+        <v>4.314264150401704</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CMriQj9N</t>
+          <t>MXB9rYOi</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1254,12 +1252,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>getafe</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>girona</t>
+          <t>ath bilbao</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1279,83 +1277,83 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.45</v>
+        <v>4.75</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3875</v>
+        <v>0.1985723556132381</v>
       </c>
       <c r="M9" t="n">
-        <v>0.30625</v>
+        <v>0.2774172615184945</v>
       </c>
       <c r="N9" t="n">
-        <v>0.30625</v>
+        <v>0.5240103828682673</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05332455562870297</v>
+        <v>0.06019951840385285</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3117114901542664</v>
+        <v>0.2148935711721427</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3761576414108276</v>
+        <v>0.3105838141353662</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3121309876441956</v>
+        <v>0.4745226146924911</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.06990764141082761</v>
+        <v>-0.04948776817577621</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.06990764141082761</v>
+        <v>-0.04948776817577621</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3761576414108276</v>
+        <v>0.4745226146924911</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4.195056857518185</v>
+        <v>4.745226146924911</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>MXB9rYOi</t>
+          <t>QP8QvjOG</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45606.60416666666</v>
+        <v>45606.70833333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>valladolid</t>
+          <t>real sociedad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ath bilbao</t>
+          <t>barcelona</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1375,83 +1373,83 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2001588562351072</v>
+        <v>0.2095531587057011</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2716441620333598</v>
+        <v>0.2357473035439137</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5281969817315331</v>
+        <v>0.5546995377503853</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05179615705931484</v>
+        <v>0.06045751633986929</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2408535778522491</v>
+        <v>0.1428502156665979</v>
       </c>
       <c r="R10" t="n">
-        <v>0.340700089931488</v>
+        <v>0.3223447561188271</v>
       </c>
       <c r="S10" t="n">
-        <v>0.418446272611618</v>
+        <v>0.534805028214575</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.109750709119915</v>
+        <v>-0.01989450953581029</v>
       </c>
       <c r="W10" t="n">
         <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.109750709119915</v>
+        <v>-0.01989450953581029</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.418446272611618</v>
+        <v>0.534805028214575</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>3.442693429420341</v>
+        <v>5.34805028214575</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>QP8QvjOG</t>
+          <t>SCX7iT7M</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45606.70833333334</v>
+        <v>45618.70833333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>real sociedad</t>
+          <t>getafe</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>barcelona</t>
+          <t>valladolid</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1471,64 +1469,448 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.75</v>
+        <v>1.67</v>
       </c>
       <c r="J11" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2532040348910872</v>
+        <v>0.5696460056964601</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2192875590858145</v>
+        <v>0.2718025227180252</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5275084060230983</v>
+        <v>0.1585514715855147</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05316910443931233</v>
+        <v>0.05118334759053322</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1872458159923553</v>
+        <v>0.3426184699525135</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3025525510311127</v>
+        <v>0.4034798208331402</v>
       </c>
       <c r="S11" t="n">
-        <v>0.510201632976532</v>
+        <v>0.2539017092143463</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-0.01730677304656636</v>
+        <v>0.131677298115115</v>
       </c>
       <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.131677298115115</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4034798208331402</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.034798208331401</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>C2KEmK6l</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45619.41666666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>valencia</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>betis</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>148</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.3303964757709251</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.3171806167400881</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3524229074889867</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.05092592592592604</v>
+      </c>
+      <c r="P12" t="n">
         <v>2</v>
       </c>
-      <c r="X11" t="n">
-        <v>-0.01730677304656636</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.510201632976532</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>5.496955889103862</v>
+      <c r="Q12" t="n">
+        <v>0.3375807081572289</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3114246541767539</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3509946376660172</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.001428269822969563</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.001428269822969563</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.3509946376660172</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.509946376660172</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vVwOqx6D</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45619.51041666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>atl  madrid</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>alaves</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>148</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>9</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6849315068493151</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2100456621004566</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1050228310502283</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.05797101449275366</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.5819079639761686</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3113331289129357</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1067589071108957</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.1030235428731465</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.1030235428731465</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.5819079639761686</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>5.819079639761686</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>buKPeYL5</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45619.60416666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>girona</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>espanyol</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>148</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5709391949757351</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2383671139023694</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.1906936911218955</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.04880239520958085</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5913279285595855</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.2967899811784423</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1118820902619721</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.0203887335838504</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.0203887335838504</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.5913279285595855</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>5.913279285595855</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IsCnpo0d</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45619.60416666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>las palmas</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>mallorca</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>148</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1481</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>laliga</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3351544442109687</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.3235973944105905</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.3412481613784409</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06560680698611732</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.2444187323844127</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.325586583467244</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.4299946841483434</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.08874652276990247</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.08874652276990247</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4299946841483434</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.299946841483433</v>
       </c>
     </row>
   </sheetData>
